--- a/사용자템플릿_엑셀_가공도.xlsx
+++ b/사용자템플릿_엑셀_가공도.xlsx
@@ -21,7 +21,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <x:si>
+    <x:t>{View_5}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_126}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_8}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_128}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_129}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_130}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_6}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_7}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_131}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_125}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_124}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_127}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
     <x:t>NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FA</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -30,10 +72,31 @@
     <x:t>T/W</x:t>
   </x:si>
   <x:si>
-    <x:t>MA</x:t>
+    <x:t>BILL OF MATERIAL</x:t>
   </x:si>
   <x:si>
-    <x:t>FA</x:t>
+    <x:t>DESCRIOPTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAG NO. [text]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[code]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHECKED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DP NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIZE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Image}</x:t>
   </x:si>
   <x:si>
     <x:t>NOTE</x:t>
@@ -42,190 +105,133 @@
     <x:t>REV.</x:t>
   </x:si>
   <x:si>
-    <x:t>SIZE</x:t>
+    <x:t>[no]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q'TY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRAWN</x:t>
   </x:si>
   <x:si>
     <x:t>DATE</x:t>
   </x:si>
   <x:si>
-    <x:t>{Image}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DRAWN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[no]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHECKED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q'TY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DP NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[code]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESCRIOPTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAG NO. [text]</x:t>
+    <x:t>{View_1}</x:t>
   </x:si>
   <x:si>
     <x:t>MATERIAL</x:t>
   </x:si>
   <x:si>
+    <x:t>{View_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_65}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_64}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_34}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_109}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_49}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_19}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_97}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_20}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_50}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_95}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_79}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_64}</x:t>
+    <x:t>{Input_80}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_19}</x:t>
+    <x:t>{Input_5}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_94}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_4}</x:t>
   </x:si>
   <x:si>
-    <x:t>{View_2}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_34}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_109}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_35}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_50}</x:t>
+    <x:t>{Input_52}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_5}</x:t>
+    <x:t>{Input_22}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_20}</x:t>
+    <x:t>{Input_82}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_94}</x:t>
+    <x:t>{Input_67}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_65}</x:t>
+    <x:t>{Input_36}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_7}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_110}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_21}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_83}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_37}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_66}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_80}</x:t>
+    <x:t>{Input_111}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_110}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_95}</x:t>
+    <x:t>{Input_81}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_51}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_36}</x:t>
+    <x:t>{Input_96}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_6}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_22}</x:t>
+    <x:t>{Input_54}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_7}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_96}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_111}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_125}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_81}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_124}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_37}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_8}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_67}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_82}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_97}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_112}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_52}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_113}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_98}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_53}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_83}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_9}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_38}</x:t>
+    <x:t>{Input_84}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_23}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_68}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_114}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_39}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_54}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_69}</x:t>
+    <x:t>{Input_98}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_24}</x:t>
@@ -234,10 +240,34 @@
     <x:t>{Input_99}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_84}</x:t>
+    <x:t>{Input_38}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_115}</x:t>
+    <x:t>{Input_9}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_39}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_53}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_68}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_112}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_69}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_113}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_8}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_56}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_70}</x:t>
@@ -246,97 +276,115 @@
     <x:t>{Input_55}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_25}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_40}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_100}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_10}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_85}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_26}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_101}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_116}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_41}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_56}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_71}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_86}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_11}</x:t>
   </x:si>
   <x:si>
-    <x:t>{View_3}</x:t>
+    <x:t>{Input_25}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_101}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_114}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_85}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_10}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_26}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_115}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_58}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_41}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_40}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_71}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_100}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_73}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_87}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_57}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_102}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_117}</x:t>
+    <x:t>{Input_45}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_103}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_116}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_27}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_88}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_12}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_42}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_27}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_87}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_12}</x:t>
+    <x:t>{Input_13}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_72}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_57}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_103}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_88}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_118}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_4}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_58}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_73}</x:t>
+    <x:t>{Input_117}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_43}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_13}</x:t>
+    <x:t>{Input_28}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_28}</x:t>
+    <x:t>{Input_44}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_89}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_105}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_29}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_90}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_14}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_30}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_59}</x:t>
@@ -345,22 +393,19 @@
     <x:t>{Input_74}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_119}</x:t>
+    <x:t>{Input_60}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_104}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_29}</x:t>
+    <x:t>{Input_120}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_89}</x:t>
+    <x:t>{Input_118}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_14}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_44}</x:t>
+    <x:t>{Input_119}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_15}</x:t>
@@ -369,49 +414,31 @@
     <x:t>{Input_75}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_60}</x:t>
+    <x:t>{Input_91}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_90}</x:t>
+    <x:t>{Input_32}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_30}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_45}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_105}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_31}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_127}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_120}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_46}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_16}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_126}</x:t>
+    <x:t>{Input_61}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_76}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_61}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_32}</x:t>
+    <x:t>{Input_92}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_106}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_77}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_78}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_16}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_121}</x:t>
@@ -420,91 +447,64 @@
     <x:t>{Input_47}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_17}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_107}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_31}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_62}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_17}</x:t>
+    <x:t>{Input_46}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_91}</x:t>
+    <x:t>{View_4}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_122}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_123}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_48}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_63}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_3}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_3}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_18}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_108}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAINT CODE</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_33}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_63}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_18}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_48}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_122}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_92}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_77}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_107}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_78}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_93}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_108}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_123}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_5}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_6}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_128}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_129}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAINT CODE</x:t>
-  </x:si>
-  <x:si>
     <x:t>APPROVED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_8}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_7}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_130}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_2}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_3}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_131}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BILL OF MATERIAL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -572,7 +572,7 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="41">
+  <x:borders count="50">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -896,20 +896,6 @@
       </x:bottom>
     </x:border>
     <x:border>
-      <x:left>
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="ff000000"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:left style="medium">
         <x:color rgb="ff000000"/>
       </x:left>
@@ -943,6 +929,20 @@
       </x:left>
       <x:right>
         <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
@@ -1147,13 +1147,139 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="ff000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="ff000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left>
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right>
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="80">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1279,13 +1405,10 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1312,10 +1435,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1449,7 +1572,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1463,6 +1586,51 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2071,7 +2239,7 @@
   <x:dimension ref="A1:BM1000"/>
   <x:sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="65" width="3.4296875" style="37" customWidth="1"/>
+    <x:col min="1" max="65" width="3.4296875" style="36" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:65" ht="16.5" customHeight="1">
@@ -2143,8 +2311,8 @@
     </x:row>
     <x:row r="2" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A2" s="1"/>
-      <x:c r="B2" s="78"/>
-      <x:c r="C2" s="52"/>
+      <x:c r="B2" s="77"/>
+      <x:c r="C2" s="51"/>
       <x:c r="D2" s="4"/>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="4"/>
@@ -2179,26 +2347,26 @@
       <x:c r="AI2" s="5"/>
       <x:c r="AJ2" s="5"/>
       <x:c r="AK2" s="5"/>
-      <x:c r="AL2" s="51"/>
-      <x:c r="AM2" s="52"/>
-      <x:c r="AN2" s="68" t="s">
-        <x:v>161</x:v>
+      <x:c r="AL2" s="50"/>
+      <x:c r="AM2" s="51"/>
+      <x:c r="AN2" s="67" t="s">
+        <x:v>17</x:v>
       </x:c>
-      <x:c r="AO2" s="69"/>
-      <x:c r="AP2" s="69"/>
-      <x:c r="AQ2" s="69"/>
-      <x:c r="AR2" s="69"/>
-      <x:c r="AS2" s="69"/>
-      <x:c r="AT2" s="69"/>
-      <x:c r="AU2" s="69"/>
-      <x:c r="AV2" s="69"/>
-      <x:c r="AW2" s="69"/>
-      <x:c r="AX2" s="69"/>
-      <x:c r="AY2" s="69"/>
-      <x:c r="AZ2" s="69"/>
-      <x:c r="BA2" s="69"/>
-      <x:c r="BB2" s="69"/>
-      <x:c r="BC2" s="70"/>
+      <x:c r="AO2" s="68"/>
+      <x:c r="AP2" s="68"/>
+      <x:c r="AQ2" s="68"/>
+      <x:c r="AR2" s="68"/>
+      <x:c r="AS2" s="68"/>
+      <x:c r="AT2" s="68"/>
+      <x:c r="AU2" s="68"/>
+      <x:c r="AV2" s="68"/>
+      <x:c r="AW2" s="68"/>
+      <x:c r="AX2" s="68"/>
+      <x:c r="AY2" s="68"/>
+      <x:c r="AZ2" s="68"/>
+      <x:c r="BA2" s="68"/>
+      <x:c r="BB2" s="68"/>
+      <x:c r="BC2" s="69"/>
       <x:c r="BD2" s="3"/>
       <x:c r="BE2" s="1"/>
       <x:c r="BF2" s="1"/>
@@ -2212,8 +2380,8 @@
     </x:row>
     <x:row r="3" spans="1:65" ht="17.25" customHeight="1">
       <x:c r="A3" s="1"/>
-      <x:c r="B3" s="79"/>
-      <x:c r="C3" s="78"/>
+      <x:c r="B3" s="78"/>
+      <x:c r="C3" s="77"/>
       <x:c r="D3" s="1"/>
       <x:c r="E3" s="1"/>
       <x:c r="F3" s="1"/>
@@ -2230,45 +2398,57 @@
       <x:c r="Q3" s="6"/>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
+      <x:c r="T3" s="1"/>
       <x:c r="U3" s="6"/>
       <x:c r="V3" s="1"/>
       <x:c r="W3" s="1"/>
       <x:c r="X3" s="1"/>
       <x:c r="Y3" s="1"/>
       <x:c r="Z3" s="1"/>
-      <x:c r="AL3" s="51"/>
-      <x:c r="AM3" s="51"/>
+      <x:c r="AA3" s="1"/>
+      <x:c r="AB3" s="1"/>
+      <x:c r="AC3" s="1"/>
+      <x:c r="AD3" s="1"/>
+      <x:c r="AE3" s="1"/>
+      <x:c r="AF3" s="1"/>
+      <x:c r="AG3" s="1"/>
+      <x:c r="AH3" s="1"/>
+      <x:c r="AI3" s="1"/>
+      <x:c r="AJ3" s="1"/>
+      <x:c r="AK3" s="1"/>
+      <x:c r="AL3" s="50"/>
+      <x:c r="AM3" s="50"/>
       <x:c r="AN3" s="7" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
-      <x:c r="AO3" s="56" t="s">
+      <x:c r="AO3" s="55" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="AP3" s="44"/>
+      <x:c r="AQ3" s="55" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="AR3" s="43"/>
+      <x:c r="AS3" s="44"/>
+      <x:c r="AT3" s="55" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AU3" s="43"/>
+      <x:c r="AV3" s="43"/>
+      <x:c r="AW3" s="44"/>
+      <x:c r="AX3" s="71" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AY3" s="44"/>
+      <x:c r="AZ3" s="71" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="AP3" s="45"/>
-      <x:c r="AQ3" s="56" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="AR3" s="44"/>
-      <x:c r="AS3" s="45"/>
-      <x:c r="AT3" s="56" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="AU3" s="44"/>
-      <x:c r="AV3" s="44"/>
-      <x:c r="AW3" s="45"/>
-      <x:c r="AX3" s="72" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="AY3" s="45"/>
-      <x:c r="AZ3" s="72" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BA3" s="45"/>
+      <x:c r="BA3" s="44"/>
       <x:c r="BB3" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BC3" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BD3" s="3"/>
       <x:c r="BE3" s="1"/>
@@ -2290,19 +2470,19 @@
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1"/>
       <x:c r="H4" s="1"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>27</x:v>
+      <x:c r="I4" s="79" t="s">
+        <x:v>32</x:v>
       </x:c>
-      <x:c r="J4" s="44"/>
-      <x:c r="K4" s="44"/>
-      <x:c r="L4" s="44"/>
-      <x:c r="M4" s="44"/>
-      <x:c r="N4" s="44"/>
-      <x:c r="O4" s="44"/>
-      <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="44"/>
-      <x:c r="R4" s="44"/>
-      <x:c r="S4" s="45"/>
+      <x:c r="J4" s="80"/>
+      <x:c r="K4" s="80"/>
+      <x:c r="L4" s="80"/>
+      <x:c r="M4" s="80"/>
+      <x:c r="N4" s="80"/>
+      <x:c r="O4" s="80"/>
+      <x:c r="P4" s="80"/>
+      <x:c r="Q4" s="80"/>
+      <x:c r="R4" s="80"/>
+      <x:c r="S4" s="81"/>
       <x:c r="T4" s="6"/>
       <x:c r="U4" s="1"/>
       <x:c r="V4" s="1"/>
@@ -2310,52 +2490,52 @@
       <x:c r="X4" s="1"/>
       <x:c r="Y4" s="1"/>
       <x:c r="Z4" s="6"/>
-      <x:c r="AA4" s="43" t="s">
-        <x:v>25</x:v>
+      <x:c r="AA4" s="79" t="s">
+        <x:v>34</x:v>
       </x:c>
-      <x:c r="AB4" s="44"/>
-      <x:c r="AC4" s="44"/>
-      <x:c r="AD4" s="44"/>
-      <x:c r="AE4" s="44"/>
-      <x:c r="AF4" s="44"/>
-      <x:c r="AG4" s="44"/>
-      <x:c r="AH4" s="44"/>
-      <x:c r="AI4" s="44"/>
-      <x:c r="AJ4" s="44"/>
-      <x:c r="AK4" s="45"/>
-      <x:c r="AL4" s="51"/>
-      <x:c r="AM4" s="51"/>
+      <x:c r="AB4" s="80"/>
+      <x:c r="AC4" s="80"/>
+      <x:c r="AD4" s="80"/>
+      <x:c r="AE4" s="80"/>
+      <x:c r="AF4" s="80"/>
+      <x:c r="AG4" s="80"/>
+      <x:c r="AH4" s="80"/>
+      <x:c r="AI4" s="80"/>
+      <x:c r="AJ4" s="80"/>
+      <x:c r="AK4" s="81"/>
+      <x:c r="AL4" s="50"/>
+      <x:c r="AM4" s="50"/>
       <x:c r="AN4" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
-      <x:c r="AO4" s="57" t="s">
-        <x:v>23</x:v>
+      <x:c r="AO4" s="56" t="s">
+        <x:v>40</x:v>
       </x:c>
-      <x:c r="AP4" s="58"/>
-      <x:c r="AQ4" s="57" t="s">
-        <x:v>26</x:v>
+      <x:c r="AP4" s="57"/>
+      <x:c r="AQ4" s="56" t="s">
+        <x:v>37</x:v>
       </x:c>
-      <x:c r="AR4" s="58"/>
-      <x:c r="AS4" s="58"/>
-      <x:c r="AT4" s="57" t="s">
-        <x:v>20</x:v>
+      <x:c r="AR4" s="57"/>
+      <x:c r="AS4" s="57"/>
+      <x:c r="AT4" s="56" t="s">
+        <x:v>39</x:v>
       </x:c>
-      <x:c r="AU4" s="58"/>
-      <x:c r="AV4" s="58"/>
-      <x:c r="AW4" s="58"/>
-      <x:c r="AX4" s="57" t="s">
-        <x:v>22</x:v>
+      <x:c r="AU4" s="57"/>
+      <x:c r="AV4" s="57"/>
+      <x:c r="AW4" s="57"/>
+      <x:c r="AX4" s="56" t="s">
+        <x:v>36</x:v>
       </x:c>
-      <x:c r="AY4" s="58"/>
-      <x:c r="AZ4" s="57" t="s">
-        <x:v>21</x:v>
+      <x:c r="AY4" s="57"/>
+      <x:c r="AZ4" s="56" t="s">
+        <x:v>45</x:v>
       </x:c>
-      <x:c r="BA4" s="58"/>
+      <x:c r="BA4" s="57"/>
       <x:c r="BB4" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BC4" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BD4" s="14"/>
       <x:c r="BE4" s="1"/>
@@ -2372,67 +2552,67 @@
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="10"/>
       <x:c r="H5" s="6"/>
-      <x:c r="I5" s="46"/>
-      <x:c r="J5" s="43"/>
-      <x:c r="K5" s="43"/>
-      <x:c r="L5" s="43"/>
-      <x:c r="M5" s="43"/>
-      <x:c r="N5" s="43"/>
-      <x:c r="O5" s="43"/>
-      <x:c r="P5" s="43"/>
-      <x:c r="Q5" s="43"/>
-      <x:c r="R5" s="43"/>
-      <x:c r="S5" s="47"/>
+      <x:c r="I5" s="82"/>
+      <x:c r="J5" s="42"/>
+      <x:c r="K5" s="42"/>
+      <x:c r="L5" s="42"/>
+      <x:c r="M5" s="42"/>
+      <x:c r="N5" s="42"/>
+      <x:c r="O5" s="42"/>
+      <x:c r="P5" s="42"/>
+      <x:c r="Q5" s="42"/>
+      <x:c r="R5" s="42"/>
+      <x:c r="S5" s="83"/>
       <x:c r="T5" s="6"/>
       <x:c r="V5" s="6"/>
       <x:c r="W5" s="6"/>
       <x:c r="X5" s="6"/>
       <x:c r="Y5" s="6"/>
       <x:c r="Z5" s="6"/>
-      <x:c r="AA5" s="46"/>
-      <x:c r="AB5" s="43"/>
-      <x:c r="AC5" s="43"/>
-      <x:c r="AD5" s="43"/>
-      <x:c r="AE5" s="43"/>
-      <x:c r="AF5" s="43"/>
-      <x:c r="AG5" s="43"/>
-      <x:c r="AH5" s="43"/>
-      <x:c r="AI5" s="43"/>
-      <x:c r="AJ5" s="43"/>
-      <x:c r="AK5" s="47"/>
+      <x:c r="AA5" s="82"/>
+      <x:c r="AB5" s="42"/>
+      <x:c r="AC5" s="42"/>
+      <x:c r="AD5" s="42"/>
+      <x:c r="AE5" s="42"/>
+      <x:c r="AF5" s="42"/>
+      <x:c r="AG5" s="42"/>
+      <x:c r="AH5" s="42"/>
+      <x:c r="AI5" s="42"/>
+      <x:c r="AJ5" s="42"/>
+      <x:c r="AK5" s="83"/>
       <x:c r="AL5" s="1"/>
       <x:c r="AM5" s="15"/>
       <x:c r="AN5" s="16" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
-      <x:c r="AO5" s="38" t="s">
-        <x:v>32</x:v>
+      <x:c r="AO5" s="37" t="s">
+        <x:v>42</x:v>
       </x:c>
-      <x:c r="AP5" s="38"/>
-      <x:c r="AQ5" s="38" t="s">
-        <x:v>29</x:v>
+      <x:c r="AP5" s="37"/>
+      <x:c r="AQ5" s="37" t="s">
+        <x:v>50</x:v>
       </x:c>
-      <x:c r="AR5" s="38"/>
-      <x:c r="AS5" s="38"/>
-      <x:c r="AT5" s="38" t="s">
-        <x:v>30</x:v>
+      <x:c r="AR5" s="37"/>
+      <x:c r="AS5" s="37"/>
+      <x:c r="AT5" s="37" t="s">
+        <x:v>43</x:v>
       </x:c>
-      <x:c r="AU5" s="38"/>
-      <x:c r="AV5" s="38"/>
-      <x:c r="AW5" s="38"/>
-      <x:c r="AX5" s="38" t="s">
-        <x:v>34</x:v>
+      <x:c r="AU5" s="37"/>
+      <x:c r="AV5" s="37"/>
+      <x:c r="AW5" s="37"/>
+      <x:c r="AX5" s="37" t="s">
+        <x:v>35</x:v>
       </x:c>
-      <x:c r="AY5" s="38"/>
-      <x:c r="AZ5" s="38" t="s">
-        <x:v>37</x:v>
+      <x:c r="AY5" s="37"/>
+      <x:c r="AZ5" s="37" t="s">
+        <x:v>46</x:v>
       </x:c>
-      <x:c r="BA5" s="38"/>
+      <x:c r="BA5" s="37"/>
       <x:c r="BB5" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="BC5" s="17" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BD5" s="3"/>
       <x:c r="BE5" s="1"/>
@@ -2454,17 +2634,17 @@
       <x:c r="F6" s="6"/>
       <x:c r="G6" s="6"/>
       <x:c r="H6" s="6"/>
-      <x:c r="I6" s="46"/>
-      <x:c r="J6" s="43"/>
-      <x:c r="K6" s="43"/>
-      <x:c r="L6" s="43"/>
-      <x:c r="M6" s="43"/>
-      <x:c r="N6" s="43"/>
-      <x:c r="O6" s="43"/>
-      <x:c r="P6" s="43"/>
-      <x:c r="Q6" s="43"/>
-      <x:c r="R6" s="43"/>
-      <x:c r="S6" s="47"/>
+      <x:c r="I6" s="82"/>
+      <x:c r="J6" s="42"/>
+      <x:c r="K6" s="42"/>
+      <x:c r="L6" s="42"/>
+      <x:c r="M6" s="42"/>
+      <x:c r="N6" s="42"/>
+      <x:c r="O6" s="42"/>
+      <x:c r="P6" s="42"/>
+      <x:c r="Q6" s="42"/>
+      <x:c r="R6" s="42"/>
+      <x:c r="S6" s="83"/>
       <x:c r="T6" s="6"/>
       <x:c r="U6" s="6"/>
       <x:c r="V6" s="6"/>
@@ -2472,50 +2652,50 @@
       <x:c r="X6" s="6"/>
       <x:c r="Y6" s="6"/>
       <x:c r="Z6" s="6"/>
-      <x:c r="AA6" s="46"/>
-      <x:c r="AB6" s="43"/>
-      <x:c r="AC6" s="43"/>
-      <x:c r="AD6" s="43"/>
-      <x:c r="AE6" s="43"/>
-      <x:c r="AF6" s="43"/>
-      <x:c r="AG6" s="43"/>
-      <x:c r="AH6" s="43"/>
-      <x:c r="AI6" s="43"/>
-      <x:c r="AJ6" s="43"/>
-      <x:c r="AK6" s="47"/>
+      <x:c r="AA6" s="82"/>
+      <x:c r="AB6" s="42"/>
+      <x:c r="AC6" s="42"/>
+      <x:c r="AD6" s="42"/>
+      <x:c r="AE6" s="42"/>
+      <x:c r="AF6" s="42"/>
+      <x:c r="AG6" s="42"/>
+      <x:c r="AH6" s="42"/>
+      <x:c r="AI6" s="42"/>
+      <x:c r="AJ6" s="42"/>
+      <x:c r="AK6" s="83"/>
       <x:c r="AL6" s="1"/>
       <x:c r="AM6" s="15"/>
       <x:c r="AN6" s="16" t="s">
-        <x:v>42</x:v>
+        <x:v>66</x:v>
       </x:c>
-      <x:c r="AO6" s="38" t="s">
-        <x:v>35</x:v>
+      <x:c r="AO6" s="37" t="s">
+        <x:v>58</x:v>
       </x:c>
-      <x:c r="AP6" s="38"/>
-      <x:c r="AQ6" s="38" t="s">
-        <x:v>41</x:v>
+      <x:c r="AP6" s="37"/>
+      <x:c r="AQ6" s="37" t="s">
+        <x:v>55</x:v>
       </x:c>
-      <x:c r="AR6" s="38"/>
-      <x:c r="AS6" s="38"/>
-      <x:c r="AT6" s="38" t="s">
-        <x:v>40</x:v>
+      <x:c r="AR6" s="37"/>
+      <x:c r="AS6" s="37"/>
+      <x:c r="AT6" s="37" t="s">
+        <x:v>64</x:v>
       </x:c>
-      <x:c r="AU6" s="38"/>
-      <x:c r="AV6" s="38"/>
-      <x:c r="AW6" s="38"/>
-      <x:c r="AX6" s="38" t="s">
-        <x:v>36</x:v>
+      <x:c r="AU6" s="37"/>
+      <x:c r="AV6" s="37"/>
+      <x:c r="AW6" s="37"/>
+      <x:c r="AX6" s="37" t="s">
+        <x:v>61</x:v>
       </x:c>
-      <x:c r="AY6" s="38"/>
-      <x:c r="AZ6" s="38" t="s">
-        <x:v>48</x:v>
+      <x:c r="AY6" s="37"/>
+      <x:c r="AZ6" s="37" t="s">
+        <x:v>63</x:v>
       </x:c>
-      <x:c r="BA6" s="38"/>
+      <x:c r="BA6" s="37"/>
       <x:c r="BB6" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BC6" s="17" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BD6" s="3"/>
       <x:c r="BE6" s="1"/>
@@ -2531,78 +2711,78 @@
     <x:row r="7" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A7" s="9"/>
       <x:c r="B7" s="10"/>
-      <x:c r="C7" s="43" t="s">
-        <x:v>49</x:v>
+      <x:c r="C7" s="79" t="s">
+        <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="44"/>
-      <x:c r="E7" s="44"/>
-      <x:c r="F7" s="44"/>
-      <x:c r="G7" s="44"/>
-      <x:c r="H7" s="45"/>
-      <x:c r="I7" s="46"/>
-      <x:c r="J7" s="43"/>
-      <x:c r="K7" s="43"/>
-      <x:c r="L7" s="43"/>
-      <x:c r="M7" s="43"/>
-      <x:c r="N7" s="43"/>
-      <x:c r="O7" s="43"/>
-      <x:c r="P7" s="43"/>
-      <x:c r="Q7" s="43"/>
-      <x:c r="R7" s="43"/>
-      <x:c r="S7" s="47"/>
+      <x:c r="D7" s="80"/>
+      <x:c r="E7" s="80"/>
+      <x:c r="F7" s="80"/>
+      <x:c r="G7" s="80"/>
+      <x:c r="H7" s="81"/>
+      <x:c r="I7" s="82"/>
+      <x:c r="J7" s="42"/>
+      <x:c r="K7" s="42"/>
+      <x:c r="L7" s="42"/>
+      <x:c r="M7" s="42"/>
+      <x:c r="N7" s="42"/>
+      <x:c r="O7" s="42"/>
+      <x:c r="P7" s="42"/>
+      <x:c r="Q7" s="42"/>
+      <x:c r="R7" s="42"/>
+      <x:c r="S7" s="83"/>
       <x:c r="T7" s="6"/>
-      <x:c r="U7" s="43" t="s">
-        <x:v>47</x:v>
+      <x:c r="U7" s="79" t="s">
+        <x:v>9</x:v>
       </x:c>
-      <x:c r="V7" s="44"/>
-      <x:c r="W7" s="44"/>
-      <x:c r="X7" s="44"/>
-      <x:c r="Y7" s="44"/>
-      <x:c r="Z7" s="45"/>
-      <x:c r="AA7" s="46"/>
-      <x:c r="AB7" s="43"/>
-      <x:c r="AC7" s="43"/>
-      <x:c r="AD7" s="43"/>
-      <x:c r="AE7" s="43"/>
-      <x:c r="AF7" s="43"/>
-      <x:c r="AG7" s="43"/>
-      <x:c r="AH7" s="43"/>
-      <x:c r="AI7" s="43"/>
-      <x:c r="AJ7" s="43"/>
-      <x:c r="AK7" s="47"/>
+      <x:c r="V7" s="80"/>
+      <x:c r="W7" s="80"/>
+      <x:c r="X7" s="80"/>
+      <x:c r="Y7" s="80"/>
+      <x:c r="Z7" s="81"/>
+      <x:c r="AA7" s="82"/>
+      <x:c r="AB7" s="42"/>
+      <x:c r="AC7" s="42"/>
+      <x:c r="AD7" s="42"/>
+      <x:c r="AE7" s="42"/>
+      <x:c r="AF7" s="42"/>
+      <x:c r="AG7" s="42"/>
+      <x:c r="AH7" s="42"/>
+      <x:c r="AI7" s="42"/>
+      <x:c r="AJ7" s="42"/>
+      <x:c r="AK7" s="83"/>
       <x:c r="AL7" s="1"/>
       <x:c r="AM7" s="6"/>
       <x:c r="AN7" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="AO7" s="38" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AP7" s="38"/>
-      <x:c r="AQ7" s="38" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AR7" s="38"/>
-      <x:c r="AS7" s="38"/>
-      <x:c r="AT7" s="38" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="AU7" s="38"/>
-      <x:c r="AV7" s="38"/>
-      <x:c r="AW7" s="38"/>
-      <x:c r="AX7" s="38" t="s">
+      <x:c r="AO7" s="37" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="AY7" s="38"/>
-      <x:c r="AZ7" s="38" t="s">
+      <x:c r="AP7" s="37"/>
+      <x:c r="AQ7" s="37" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AR7" s="37"/>
+      <x:c r="AS7" s="37"/>
+      <x:c r="AT7" s="37" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AU7" s="37"/>
+      <x:c r="AV7" s="37"/>
+      <x:c r="AW7" s="37"/>
+      <x:c r="AX7" s="37" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AY7" s="37"/>
+      <x:c r="AZ7" s="37" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="BA7" s="38"/>
+      <x:c r="BA7" s="37"/>
       <x:c r="BB7" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BC7" s="17" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BD7" s="14"/>
       <x:c r="BE7" s="1"/>
@@ -2618,74 +2798,74 @@
     <x:row r="8" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="10"/>
-      <x:c r="C8" s="48"/>
-      <x:c r="D8" s="49"/>
-      <x:c r="E8" s="49"/>
-      <x:c r="F8" s="49"/>
-      <x:c r="G8" s="49"/>
-      <x:c r="H8" s="50"/>
-      <x:c r="I8" s="46"/>
-      <x:c r="J8" s="43"/>
-      <x:c r="K8" s="43"/>
-      <x:c r="L8" s="43"/>
-      <x:c r="M8" s="43"/>
-      <x:c r="N8" s="43"/>
-      <x:c r="O8" s="43"/>
-      <x:c r="P8" s="43"/>
-      <x:c r="Q8" s="43"/>
-      <x:c r="R8" s="43"/>
-      <x:c r="S8" s="47"/>
+      <x:c r="C8" s="84"/>
+      <x:c r="D8" s="85"/>
+      <x:c r="E8" s="85"/>
+      <x:c r="F8" s="85"/>
+      <x:c r="G8" s="85"/>
+      <x:c r="H8" s="86"/>
+      <x:c r="I8" s="82"/>
+      <x:c r="J8" s="42"/>
+      <x:c r="K8" s="42"/>
+      <x:c r="L8" s="42"/>
+      <x:c r="M8" s="42"/>
+      <x:c r="N8" s="42"/>
+      <x:c r="O8" s="42"/>
+      <x:c r="P8" s="42"/>
+      <x:c r="Q8" s="42"/>
+      <x:c r="R8" s="42"/>
+      <x:c r="S8" s="83"/>
       <x:c r="T8" s="6"/>
-      <x:c r="U8" s="48"/>
-      <x:c r="V8" s="49"/>
-      <x:c r="W8" s="49"/>
-      <x:c r="X8" s="49"/>
-      <x:c r="Y8" s="49"/>
-      <x:c r="Z8" s="50"/>
-      <x:c r="AA8" s="46"/>
-      <x:c r="AB8" s="43"/>
-      <x:c r="AC8" s="43"/>
-      <x:c r="AD8" s="43"/>
-      <x:c r="AE8" s="43"/>
-      <x:c r="AF8" s="43"/>
-      <x:c r="AG8" s="43"/>
-      <x:c r="AH8" s="43"/>
-      <x:c r="AI8" s="43"/>
-      <x:c r="AJ8" s="43"/>
-      <x:c r="AK8" s="47"/>
+      <x:c r="U8" s="84"/>
+      <x:c r="V8" s="85"/>
+      <x:c r="W8" s="85"/>
+      <x:c r="X8" s="85"/>
+      <x:c r="Y8" s="85"/>
+      <x:c r="Z8" s="86"/>
+      <x:c r="AA8" s="82"/>
+      <x:c r="AB8" s="42"/>
+      <x:c r="AC8" s="42"/>
+      <x:c r="AD8" s="42"/>
+      <x:c r="AE8" s="42"/>
+      <x:c r="AF8" s="42"/>
+      <x:c r="AG8" s="42"/>
+      <x:c r="AH8" s="42"/>
+      <x:c r="AI8" s="42"/>
+      <x:c r="AJ8" s="42"/>
+      <x:c r="AK8" s="83"/>
       <x:c r="AL8" s="1"/>
       <x:c r="AM8" s="6"/>
       <x:c r="AN8" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
-      <x:c r="AO8" s="38" t="s">
-        <x:v>63</x:v>
+      <x:c r="AO8" s="37" t="s">
+        <x:v>69</x:v>
       </x:c>
-      <x:c r="AP8" s="38"/>
-      <x:c r="AQ8" s="38" t="s">
-        <x:v>62</x:v>
+      <x:c r="AP8" s="37"/>
+      <x:c r="AQ8" s="37" t="s">
+        <x:v>73</x:v>
       </x:c>
-      <x:c r="AR8" s="38"/>
-      <x:c r="AS8" s="38"/>
-      <x:c r="AT8" s="38" t="s">
+      <x:c r="AR8" s="37"/>
+      <x:c r="AS8" s="37"/>
+      <x:c r="AT8" s="37" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="AU8" s="37"/>
+      <x:c r="AV8" s="37"/>
+      <x:c r="AW8" s="37"/>
+      <x:c r="AX8" s="37" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="AY8" s="37"/>
+      <x:c r="AZ8" s="37" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="AU8" s="38"/>
-      <x:c r="AV8" s="38"/>
-      <x:c r="AW8" s="38"/>
-      <x:c r="AX8" s="38" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="AY8" s="38"/>
-      <x:c r="AZ8" s="38" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="BA8" s="38"/>
+      <x:c r="BA8" s="37"/>
       <x:c r="BB8" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BC8" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BD8" s="3"/>
       <x:c r="BE8" s="1"/>
@@ -2701,63 +2881,74 @@
     <x:row r="9" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="10"/>
+      <x:c r="C9" s="1"/>
+      <x:c r="D9" s="1"/>
+      <x:c r="E9" s="1"/>
+      <x:c r="F9" s="1"/>
+      <x:c r="G9" s="1"/>
       <x:c r="H9" s="6"/>
-      <x:c r="I9" s="46"/>
-      <x:c r="J9" s="43"/>
-      <x:c r="K9" s="43"/>
-      <x:c r="L9" s="43"/>
-      <x:c r="M9" s="43"/>
-      <x:c r="N9" s="43"/>
-      <x:c r="O9" s="43"/>
-      <x:c r="P9" s="43"/>
-      <x:c r="Q9" s="43"/>
-      <x:c r="R9" s="43"/>
-      <x:c r="S9" s="47"/>
+      <x:c r="I9" s="82"/>
+      <x:c r="J9" s="42"/>
+      <x:c r="K9" s="42"/>
+      <x:c r="L9" s="42"/>
+      <x:c r="M9" s="42"/>
+      <x:c r="N9" s="42"/>
+      <x:c r="O9" s="42"/>
+      <x:c r="P9" s="42"/>
+      <x:c r="Q9" s="42"/>
+      <x:c r="R9" s="42"/>
+      <x:c r="S9" s="83"/>
       <x:c r="T9" s="6"/>
-      <x:c r="AA9" s="46"/>
-      <x:c r="AB9" s="43"/>
-      <x:c r="AC9" s="43"/>
-      <x:c r="AD9" s="43"/>
-      <x:c r="AE9" s="43"/>
-      <x:c r="AF9" s="43"/>
-      <x:c r="AG9" s="43"/>
-      <x:c r="AH9" s="43"/>
-      <x:c r="AI9" s="43"/>
-      <x:c r="AJ9" s="43"/>
-      <x:c r="AK9" s="47"/>
+      <x:c r="U9" s="1"/>
+      <x:c r="V9" s="1"/>
+      <x:c r="W9" s="1"/>
+      <x:c r="X9" s="1"/>
+      <x:c r="Y9" s="1"/>
+      <x:c r="Z9" s="1"/>
+      <x:c r="AA9" s="82"/>
+      <x:c r="AB9" s="42"/>
+      <x:c r="AC9" s="42"/>
+      <x:c r="AD9" s="42"/>
+      <x:c r="AE9" s="42"/>
+      <x:c r="AF9" s="42"/>
+      <x:c r="AG9" s="42"/>
+      <x:c r="AH9" s="42"/>
+      <x:c r="AI9" s="42"/>
+      <x:c r="AJ9" s="42"/>
+      <x:c r="AK9" s="83"/>
       <x:c r="AL9" s="6"/>
       <x:c r="AM9" s="6"/>
       <x:c r="AN9" s="16" t="s">
-        <x:v>61</x:v>
+        <x:v>74</x:v>
       </x:c>
-      <x:c r="AO9" s="38" t="s">
-        <x:v>69</x:v>
+      <x:c r="AO9" s="37" t="s">
+        <x:v>71</x:v>
       </x:c>
-      <x:c r="AP9" s="38"/>
-      <x:c r="AQ9" s="38" t="s">
-        <x:v>66</x:v>
+      <x:c r="AP9" s="37"/>
+      <x:c r="AQ9" s="37" t="s">
+        <x:v>75</x:v>
       </x:c>
-      <x:c r="AR9" s="38"/>
-      <x:c r="AS9" s="38"/>
-      <x:c r="AT9" s="38" t="s">
+      <x:c r="AR9" s="37"/>
+      <x:c r="AS9" s="37"/>
+      <x:c r="AT9" s="37" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="AU9" s="38"/>
-      <x:c r="AV9" s="38"/>
-      <x:c r="AW9" s="38"/>
-      <x:c r="AX9" s="38" t="s">
+      <x:c r="AU9" s="37"/>
+      <x:c r="AV9" s="37"/>
+      <x:c r="AW9" s="37"/>
+      <x:c r="AX9" s="37" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="AY9" s="37"/>
+      <x:c r="AZ9" s="37" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="AY9" s="38"/>
-      <x:c r="AZ9" s="38" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="BA9" s="38"/>
+      <x:c r="BA9" s="37"/>
       <x:c r="BB9" s="6" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BC9" s="17" t="s">
-        <x:v>65</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BD9" s="3"/>
       <x:c r="BE9" s="1"/>
@@ -2774,17 +2965,17 @@
       <x:c r="A10" s="9"/>
       <x:c r="B10" s="10"/>
       <x:c r="H10" s="1"/>
-      <x:c r="I10" s="46"/>
-      <x:c r="J10" s="43"/>
-      <x:c r="K10" s="43"/>
-      <x:c r="L10" s="43"/>
-      <x:c r="M10" s="43"/>
-      <x:c r="N10" s="43"/>
-      <x:c r="O10" s="43"/>
-      <x:c r="P10" s="43"/>
-      <x:c r="Q10" s="43"/>
-      <x:c r="R10" s="43"/>
-      <x:c r="S10" s="47"/>
+      <x:c r="I10" s="82"/>
+      <x:c r="J10" s="42"/>
+      <x:c r="K10" s="42"/>
+      <x:c r="L10" s="42"/>
+      <x:c r="M10" s="42"/>
+      <x:c r="N10" s="42"/>
+      <x:c r="O10" s="42"/>
+      <x:c r="P10" s="42"/>
+      <x:c r="Q10" s="42"/>
+      <x:c r="R10" s="42"/>
+      <x:c r="S10" s="83"/>
       <x:c r="T10" s="6"/>
       <x:c r="U10" s="1"/>
       <x:c r="V10" s="1"/>
@@ -2792,50 +2983,50 @@
       <x:c r="X10" s="1"/>
       <x:c r="Y10" s="1"/>
       <x:c r="Z10" s="1"/>
-      <x:c r="AA10" s="46"/>
-      <x:c r="AB10" s="43"/>
-      <x:c r="AC10" s="43"/>
-      <x:c r="AD10" s="43"/>
-      <x:c r="AE10" s="43"/>
-      <x:c r="AF10" s="43"/>
-      <x:c r="AG10" s="43"/>
-      <x:c r="AH10" s="43"/>
-      <x:c r="AI10" s="43"/>
-      <x:c r="AJ10" s="43"/>
-      <x:c r="AK10" s="47"/>
+      <x:c r="AA10" s="82"/>
+      <x:c r="AB10" s="42"/>
+      <x:c r="AC10" s="42"/>
+      <x:c r="AD10" s="42"/>
+      <x:c r="AE10" s="42"/>
+      <x:c r="AF10" s="42"/>
+      <x:c r="AG10" s="42"/>
+      <x:c r="AH10" s="42"/>
+      <x:c r="AI10" s="42"/>
+      <x:c r="AJ10" s="42"/>
+      <x:c r="AK10" s="83"/>
       <x:c r="AL10" s="1"/>
       <x:c r="AM10" s="6"/>
       <x:c r="AN10" s="16" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
-      <x:c r="AO10" s="38" t="s">
-        <x:v>75</x:v>
+      <x:c r="AO10" s="37" t="s">
+        <x:v>87</x:v>
       </x:c>
-      <x:c r="AP10" s="38"/>
-      <x:c r="AQ10" s="38" t="s">
-        <x:v>76</x:v>
+      <x:c r="AP10" s="37"/>
+      <x:c r="AQ10" s="37" t="s">
+        <x:v>96</x:v>
       </x:c>
-      <x:c r="AR10" s="38"/>
-      <x:c r="AS10" s="38"/>
-      <x:c r="AT10" s="38" t="s">
-        <x:v>74</x:v>
+      <x:c r="AR10" s="37"/>
+      <x:c r="AS10" s="37"/>
+      <x:c r="AT10" s="37" t="s">
+        <x:v>84</x:v>
       </x:c>
-      <x:c r="AU10" s="38"/>
-      <x:c r="AV10" s="38"/>
-      <x:c r="AW10" s="38"/>
-      <x:c r="AX10" s="38" t="s">
-        <x:v>73</x:v>
+      <x:c r="AU10" s="37"/>
+      <x:c r="AV10" s="37"/>
+      <x:c r="AW10" s="37"/>
+      <x:c r="AX10" s="37" t="s">
+        <x:v>83</x:v>
       </x:c>
-      <x:c r="AY10" s="38"/>
-      <x:c r="AZ10" s="38" t="s">
-        <x:v>79</x:v>
+      <x:c r="AY10" s="37"/>
+      <x:c r="AZ10" s="37" t="s">
+        <x:v>90</x:v>
       </x:c>
-      <x:c r="BA10" s="38"/>
+      <x:c r="BA10" s="37"/>
       <x:c r="BB10" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BC10" s="17" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BD10" s="14"/>
       <x:c r="BE10" s="1"/>
@@ -2851,61 +3042,64 @@
     <x:row r="11" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="10"/>
-      <x:c r="I11" s="48"/>
-      <x:c r="J11" s="49"/>
-      <x:c r="K11" s="49"/>
-      <x:c r="L11" s="49"/>
-      <x:c r="M11" s="49"/>
-      <x:c r="N11" s="49"/>
-      <x:c r="O11" s="49"/>
-      <x:c r="P11" s="49"/>
-      <x:c r="Q11" s="49"/>
-      <x:c r="R11" s="49"/>
-      <x:c r="S11" s="50"/>
-      <x:c r="AA11" s="48"/>
-      <x:c r="AB11" s="49"/>
-      <x:c r="AC11" s="49"/>
-      <x:c r="AD11" s="49"/>
-      <x:c r="AE11" s="49"/>
-      <x:c r="AF11" s="49"/>
-      <x:c r="AG11" s="49"/>
-      <x:c r="AH11" s="49"/>
-      <x:c r="AI11" s="49"/>
-      <x:c r="AJ11" s="49"/>
-      <x:c r="AK11" s="50"/>
+      <x:c r="H11" s="1"/>
+      <x:c r="I11" s="84"/>
+      <x:c r="J11" s="85"/>
+      <x:c r="K11" s="85"/>
+      <x:c r="L11" s="85"/>
+      <x:c r="M11" s="85"/>
+      <x:c r="N11" s="85"/>
+      <x:c r="O11" s="85"/>
+      <x:c r="P11" s="85"/>
+      <x:c r="Q11" s="85"/>
+      <x:c r="R11" s="85"/>
+      <x:c r="S11" s="86"/>
+      <x:c r="T11" s="1"/>
+      <x:c r="Z11" s="1"/>
+      <x:c r="AA11" s="84"/>
+      <x:c r="AB11" s="85"/>
+      <x:c r="AC11" s="85"/>
+      <x:c r="AD11" s="85"/>
+      <x:c r="AE11" s="85"/>
+      <x:c r="AF11" s="85"/>
+      <x:c r="AG11" s="85"/>
+      <x:c r="AH11" s="85"/>
+      <x:c r="AI11" s="85"/>
+      <x:c r="AJ11" s="85"/>
+      <x:c r="AK11" s="86"/>
       <x:c r="AL11" s="1"/>
       <x:c r="AM11" s="6"/>
       <x:c r="AN11" s="16" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
-      <x:c r="AO11" s="38" t="s">
-        <x:v>80</x:v>
+      <x:c r="AO11" s="37" t="s">
+        <x:v>92</x:v>
       </x:c>
-      <x:c r="AP11" s="38"/>
-      <x:c r="AQ11" s="38" t="s">
-        <x:v>83</x:v>
+      <x:c r="AP11" s="37"/>
+      <x:c r="AQ11" s="37" t="s">
+        <x:v>95</x:v>
       </x:c>
-      <x:c r="AR11" s="38"/>
-      <x:c r="AS11" s="38"/>
-      <x:c r="AT11" s="38" t="s">
-        <x:v>84</x:v>
+      <x:c r="AR11" s="37"/>
+      <x:c r="AS11" s="37"/>
+      <x:c r="AT11" s="37" t="s">
+        <x:v>82</x:v>
       </x:c>
-      <x:c r="AU11" s="38"/>
-      <x:c r="AV11" s="38"/>
-      <x:c r="AW11" s="38"/>
-      <x:c r="AX11" s="38" t="s">
+      <x:c r="AU11" s="37"/>
+      <x:c r="AV11" s="37"/>
+      <x:c r="AW11" s="37"/>
+      <x:c r="AX11" s="37" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="AY11" s="37"/>
+      <x:c r="AZ11" s="37" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="AY11" s="38"/>
-      <x:c r="AZ11" s="38" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BA11" s="38"/>
+      <x:c r="BA11" s="37"/>
       <x:c r="BB11" s="6" t="s">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BC11" s="17" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BD11" s="3"/>
       <x:c r="BE11" s="1"/>
@@ -2921,39 +3115,64 @@
     <x:row r="12" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="10"/>
+      <x:c r="H12" s="1"/>
+      <x:c r="I12" s="1"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+      <x:c r="M12" s="1"/>
+      <x:c r="N12" s="1"/>
+      <x:c r="O12" s="1"/>
+      <x:c r="P12" s="1"/>
+      <x:c r="Q12" s="1"/>
+      <x:c r="R12" s="1"/>
+      <x:c r="S12" s="1"/>
+      <x:c r="T12" s="1"/>
+      <x:c r="Z12" s="1"/>
+      <x:c r="AA12" s="1"/>
+      <x:c r="AB12" s="1"/>
+      <x:c r="AC12" s="1"/>
+      <x:c r="AD12" s="1"/>
+      <x:c r="AE12" s="1"/>
+      <x:c r="AF12" s="1"/>
+      <x:c r="AG12" s="1"/>
+      <x:c r="AH12" s="1"/>
+      <x:c r="AI12" s="1"/>
+      <x:c r="AJ12" s="1"/>
+      <x:c r="AK12" s="1"/>
       <x:c r="AL12" s="1"/>
       <x:c r="AM12" s="6"/>
       <x:c r="AN12" s="16" t="s">
-        <x:v>94</x:v>
+        <x:v>108</x:v>
       </x:c>
-      <x:c r="AO12" s="38" t="s">
-        <x:v>92</x:v>
+      <x:c r="AO12" s="37" t="s">
+        <x:v>106</x:v>
       </x:c>
-      <x:c r="AP12" s="38"/>
-      <x:c r="AQ12" s="38" t="s">
-        <x:v>91</x:v>
+      <x:c r="AP12" s="37"/>
+      <x:c r="AQ12" s="37" t="s">
+        <x:v>109</x:v>
       </x:c>
-      <x:c r="AR12" s="38"/>
-      <x:c r="AS12" s="38"/>
-      <x:c r="AT12" s="38" t="s">
-        <x:v>96</x:v>
+      <x:c r="AR12" s="37"/>
+      <x:c r="AS12" s="37"/>
+      <x:c r="AT12" s="37" t="s">
+        <x:v>101</x:v>
       </x:c>
-      <x:c r="AU12" s="38"/>
-      <x:c r="AV12" s="38"/>
-      <x:c r="AW12" s="38"/>
-      <x:c r="AX12" s="38" t="s">
-        <x:v>95</x:v>
+      <x:c r="AU12" s="37"/>
+      <x:c r="AV12" s="37"/>
+      <x:c r="AW12" s="37"/>
+      <x:c r="AX12" s="37" t="s">
+        <x:v>111</x:v>
       </x:c>
-      <x:c r="AY12" s="38"/>
-      <x:c r="AZ12" s="38" t="s">
-        <x:v>93</x:v>
+      <x:c r="AY12" s="37"/>
+      <x:c r="AZ12" s="37" t="s">
+        <x:v>100</x:v>
       </x:c>
-      <x:c r="BA12" s="38"/>
+      <x:c r="BA12" s="37"/>
       <x:c r="BB12" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="BC12" s="17" t="s">
-        <x:v>90</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BD12" s="3"/>
       <x:c r="BE12" s="1"/>
@@ -2969,67 +3188,68 @@
     <x:row r="13" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A13" s="9"/>
       <x:c r="B13" s="10"/>
-      <x:c r="I13" s="43" t="s">
-        <x:v>88</x:v>
+      <x:c r="H13" s="1"/>
+      <x:c r="I13" s="79" t="s">
+        <x:v>154</x:v>
       </x:c>
-      <x:c r="J13" s="44"/>
-      <x:c r="K13" s="44"/>
-      <x:c r="L13" s="44"/>
-      <x:c r="M13" s="44"/>
-      <x:c r="N13" s="44"/>
-      <x:c r="O13" s="44"/>
-      <x:c r="P13" s="44"/>
-      <x:c r="Q13" s="44"/>
-      <x:c r="R13" s="44"/>
-      <x:c r="S13" s="45"/>
+      <x:c r="J13" s="80"/>
+      <x:c r="K13" s="80"/>
+      <x:c r="L13" s="80"/>
+      <x:c r="M13" s="80"/>
+      <x:c r="N13" s="80"/>
+      <x:c r="O13" s="80"/>
+      <x:c r="P13" s="80"/>
+      <x:c r="Q13" s="80"/>
+      <x:c r="R13" s="80"/>
+      <x:c r="S13" s="81"/>
       <x:c r="T13" s="6"/>
       <x:c r="Z13" s="6"/>
-      <x:c r="AA13" s="43" t="s">
-        <x:v>100</x:v>
+      <x:c r="AA13" s="79" t="s">
+        <x:v>147</x:v>
       </x:c>
-      <x:c r="AB13" s="44"/>
-      <x:c r="AC13" s="44"/>
-      <x:c r="AD13" s="44"/>
-      <x:c r="AE13" s="44"/>
-      <x:c r="AF13" s="44"/>
-      <x:c r="AG13" s="44"/>
-      <x:c r="AH13" s="44"/>
-      <x:c r="AI13" s="44"/>
-      <x:c r="AJ13" s="44"/>
-      <x:c r="AK13" s="45"/>
+      <x:c r="AB13" s="80"/>
+      <x:c r="AC13" s="80"/>
+      <x:c r="AD13" s="80"/>
+      <x:c r="AE13" s="80"/>
+      <x:c r="AF13" s="80"/>
+      <x:c r="AG13" s="80"/>
+      <x:c r="AH13" s="80"/>
+      <x:c r="AI13" s="80"/>
+      <x:c r="AJ13" s="80"/>
+      <x:c r="AK13" s="81"/>
       <x:c r="AL13" s="1"/>
       <x:c r="AM13" s="6"/>
       <x:c r="AN13" s="16" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="AO13" s="37" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AP13" s="37"/>
+      <x:c r="AQ13" s="37" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="AR13" s="37"/>
+      <x:c r="AS13" s="37"/>
+      <x:c r="AT13" s="37" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="AU13" s="37"/>
+      <x:c r="AV13" s="37"/>
+      <x:c r="AW13" s="37"/>
+      <x:c r="AX13" s="37" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="AY13" s="37"/>
+      <x:c r="AZ13" s="37" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="BA13" s="37"/>
+      <x:c r="BB13" s="6" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="AO13" s="38" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="AP13" s="38"/>
-      <x:c r="AQ13" s="38" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="AR13" s="38"/>
-      <x:c r="AS13" s="38"/>
-      <x:c r="AT13" s="38" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AU13" s="38"/>
-      <x:c r="AV13" s="38"/>
-      <x:c r="AW13" s="38"/>
-      <x:c r="AX13" s="38" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="AY13" s="38"/>
-      <x:c r="AZ13" s="38" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BA13" s="38"/>
-      <x:c r="BB13" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="BC13" s="17" t="s">
-        <x:v>99</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="BD13" s="14"/>
       <x:c r="BE13" s="1"/>
@@ -3051,17 +3271,17 @@
       <x:c r="F14" s="6"/>
       <x:c r="G14" s="6"/>
       <x:c r="H14" s="6"/>
-      <x:c r="I14" s="46"/>
-      <x:c r="J14" s="43"/>
-      <x:c r="K14" s="43"/>
-      <x:c r="L14" s="43"/>
-      <x:c r="M14" s="43"/>
-      <x:c r="N14" s="43"/>
-      <x:c r="O14" s="43"/>
-      <x:c r="P14" s="43"/>
-      <x:c r="Q14" s="43"/>
-      <x:c r="R14" s="43"/>
-      <x:c r="S14" s="47"/>
+      <x:c r="I14" s="82"/>
+      <x:c r="J14" s="42"/>
+      <x:c r="K14" s="42"/>
+      <x:c r="L14" s="42"/>
+      <x:c r="M14" s="42"/>
+      <x:c r="N14" s="42"/>
+      <x:c r="O14" s="42"/>
+      <x:c r="P14" s="42"/>
+      <x:c r="Q14" s="42"/>
+      <x:c r="R14" s="42"/>
+      <x:c r="S14" s="83"/>
       <x:c r="T14" s="6"/>
       <x:c r="U14" s="6"/>
       <x:c r="V14" s="6"/>
@@ -3069,50 +3289,50 @@
       <x:c r="X14" s="6"/>
       <x:c r="Y14" s="6"/>
       <x:c r="Z14" s="6"/>
-      <x:c r="AA14" s="46"/>
-      <x:c r="AB14" s="43"/>
-      <x:c r="AC14" s="43"/>
-      <x:c r="AD14" s="43"/>
-      <x:c r="AE14" s="43"/>
-      <x:c r="AF14" s="43"/>
-      <x:c r="AG14" s="43"/>
-      <x:c r="AH14" s="43"/>
-      <x:c r="AI14" s="43"/>
-      <x:c r="AJ14" s="43"/>
-      <x:c r="AK14" s="47"/>
+      <x:c r="AA14" s="82"/>
+      <x:c r="AB14" s="42"/>
+      <x:c r="AC14" s="42"/>
+      <x:c r="AD14" s="42"/>
+      <x:c r="AE14" s="42"/>
+      <x:c r="AF14" s="42"/>
+      <x:c r="AG14" s="42"/>
+      <x:c r="AH14" s="42"/>
+      <x:c r="AI14" s="42"/>
+      <x:c r="AJ14" s="42"/>
+      <x:c r="AK14" s="83"/>
       <x:c r="AL14" s="1"/>
       <x:c r="AM14" s="6"/>
       <x:c r="AN14" s="16" t="s">
-        <x:v>112</x:v>
+        <x:v>120</x:v>
       </x:c>
-      <x:c r="AO14" s="38" t="s">
-        <x:v>110</x:v>
+      <x:c r="AO14" s="37" t="s">
+        <x:v>118</x:v>
       </x:c>
-      <x:c r="AP14" s="38"/>
-      <x:c r="AQ14" s="38" t="s">
-        <x:v>113</x:v>
+      <x:c r="AP14" s="37"/>
+      <x:c r="AQ14" s="37" t="s">
+        <x:v>115</x:v>
       </x:c>
-      <x:c r="AR14" s="38"/>
-      <x:c r="AS14" s="38"/>
-      <x:c r="AT14" s="38" t="s">
-        <x:v>106</x:v>
+      <x:c r="AR14" s="37"/>
+      <x:c r="AS14" s="37"/>
+      <x:c r="AT14" s="37" t="s">
+        <x:v>122</x:v>
       </x:c>
-      <x:c r="AU14" s="38"/>
-      <x:c r="AV14" s="38"/>
-      <x:c r="AW14" s="38"/>
-      <x:c r="AX14" s="38" t="s">
-        <x:v>107</x:v>
+      <x:c r="AU14" s="37"/>
+      <x:c r="AV14" s="37"/>
+      <x:c r="AW14" s="37"/>
+      <x:c r="AX14" s="37" t="s">
+        <x:v>123</x:v>
       </x:c>
-      <x:c r="AY14" s="38"/>
-      <x:c r="AZ14" s="38" t="s">
-        <x:v>111</x:v>
+      <x:c r="AY14" s="37"/>
+      <x:c r="AZ14" s="37" t="s">
+        <x:v>116</x:v>
       </x:c>
-      <x:c r="BA14" s="38"/>
+      <x:c r="BA14" s="37"/>
       <x:c r="BB14" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BC14" s="17" t="s">
-        <x:v>108</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="BD14" s="3"/>
       <x:c r="BE14" s="1"/>
@@ -3134,17 +3354,17 @@
       <x:c r="F15" s="6"/>
       <x:c r="G15" s="6"/>
       <x:c r="H15" s="6"/>
-      <x:c r="I15" s="46"/>
-      <x:c r="J15" s="43"/>
-      <x:c r="K15" s="43"/>
-      <x:c r="L15" s="43"/>
-      <x:c r="M15" s="43"/>
-      <x:c r="N15" s="43"/>
-      <x:c r="O15" s="43"/>
-      <x:c r="P15" s="43"/>
-      <x:c r="Q15" s="43"/>
-      <x:c r="R15" s="43"/>
-      <x:c r="S15" s="47"/>
+      <x:c r="I15" s="82"/>
+      <x:c r="J15" s="42"/>
+      <x:c r="K15" s="42"/>
+      <x:c r="L15" s="42"/>
+      <x:c r="M15" s="42"/>
+      <x:c r="N15" s="42"/>
+      <x:c r="O15" s="42"/>
+      <x:c r="P15" s="42"/>
+      <x:c r="Q15" s="42"/>
+      <x:c r="R15" s="42"/>
+      <x:c r="S15" s="83"/>
       <x:c r="T15" s="6"/>
       <x:c r="U15" s="6"/>
       <x:c r="V15" s="6"/>
@@ -3152,50 +3372,50 @@
       <x:c r="X15" s="6"/>
       <x:c r="Y15" s="6"/>
       <x:c r="Z15" s="6"/>
-      <x:c r="AA15" s="46"/>
-      <x:c r="AB15" s="43"/>
-      <x:c r="AC15" s="43"/>
-      <x:c r="AD15" s="43"/>
-      <x:c r="AE15" s="43"/>
-      <x:c r="AF15" s="43"/>
-      <x:c r="AG15" s="43"/>
-      <x:c r="AH15" s="43"/>
-      <x:c r="AI15" s="43"/>
-      <x:c r="AJ15" s="43"/>
-      <x:c r="AK15" s="47"/>
+      <x:c r="AA15" s="82"/>
+      <x:c r="AB15" s="42"/>
+      <x:c r="AC15" s="42"/>
+      <x:c r="AD15" s="42"/>
+      <x:c r="AE15" s="42"/>
+      <x:c r="AF15" s="42"/>
+      <x:c r="AG15" s="42"/>
+      <x:c r="AH15" s="42"/>
+      <x:c r="AI15" s="42"/>
+      <x:c r="AJ15" s="42"/>
+      <x:c r="AK15" s="83"/>
       <x:c r="AL15" s="1"/>
       <x:c r="AM15" s="6"/>
       <x:c r="AN15" s="16" t="s">
-        <x:v>114</x:v>
+        <x:v>129</x:v>
       </x:c>
-      <x:c r="AO15" s="38" t="s">
-        <x:v>118</x:v>
+      <x:c r="AO15" s="37" t="s">
+        <x:v>121</x:v>
       </x:c>
-      <x:c r="AP15" s="38"/>
-      <x:c r="AQ15" s="38" t="s">
+      <x:c r="AP15" s="37"/>
+      <x:c r="AQ15" s="37" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AR15" s="37"/>
+      <x:c r="AS15" s="37"/>
+      <x:c r="AT15" s="37" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="AU15" s="37"/>
+      <x:c r="AV15" s="37"/>
+      <x:c r="AW15" s="37"/>
+      <x:c r="AX15" s="37" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="AY15" s="37"/>
+      <x:c r="AZ15" s="37" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="AR15" s="38"/>
-      <x:c r="AS15" s="38"/>
-      <x:c r="AT15" s="38" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="AU15" s="38"/>
-      <x:c r="AV15" s="38"/>
-      <x:c r="AW15" s="38"/>
-      <x:c r="AX15" s="38" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="AY15" s="38"/>
-      <x:c r="AZ15" s="38" t="s">
+      <x:c r="BA15" s="37"/>
+      <x:c r="BB15" s="6" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="BA15" s="38"/>
-      <x:c r="BB15" s="6" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="BC15" s="17" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BD15" s="3"/>
       <x:c r="BE15" s="1"/>
@@ -3211,78 +3431,78 @@
     <x:row r="16" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A16" s="9"/>
       <x:c r="B16" s="10"/>
-      <x:c r="C16" s="43" t="s">
-        <x:v>126</x:v>
+      <x:c r="C16" s="79" t="s">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="D16" s="44"/>
-      <x:c r="E16" s="44"/>
-      <x:c r="F16" s="44"/>
-      <x:c r="G16" s="44"/>
-      <x:c r="H16" s="45"/>
-      <x:c r="I16" s="46"/>
-      <x:c r="J16" s="43"/>
-      <x:c r="K16" s="43"/>
-      <x:c r="L16" s="43"/>
-      <x:c r="M16" s="43"/>
-      <x:c r="N16" s="43"/>
-      <x:c r="O16" s="43"/>
-      <x:c r="P16" s="43"/>
-      <x:c r="Q16" s="43"/>
-      <x:c r="R16" s="43"/>
-      <x:c r="S16" s="47"/>
+      <x:c r="D16" s="80"/>
+      <x:c r="E16" s="80"/>
+      <x:c r="F16" s="80"/>
+      <x:c r="G16" s="80"/>
+      <x:c r="H16" s="81"/>
+      <x:c r="I16" s="82"/>
+      <x:c r="J16" s="42"/>
+      <x:c r="K16" s="42"/>
+      <x:c r="L16" s="42"/>
+      <x:c r="M16" s="42"/>
+      <x:c r="N16" s="42"/>
+      <x:c r="O16" s="42"/>
+      <x:c r="P16" s="42"/>
+      <x:c r="Q16" s="42"/>
+      <x:c r="R16" s="42"/>
+      <x:c r="S16" s="83"/>
       <x:c r="T16" s="6"/>
-      <x:c r="U16" s="43" t="s">
-        <x:v>122</x:v>
+      <x:c r="U16" s="79" t="s">
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="V16" s="44"/>
-      <x:c r="W16" s="44"/>
-      <x:c r="X16" s="44"/>
-      <x:c r="Y16" s="44"/>
-      <x:c r="Z16" s="45"/>
-      <x:c r="AA16" s="46"/>
-      <x:c r="AB16" s="43"/>
-      <x:c r="AC16" s="43"/>
-      <x:c r="AD16" s="43"/>
-      <x:c r="AE16" s="43"/>
-      <x:c r="AF16" s="43"/>
-      <x:c r="AG16" s="43"/>
-      <x:c r="AH16" s="43"/>
-      <x:c r="AI16" s="43"/>
-      <x:c r="AJ16" s="43"/>
-      <x:c r="AK16" s="47"/>
+      <x:c r="V16" s="80"/>
+      <x:c r="W16" s="80"/>
+      <x:c r="X16" s="80"/>
+      <x:c r="Y16" s="80"/>
+      <x:c r="Z16" s="81"/>
+      <x:c r="AA16" s="82"/>
+      <x:c r="AB16" s="42"/>
+      <x:c r="AC16" s="42"/>
+      <x:c r="AD16" s="42"/>
+      <x:c r="AE16" s="42"/>
+      <x:c r="AF16" s="42"/>
+      <x:c r="AG16" s="42"/>
+      <x:c r="AH16" s="42"/>
+      <x:c r="AI16" s="42"/>
+      <x:c r="AJ16" s="42"/>
+      <x:c r="AK16" s="83"/>
       <x:c r="AL16" s="6"/>
       <x:c r="AM16" s="6"/>
       <x:c r="AN16" s="16" t="s">
-        <x:v>125</x:v>
+        <x:v>139</x:v>
       </x:c>
-      <x:c r="AO16" s="55" t="s">
-        <x:v>121</x:v>
+      <x:c r="AO16" s="54" t="s">
+        <x:v>144</x:v>
       </x:c>
-      <x:c r="AP16" s="55"/>
-      <x:c r="AQ16" s="55" t="s">
-        <x:v>124</x:v>
+      <x:c r="AP16" s="54"/>
+      <x:c r="AQ16" s="54" t="s">
+        <x:v>146</x:v>
       </x:c>
-      <x:c r="AR16" s="55"/>
-      <x:c r="AS16" s="55"/>
-      <x:c r="AT16" s="55" t="s">
-        <x:v>128</x:v>
+      <x:c r="AR16" s="54"/>
+      <x:c r="AS16" s="54"/>
+      <x:c r="AT16" s="54" t="s">
+        <x:v>133</x:v>
       </x:c>
-      <x:c r="AU16" s="55"/>
-      <x:c r="AV16" s="55"/>
-      <x:c r="AW16" s="55"/>
-      <x:c r="AX16" s="55" t="s">
-        <x:v>127</x:v>
+      <x:c r="AU16" s="54"/>
+      <x:c r="AV16" s="54"/>
+      <x:c r="AW16" s="54"/>
+      <x:c r="AX16" s="54" t="s">
+        <x:v>134</x:v>
       </x:c>
-      <x:c r="AY16" s="55"/>
-      <x:c r="AZ16" s="55" t="s">
-        <x:v>135</x:v>
+      <x:c r="AY16" s="54"/>
+      <x:c r="AZ16" s="54" t="s">
+        <x:v>131</x:v>
       </x:c>
-      <x:c r="BA16" s="55"/>
+      <x:c r="BA16" s="54"/>
       <x:c r="BB16" s="18" t="s">
-        <x:v>130</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BC16" s="17" t="s">
-        <x:v>131</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="BD16" s="14"/>
       <x:c r="BE16" s="1"/>
@@ -3298,74 +3518,74 @@
     <x:row r="17" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="10"/>
-      <x:c r="C17" s="48"/>
-      <x:c r="D17" s="49"/>
-      <x:c r="E17" s="49"/>
-      <x:c r="F17" s="49"/>
-      <x:c r="G17" s="49"/>
-      <x:c r="H17" s="50"/>
-      <x:c r="I17" s="46"/>
-      <x:c r="J17" s="43"/>
-      <x:c r="K17" s="43"/>
-      <x:c r="L17" s="43"/>
-      <x:c r="M17" s="43"/>
-      <x:c r="N17" s="43"/>
-      <x:c r="O17" s="43"/>
-      <x:c r="P17" s="43"/>
-      <x:c r="Q17" s="43"/>
-      <x:c r="R17" s="43"/>
-      <x:c r="S17" s="47"/>
+      <x:c r="C17" s="84"/>
+      <x:c r="D17" s="85"/>
+      <x:c r="E17" s="85"/>
+      <x:c r="F17" s="85"/>
+      <x:c r="G17" s="85"/>
+      <x:c r="H17" s="86"/>
+      <x:c r="I17" s="82"/>
+      <x:c r="J17" s="42"/>
+      <x:c r="K17" s="42"/>
+      <x:c r="L17" s="42"/>
+      <x:c r="M17" s="42"/>
+      <x:c r="N17" s="42"/>
+      <x:c r="O17" s="42"/>
+      <x:c r="P17" s="42"/>
+      <x:c r="Q17" s="42"/>
+      <x:c r="R17" s="42"/>
+      <x:c r="S17" s="83"/>
       <x:c r="T17" s="6"/>
-      <x:c r="U17" s="48"/>
-      <x:c r="V17" s="49"/>
-      <x:c r="W17" s="49"/>
-      <x:c r="X17" s="49"/>
-      <x:c r="Y17" s="49"/>
-      <x:c r="Z17" s="50"/>
-      <x:c r="AA17" s="46"/>
-      <x:c r="AB17" s="43"/>
-      <x:c r="AC17" s="43"/>
-      <x:c r="AD17" s="43"/>
-      <x:c r="AE17" s="43"/>
-      <x:c r="AF17" s="43"/>
-      <x:c r="AG17" s="43"/>
-      <x:c r="AH17" s="43"/>
-      <x:c r="AI17" s="43"/>
-      <x:c r="AJ17" s="43"/>
-      <x:c r="AK17" s="47"/>
+      <x:c r="U17" s="84"/>
+      <x:c r="V17" s="85"/>
+      <x:c r="W17" s="85"/>
+      <x:c r="X17" s="85"/>
+      <x:c r="Y17" s="85"/>
+      <x:c r="Z17" s="86"/>
+      <x:c r="AA17" s="82"/>
+      <x:c r="AB17" s="42"/>
+      <x:c r="AC17" s="42"/>
+      <x:c r="AD17" s="42"/>
+      <x:c r="AE17" s="42"/>
+      <x:c r="AF17" s="42"/>
+      <x:c r="AG17" s="42"/>
+      <x:c r="AH17" s="42"/>
+      <x:c r="AI17" s="42"/>
+      <x:c r="AJ17" s="42"/>
+      <x:c r="AK17" s="83"/>
       <x:c r="AL17" s="1"/>
       <x:c r="AM17" s="6"/>
       <x:c r="AN17" s="19" t="s">
-        <x:v>134</x:v>
+        <x:v>142</x:v>
       </x:c>
-      <x:c r="AO17" s="53" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="AP17" s="54"/>
-      <x:c r="AQ17" s="53" t="s">
+      <x:c r="AO17" s="52" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="AR17" s="54"/>
-      <x:c r="AS17" s="54"/>
-      <x:c r="AT17" s="53" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="AU17" s="54"/>
-      <x:c r="AV17" s="54"/>
-      <x:c r="AW17" s="54"/>
-      <x:c r="AX17" s="53" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="AY17" s="54"/>
-      <x:c r="AZ17" s="53" t="s">
+      <x:c r="AP17" s="53"/>
+      <x:c r="AQ17" s="52" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="BA17" s="54"/>
+      <x:c r="AR17" s="53"/>
+      <x:c r="AS17" s="53"/>
+      <x:c r="AT17" s="52" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="AU17" s="53"/>
+      <x:c r="AV17" s="53"/>
+      <x:c r="AW17" s="53"/>
+      <x:c r="AX17" s="52" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="AY17" s="53"/>
+      <x:c r="AZ17" s="52" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="BA17" s="53"/>
       <x:c r="BB17" s="20" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="BC17" s="21" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="BD17" s="3"/>
       <x:c r="BE17" s="1"/>
@@ -3387,17 +3607,17 @@
       <x:c r="F18" s="6"/>
       <x:c r="G18" s="6"/>
       <x:c r="H18" s="6"/>
-      <x:c r="I18" s="46"/>
-      <x:c r="J18" s="43"/>
-      <x:c r="K18" s="43"/>
-      <x:c r="L18" s="43"/>
-      <x:c r="M18" s="43"/>
-      <x:c r="N18" s="43"/>
-      <x:c r="O18" s="43"/>
-      <x:c r="P18" s="43"/>
-      <x:c r="Q18" s="43"/>
-      <x:c r="R18" s="43"/>
-      <x:c r="S18" s="47"/>
+      <x:c r="I18" s="82"/>
+      <x:c r="J18" s="42"/>
+      <x:c r="K18" s="42"/>
+      <x:c r="L18" s="42"/>
+      <x:c r="M18" s="42"/>
+      <x:c r="N18" s="42"/>
+      <x:c r="O18" s="42"/>
+      <x:c r="P18" s="42"/>
+      <x:c r="Q18" s="42"/>
+      <x:c r="R18" s="42"/>
+      <x:c r="S18" s="83"/>
       <x:c r="T18" s="6"/>
       <x:c r="U18" s="6"/>
       <x:c r="V18" s="6"/>
@@ -3405,50 +3625,50 @@
       <x:c r="X18" s="6"/>
       <x:c r="Y18" s="6"/>
       <x:c r="Z18" s="6"/>
-      <x:c r="AA18" s="46"/>
-      <x:c r="AB18" s="43"/>
-      <x:c r="AC18" s="43"/>
-      <x:c r="AD18" s="43"/>
-      <x:c r="AE18" s="43"/>
-      <x:c r="AF18" s="43"/>
-      <x:c r="AG18" s="43"/>
-      <x:c r="AH18" s="43"/>
-      <x:c r="AI18" s="43"/>
-      <x:c r="AJ18" s="43"/>
-      <x:c r="AK18" s="47"/>
+      <x:c r="AA18" s="82"/>
+      <x:c r="AB18" s="42"/>
+      <x:c r="AC18" s="42"/>
+      <x:c r="AD18" s="42"/>
+      <x:c r="AE18" s="42"/>
+      <x:c r="AF18" s="42"/>
+      <x:c r="AG18" s="42"/>
+      <x:c r="AH18" s="42"/>
+      <x:c r="AI18" s="42"/>
+      <x:c r="AJ18" s="42"/>
+      <x:c r="AK18" s="83"/>
       <x:c r="AL18" s="1"/>
       <x:c r="AM18" s="6"/>
       <x:c r="AN18" s="18" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="AO18" s="54" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="AP18" s="54"/>
+      <x:c r="AQ18" s="54" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AR18" s="54"/>
+      <x:c r="AS18" s="54"/>
+      <x:c r="AT18" s="54" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="AU18" s="54"/>
+      <x:c r="AV18" s="54"/>
+      <x:c r="AW18" s="54"/>
+      <x:c r="AX18" s="54" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="AO18" s="55" t="s">
-        <x:v>136</x:v>
+      <x:c r="AY18" s="54"/>
+      <x:c r="AZ18" s="54" t="s">
+        <x:v>160</x:v>
       </x:c>
-      <x:c r="AP18" s="55"/>
-      <x:c r="AQ18" s="55" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="AR18" s="55"/>
-      <x:c r="AS18" s="55"/>
-      <x:c r="AT18" s="55" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="AU18" s="55"/>
-      <x:c r="AV18" s="55"/>
-      <x:c r="AW18" s="55"/>
-      <x:c r="AX18" s="55" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="AY18" s="55"/>
-      <x:c r="AZ18" s="55" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="BA18" s="55"/>
+      <x:c r="BA18" s="54"/>
       <x:c r="BB18" s="18" t="s">
-        <x:v>146</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="BC18" s="17" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="BD18" s="3"/>
       <x:c r="BE18" s="1"/>
@@ -3470,17 +3690,17 @@
       <x:c r="F19" s="6"/>
       <x:c r="G19" s="6"/>
       <x:c r="H19" s="6"/>
-      <x:c r="I19" s="46"/>
-      <x:c r="J19" s="43"/>
-      <x:c r="K19" s="43"/>
-      <x:c r="L19" s="43"/>
-      <x:c r="M19" s="43"/>
-      <x:c r="N19" s="43"/>
-      <x:c r="O19" s="43"/>
-      <x:c r="P19" s="43"/>
-      <x:c r="Q19" s="43"/>
-      <x:c r="R19" s="43"/>
-      <x:c r="S19" s="47"/>
+      <x:c r="I19" s="82"/>
+      <x:c r="J19" s="42"/>
+      <x:c r="K19" s="42"/>
+      <x:c r="L19" s="42"/>
+      <x:c r="M19" s="42"/>
+      <x:c r="N19" s="42"/>
+      <x:c r="O19" s="42"/>
+      <x:c r="P19" s="42"/>
+      <x:c r="Q19" s="42"/>
+      <x:c r="R19" s="42"/>
+      <x:c r="S19" s="83"/>
       <x:c r="T19" s="6"/>
       <x:c r="U19" s="6"/>
       <x:c r="V19" s="6"/>
@@ -3488,37 +3708,37 @@
       <x:c r="X19" s="6"/>
       <x:c r="Y19" s="6"/>
       <x:c r="Z19" s="6"/>
-      <x:c r="AA19" s="46"/>
-      <x:c r="AB19" s="43"/>
-      <x:c r="AC19" s="43"/>
-      <x:c r="AD19" s="43"/>
-      <x:c r="AE19" s="43"/>
-      <x:c r="AF19" s="43"/>
-      <x:c r="AG19" s="43"/>
-      <x:c r="AH19" s="43"/>
-      <x:c r="AI19" s="43"/>
-      <x:c r="AJ19" s="43"/>
-      <x:c r="AK19" s="47"/>
+      <x:c r="AA19" s="82"/>
+      <x:c r="AB19" s="42"/>
+      <x:c r="AC19" s="42"/>
+      <x:c r="AD19" s="42"/>
+      <x:c r="AE19" s="42"/>
+      <x:c r="AF19" s="42"/>
+      <x:c r="AG19" s="42"/>
+      <x:c r="AH19" s="42"/>
+      <x:c r="AI19" s="42"/>
+      <x:c r="AJ19" s="42"/>
+      <x:c r="AK19" s="83"/>
       <x:c r="AL19" s="1"/>
       <x:c r="AM19" s="6"/>
-      <x:c r="AN19" s="43" t="s">
-        <x:v>5</x:v>
+      <x:c r="AN19" s="42" t="s">
+        <x:v>26</x:v>
       </x:c>
-      <x:c r="AO19" s="44"/>
-      <x:c r="AP19" s="44"/>
-      <x:c r="AQ19" s="44"/>
-      <x:c r="AR19" s="44"/>
-      <x:c r="AS19" s="44"/>
-      <x:c r="AT19" s="44"/>
-      <x:c r="AU19" s="44"/>
-      <x:c r="AV19" s="44"/>
-      <x:c r="AW19" s="44"/>
-      <x:c r="AX19" s="44"/>
-      <x:c r="AY19" s="44"/>
-      <x:c r="AZ19" s="44"/>
-      <x:c r="BA19" s="44"/>
-      <x:c r="BB19" s="44"/>
-      <x:c r="BC19" s="45"/>
+      <x:c r="AO19" s="43"/>
+      <x:c r="AP19" s="43"/>
+      <x:c r="AQ19" s="43"/>
+      <x:c r="AR19" s="43"/>
+      <x:c r="AS19" s="43"/>
+      <x:c r="AT19" s="43"/>
+      <x:c r="AU19" s="43"/>
+      <x:c r="AV19" s="43"/>
+      <x:c r="AW19" s="43"/>
+      <x:c r="AX19" s="43"/>
+      <x:c r="AY19" s="43"/>
+      <x:c r="AZ19" s="43"/>
+      <x:c r="BA19" s="43"/>
+      <x:c r="BB19" s="43"/>
+      <x:c r="BC19" s="44"/>
       <x:c r="BD19" s="14"/>
       <x:c r="BE19" s="1"/>
       <x:c r="BF19" s="1"/>
@@ -3529,53 +3749,55 @@
       <x:c r="BK19" s="1"/>
       <x:c r="BL19" s="1"/>
       <x:c r="BM19" s="18" t="s">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="10"/>
-      <x:c r="I20" s="48"/>
-      <x:c r="J20" s="49"/>
-      <x:c r="K20" s="49"/>
-      <x:c r="L20" s="49"/>
-      <x:c r="M20" s="49"/>
-      <x:c r="N20" s="49"/>
-      <x:c r="O20" s="49"/>
-      <x:c r="P20" s="49"/>
-      <x:c r="Q20" s="49"/>
-      <x:c r="R20" s="49"/>
-      <x:c r="S20" s="50"/>
+      <x:c r="H20" s="1"/>
+      <x:c r="I20" s="84"/>
+      <x:c r="J20" s="85"/>
+      <x:c r="K20" s="85"/>
+      <x:c r="L20" s="85"/>
+      <x:c r="M20" s="85"/>
+      <x:c r="N20" s="85"/>
+      <x:c r="O20" s="85"/>
+      <x:c r="P20" s="85"/>
+      <x:c r="Q20" s="85"/>
+      <x:c r="R20" s="85"/>
+      <x:c r="S20" s="86"/>
+      <x:c r="T20" s="1"/>
       <x:c r="Z20" s="6"/>
-      <x:c r="AA20" s="48"/>
-      <x:c r="AB20" s="49"/>
-      <x:c r="AC20" s="49"/>
-      <x:c r="AD20" s="49"/>
-      <x:c r="AE20" s="49"/>
-      <x:c r="AF20" s="49"/>
-      <x:c r="AG20" s="49"/>
-      <x:c r="AH20" s="49"/>
-      <x:c r="AI20" s="49"/>
-      <x:c r="AJ20" s="49"/>
-      <x:c r="AK20" s="50"/>
+      <x:c r="AA20" s="84"/>
+      <x:c r="AB20" s="85"/>
+      <x:c r="AC20" s="85"/>
+      <x:c r="AD20" s="85"/>
+      <x:c r="AE20" s="85"/>
+      <x:c r="AF20" s="85"/>
+      <x:c r="AG20" s="85"/>
+      <x:c r="AH20" s="85"/>
+      <x:c r="AI20" s="85"/>
+      <x:c r="AJ20" s="85"/>
+      <x:c r="AK20" s="86"/>
       <x:c r="AL20" s="1"/>
       <x:c r="AM20" s="6"/>
-      <x:c r="AN20" s="46"/>
-      <x:c r="AO20" s="43"/>
-      <x:c r="AP20" s="43"/>
-      <x:c r="AQ20" s="43"/>
-      <x:c r="AR20" s="43"/>
-      <x:c r="AS20" s="43"/>
-      <x:c r="AT20" s="43"/>
-      <x:c r="AU20" s="43"/>
-      <x:c r="AV20" s="43"/>
-      <x:c r="AW20" s="43"/>
-      <x:c r="AX20" s="43"/>
-      <x:c r="AY20" s="43"/>
-      <x:c r="AZ20" s="43"/>
-      <x:c r="BA20" s="43"/>
-      <x:c r="BB20" s="43"/>
-      <x:c r="BC20" s="47"/>
+      <x:c r="AN20" s="45"/>
+      <x:c r="AO20" s="42"/>
+      <x:c r="AP20" s="42"/>
+      <x:c r="AQ20" s="42"/>
+      <x:c r="AR20" s="42"/>
+      <x:c r="AS20" s="42"/>
+      <x:c r="AT20" s="42"/>
+      <x:c r="AU20" s="42"/>
+      <x:c r="AV20" s="42"/>
+      <x:c r="AW20" s="42"/>
+      <x:c r="AX20" s="42"/>
+      <x:c r="AY20" s="42"/>
+      <x:c r="AZ20" s="42"/>
+      <x:c r="BA20" s="42"/>
+      <x:c r="BB20" s="42"/>
+      <x:c r="BC20" s="46"/>
       <x:c r="BD20" s="3"/>
       <x:c r="BE20" s="1"/>
       <x:c r="BF20" s="1"/>
@@ -3590,6 +3812,7 @@
     <x:row r="21" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="10"/>
+      <x:c r="H21" s="1"/>
       <x:c r="I21" s="6"/>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="6"/>
@@ -3601,6 +3824,8 @@
       <x:c r="Q21" s="6"/>
       <x:c r="R21" s="6"/>
       <x:c r="S21" s="6"/>
+      <x:c r="T21" s="1"/>
+      <x:c r="Z21" s="1"/>
       <x:c r="AA21" s="6"/>
       <x:c r="AB21" s="6"/>
       <x:c r="AC21" s="6"/>
@@ -3614,22 +3839,22 @@
       <x:c r="AK21" s="6"/>
       <x:c r="AL21" s="1"/>
       <x:c r="AM21" s="6"/>
-      <x:c r="AN21" s="48"/>
-      <x:c r="AO21" s="49"/>
-      <x:c r="AP21" s="49"/>
-      <x:c r="AQ21" s="49"/>
-      <x:c r="AR21" s="49"/>
-      <x:c r="AS21" s="49"/>
-      <x:c r="AT21" s="49"/>
-      <x:c r="AU21" s="49"/>
-      <x:c r="AV21" s="49"/>
-      <x:c r="AW21" s="49"/>
-      <x:c r="AX21" s="49"/>
-      <x:c r="AY21" s="49"/>
-      <x:c r="AZ21" s="49"/>
-      <x:c r="BA21" s="49"/>
-      <x:c r="BB21" s="49"/>
-      <x:c r="BC21" s="50"/>
+      <x:c r="AN21" s="47"/>
+      <x:c r="AO21" s="48"/>
+      <x:c r="AP21" s="48"/>
+      <x:c r="AQ21" s="48"/>
+      <x:c r="AR21" s="48"/>
+      <x:c r="AS21" s="48"/>
+      <x:c r="AT21" s="48"/>
+      <x:c r="AU21" s="48"/>
+      <x:c r="AV21" s="48"/>
+      <x:c r="AW21" s="48"/>
+      <x:c r="AX21" s="48"/>
+      <x:c r="AY21" s="48"/>
+      <x:c r="AZ21" s="48"/>
+      <x:c r="BA21" s="48"/>
+      <x:c r="BB21" s="48"/>
+      <x:c r="BC21" s="49"/>
       <x:c r="BD21" s="3"/>
       <x:c r="BE21" s="1"/>
       <x:c r="BF21" s="1"/>
@@ -3644,33 +3869,35 @@
     <x:row r="22" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="10"/>
-      <x:c r="I22" s="43" t="s">
-        <x:v>148</x:v>
+      <x:c r="H22" s="1"/>
+      <x:c r="I22" s="79" t="s">
+        <x:v>0</x:v>
       </x:c>
-      <x:c r="J22" s="44"/>
-      <x:c r="K22" s="44"/>
-      <x:c r="L22" s="44"/>
-      <x:c r="M22" s="44"/>
-      <x:c r="N22" s="44"/>
-      <x:c r="O22" s="44"/>
-      <x:c r="P22" s="44"/>
-      <x:c r="Q22" s="44"/>
-      <x:c r="R22" s="44"/>
-      <x:c r="S22" s="45"/>
+      <x:c r="J22" s="80"/>
+      <x:c r="K22" s="80"/>
+      <x:c r="L22" s="80"/>
+      <x:c r="M22" s="80"/>
+      <x:c r="N22" s="80"/>
+      <x:c r="O22" s="80"/>
+      <x:c r="P22" s="80"/>
+      <x:c r="Q22" s="80"/>
+      <x:c r="R22" s="80"/>
+      <x:c r="S22" s="81"/>
+      <x:c r="T22" s="1"/>
       <x:c r="Z22" s="6"/>
-      <x:c r="AA22" s="43" t="s">
-        <x:v>149</x:v>
+      <x:c r="AA22" s="79" t="s">
+        <x:v>6</x:v>
       </x:c>
-      <x:c r="AB22" s="44"/>
-      <x:c r="AC22" s="44"/>
-      <x:c r="AD22" s="44"/>
-      <x:c r="AE22" s="44"/>
-      <x:c r="AF22" s="44"/>
-      <x:c r="AG22" s="44"/>
-      <x:c r="AH22" s="44"/>
-      <x:c r="AI22" s="44"/>
-      <x:c r="AJ22" s="44"/>
-      <x:c r="AK22" s="45"/>
+      <x:c r="AB22" s="80"/>
+      <x:c r="AC22" s="80"/>
+      <x:c r="AD22" s="80"/>
+      <x:c r="AE22" s="80"/>
+      <x:c r="AF22" s="80"/>
+      <x:c r="AG22" s="80"/>
+      <x:c r="AH22" s="80"/>
+      <x:c r="AI22" s="80"/>
+      <x:c r="AJ22" s="80"/>
+      <x:c r="AK22" s="81"/>
       <x:c r="AL22" s="1"/>
       <x:c r="AM22" s="6"/>
       <x:c r="AN22" s="6"/>
@@ -3709,17 +3936,17 @@
       <x:c r="F23" s="6"/>
       <x:c r="G23" s="6"/>
       <x:c r="H23" s="1"/>
-      <x:c r="I23" s="46"/>
-      <x:c r="J23" s="43"/>
-      <x:c r="K23" s="43"/>
-      <x:c r="L23" s="43"/>
-      <x:c r="M23" s="43"/>
-      <x:c r="N23" s="43"/>
-      <x:c r="O23" s="43"/>
-      <x:c r="P23" s="43"/>
-      <x:c r="Q23" s="43"/>
-      <x:c r="R23" s="43"/>
-      <x:c r="S23" s="47"/>
+      <x:c r="I23" s="82"/>
+      <x:c r="J23" s="42"/>
+      <x:c r="K23" s="42"/>
+      <x:c r="L23" s="42"/>
+      <x:c r="M23" s="42"/>
+      <x:c r="N23" s="42"/>
+      <x:c r="O23" s="42"/>
+      <x:c r="P23" s="42"/>
+      <x:c r="Q23" s="42"/>
+      <x:c r="R23" s="42"/>
+      <x:c r="S23" s="83"/>
       <x:c r="T23" s="6"/>
       <x:c r="U23" s="6"/>
       <x:c r="V23" s="6"/>
@@ -3727,35 +3954,35 @@
       <x:c r="X23" s="6"/>
       <x:c r="Y23" s="6"/>
       <x:c r="Z23" s="6"/>
-      <x:c r="AA23" s="46"/>
-      <x:c r="AB23" s="43"/>
-      <x:c r="AC23" s="43"/>
-      <x:c r="AD23" s="43"/>
-      <x:c r="AE23" s="43"/>
-      <x:c r="AF23" s="43"/>
-      <x:c r="AG23" s="43"/>
-      <x:c r="AH23" s="43"/>
-      <x:c r="AI23" s="43"/>
-      <x:c r="AJ23" s="43"/>
-      <x:c r="AK23" s="47"/>
+      <x:c r="AA23" s="82"/>
+      <x:c r="AB23" s="42"/>
+      <x:c r="AC23" s="42"/>
+      <x:c r="AD23" s="42"/>
+      <x:c r="AE23" s="42"/>
+      <x:c r="AF23" s="42"/>
+      <x:c r="AG23" s="42"/>
+      <x:c r="AH23" s="42"/>
+      <x:c r="AI23" s="42"/>
+      <x:c r="AJ23" s="42"/>
+      <x:c r="AK23" s="83"/>
       <x:c r="AL23" s="6"/>
       <x:c r="AM23" s="6"/>
       <x:c r="AN23" s="23"/>
-      <x:c r="AO23" s="39"/>
-      <x:c r="AP23" s="40"/>
-      <x:c r="AQ23" s="39"/>
-      <x:c r="AR23" s="42"/>
-      <x:c r="AS23" s="42"/>
-      <x:c r="AT23" s="40"/>
-      <x:c r="AU23" s="39"/>
-      <x:c r="AV23" s="40"/>
-      <x:c r="AW23" s="39"/>
-      <x:c r="AX23" s="42"/>
-      <x:c r="AY23" s="40"/>
-      <x:c r="AZ23" s="65"/>
-      <x:c r="BA23" s="42"/>
-      <x:c r="BB23" s="42"/>
-      <x:c r="BC23" s="66"/>
+      <x:c r="AO23" s="38"/>
+      <x:c r="AP23" s="39"/>
+      <x:c r="AQ23" s="38"/>
+      <x:c r="AR23" s="41"/>
+      <x:c r="AS23" s="41"/>
+      <x:c r="AT23" s="39"/>
+      <x:c r="AU23" s="38"/>
+      <x:c r="AV23" s="39"/>
+      <x:c r="AW23" s="38"/>
+      <x:c r="AX23" s="41"/>
+      <x:c r="AY23" s="39"/>
+      <x:c r="AZ23" s="64"/>
+      <x:c r="BA23" s="41"/>
+      <x:c r="BB23" s="41"/>
+      <x:c r="BC23" s="65"/>
       <x:c r="BD23" s="3"/>
       <x:c r="BE23" s="1"/>
       <x:c r="BF23" s="1"/>
@@ -3776,17 +4003,17 @@
       <x:c r="F24" s="6"/>
       <x:c r="G24" s="6"/>
       <x:c r="H24" s="1"/>
-      <x:c r="I24" s="46"/>
-      <x:c r="J24" s="43"/>
-      <x:c r="K24" s="43"/>
-      <x:c r="L24" s="43"/>
-      <x:c r="M24" s="43"/>
-      <x:c r="N24" s="43"/>
-      <x:c r="O24" s="43"/>
-      <x:c r="P24" s="43"/>
-      <x:c r="Q24" s="43"/>
-      <x:c r="R24" s="43"/>
-      <x:c r="S24" s="47"/>
+      <x:c r="I24" s="82"/>
+      <x:c r="J24" s="42"/>
+      <x:c r="K24" s="42"/>
+      <x:c r="L24" s="42"/>
+      <x:c r="M24" s="42"/>
+      <x:c r="N24" s="42"/>
+      <x:c r="O24" s="42"/>
+      <x:c r="P24" s="42"/>
+      <x:c r="Q24" s="42"/>
+      <x:c r="R24" s="42"/>
+      <x:c r="S24" s="83"/>
       <x:c r="T24" s="6"/>
       <x:c r="U24" s="6"/>
       <x:c r="V24" s="6"/>
@@ -3794,35 +4021,35 @@
       <x:c r="X24" s="6"/>
       <x:c r="Y24" s="6"/>
       <x:c r="Z24" s="6"/>
-      <x:c r="AA24" s="46"/>
-      <x:c r="AB24" s="43"/>
-      <x:c r="AC24" s="43"/>
-      <x:c r="AD24" s="43"/>
-      <x:c r="AE24" s="43"/>
-      <x:c r="AF24" s="43"/>
-      <x:c r="AG24" s="43"/>
-      <x:c r="AH24" s="43"/>
-      <x:c r="AI24" s="43"/>
-      <x:c r="AJ24" s="43"/>
-      <x:c r="AK24" s="47"/>
+      <x:c r="AA24" s="82"/>
+      <x:c r="AB24" s="42"/>
+      <x:c r="AC24" s="42"/>
+      <x:c r="AD24" s="42"/>
+      <x:c r="AE24" s="42"/>
+      <x:c r="AF24" s="42"/>
+      <x:c r="AG24" s="42"/>
+      <x:c r="AH24" s="42"/>
+      <x:c r="AI24" s="42"/>
+      <x:c r="AJ24" s="42"/>
+      <x:c r="AK24" s="83"/>
       <x:c r="AL24" s="1"/>
       <x:c r="AM24" s="6"/>
       <x:c r="AN24" s="23"/>
-      <x:c r="AO24" s="39"/>
-      <x:c r="AP24" s="40"/>
-      <x:c r="AQ24" s="39"/>
-      <x:c r="AR24" s="42"/>
-      <x:c r="AS24" s="42"/>
-      <x:c r="AT24" s="40"/>
-      <x:c r="AU24" s="39"/>
-      <x:c r="AV24" s="40"/>
-      <x:c r="AW24" s="39"/>
-      <x:c r="AX24" s="42"/>
-      <x:c r="AY24" s="40"/>
-      <x:c r="AZ24" s="65"/>
-      <x:c r="BA24" s="42"/>
-      <x:c r="BB24" s="42"/>
-      <x:c r="BC24" s="66"/>
+      <x:c r="AO24" s="38"/>
+      <x:c r="AP24" s="39"/>
+      <x:c r="AQ24" s="38"/>
+      <x:c r="AR24" s="41"/>
+      <x:c r="AS24" s="41"/>
+      <x:c r="AT24" s="39"/>
+      <x:c r="AU24" s="38"/>
+      <x:c r="AV24" s="39"/>
+      <x:c r="AW24" s="38"/>
+      <x:c r="AX24" s="41"/>
+      <x:c r="AY24" s="39"/>
+      <x:c r="AZ24" s="64"/>
+      <x:c r="BA24" s="41"/>
+      <x:c r="BB24" s="41"/>
+      <x:c r="BC24" s="65"/>
       <x:c r="BD24" s="3"/>
       <x:c r="BE24" s="1"/>
       <x:c r="BF24" s="1"/>
@@ -3837,63 +4064,63 @@
     <x:row r="25" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="10"/>
-      <x:c r="C25" s="43" t="s">
-        <x:v>150</x:v>
+      <x:c r="C25" s="79" t="s">
+        <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="44"/>
-      <x:c r="E25" s="44"/>
-      <x:c r="F25" s="44"/>
-      <x:c r="G25" s="44"/>
-      <x:c r="H25" s="45"/>
-      <x:c r="I25" s="46"/>
-      <x:c r="J25" s="43"/>
-      <x:c r="K25" s="43"/>
-      <x:c r="L25" s="43"/>
-      <x:c r="M25" s="43"/>
-      <x:c r="N25" s="43"/>
-      <x:c r="O25" s="43"/>
-      <x:c r="P25" s="43"/>
-      <x:c r="Q25" s="43"/>
-      <x:c r="R25" s="43"/>
-      <x:c r="S25" s="47"/>
+      <x:c r="D25" s="80"/>
+      <x:c r="E25" s="80"/>
+      <x:c r="F25" s="80"/>
+      <x:c r="G25" s="80"/>
+      <x:c r="H25" s="81"/>
+      <x:c r="I25" s="82"/>
+      <x:c r="J25" s="42"/>
+      <x:c r="K25" s="42"/>
+      <x:c r="L25" s="42"/>
+      <x:c r="M25" s="42"/>
+      <x:c r="N25" s="42"/>
+      <x:c r="O25" s="42"/>
+      <x:c r="P25" s="42"/>
+      <x:c r="Q25" s="42"/>
+      <x:c r="R25" s="42"/>
+      <x:c r="S25" s="83"/>
       <x:c r="T25" s="6"/>
-      <x:c r="U25" s="43" t="s">
-        <x:v>151</x:v>
+      <x:c r="U25" s="79" t="s">
+        <x:v>4</x:v>
       </x:c>
-      <x:c r="V25" s="44"/>
-      <x:c r="W25" s="44"/>
-      <x:c r="X25" s="44"/>
-      <x:c r="Y25" s="44"/>
-      <x:c r="Z25" s="45"/>
-      <x:c r="AA25" s="46"/>
-      <x:c r="AB25" s="43"/>
-      <x:c r="AC25" s="43"/>
-      <x:c r="AD25" s="43"/>
-      <x:c r="AE25" s="43"/>
-      <x:c r="AF25" s="43"/>
-      <x:c r="AG25" s="43"/>
-      <x:c r="AH25" s="43"/>
-      <x:c r="AI25" s="43"/>
-      <x:c r="AJ25" s="43"/>
-      <x:c r="AK25" s="47"/>
+      <x:c r="V25" s="80"/>
+      <x:c r="W25" s="80"/>
+      <x:c r="X25" s="80"/>
+      <x:c r="Y25" s="80"/>
+      <x:c r="Z25" s="81"/>
+      <x:c r="AA25" s="82"/>
+      <x:c r="AB25" s="42"/>
+      <x:c r="AC25" s="42"/>
+      <x:c r="AD25" s="42"/>
+      <x:c r="AE25" s="42"/>
+      <x:c r="AF25" s="42"/>
+      <x:c r="AG25" s="42"/>
+      <x:c r="AH25" s="42"/>
+      <x:c r="AI25" s="42"/>
+      <x:c r="AJ25" s="42"/>
+      <x:c r="AK25" s="83"/>
       <x:c r="AL25" s="1"/>
       <x:c r="AM25" s="6"/>
       <x:c r="AN25" s="23"/>
-      <x:c r="AO25" s="39"/>
-      <x:c r="AP25" s="40"/>
-      <x:c r="AQ25" s="39"/>
-      <x:c r="AR25" s="42"/>
-      <x:c r="AS25" s="42"/>
-      <x:c r="AT25" s="40"/>
-      <x:c r="AU25" s="39"/>
-      <x:c r="AV25" s="40"/>
-      <x:c r="AW25" s="39"/>
-      <x:c r="AX25" s="42"/>
-      <x:c r="AY25" s="40"/>
-      <x:c r="AZ25" s="65"/>
-      <x:c r="BA25" s="42"/>
-      <x:c r="BB25" s="42"/>
-      <x:c r="BC25" s="66"/>
+      <x:c r="AO25" s="38"/>
+      <x:c r="AP25" s="39"/>
+      <x:c r="AQ25" s="38"/>
+      <x:c r="AR25" s="41"/>
+      <x:c r="AS25" s="41"/>
+      <x:c r="AT25" s="39"/>
+      <x:c r="AU25" s="38"/>
+      <x:c r="AV25" s="39"/>
+      <x:c r="AW25" s="38"/>
+      <x:c r="AX25" s="41"/>
+      <x:c r="AY25" s="39"/>
+      <x:c r="AZ25" s="64"/>
+      <x:c r="BA25" s="41"/>
+      <x:c r="BB25" s="41"/>
+      <x:c r="BC25" s="65"/>
       <x:c r="BD25" s="14"/>
       <x:c r="BE25" s="1"/>
       <x:c r="BF25" s="1"/>
@@ -3908,59 +4135,59 @@
     <x:row r="26" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="10"/>
-      <x:c r="C26" s="48"/>
-      <x:c r="D26" s="49"/>
-      <x:c r="E26" s="49"/>
-      <x:c r="F26" s="49"/>
-      <x:c r="G26" s="49"/>
-      <x:c r="H26" s="50"/>
-      <x:c r="I26" s="46"/>
-      <x:c r="J26" s="43"/>
-      <x:c r="K26" s="43"/>
-      <x:c r="L26" s="43"/>
-      <x:c r="M26" s="43"/>
-      <x:c r="N26" s="43"/>
-      <x:c r="O26" s="43"/>
-      <x:c r="P26" s="43"/>
-      <x:c r="Q26" s="43"/>
-      <x:c r="R26" s="43"/>
-      <x:c r="S26" s="47"/>
+      <x:c r="C26" s="84"/>
+      <x:c r="D26" s="85"/>
+      <x:c r="E26" s="85"/>
+      <x:c r="F26" s="85"/>
+      <x:c r="G26" s="85"/>
+      <x:c r="H26" s="86"/>
+      <x:c r="I26" s="82"/>
+      <x:c r="J26" s="42"/>
+      <x:c r="K26" s="42"/>
+      <x:c r="L26" s="42"/>
+      <x:c r="M26" s="42"/>
+      <x:c r="N26" s="42"/>
+      <x:c r="O26" s="42"/>
+      <x:c r="P26" s="42"/>
+      <x:c r="Q26" s="42"/>
+      <x:c r="R26" s="42"/>
+      <x:c r="S26" s="83"/>
       <x:c r="T26" s="25"/>
-      <x:c r="U26" s="48"/>
-      <x:c r="V26" s="49"/>
-      <x:c r="W26" s="49"/>
-      <x:c r="X26" s="49"/>
-      <x:c r="Y26" s="49"/>
-      <x:c r="Z26" s="50"/>
-      <x:c r="AA26" s="46"/>
-      <x:c r="AB26" s="43"/>
-      <x:c r="AC26" s="43"/>
-      <x:c r="AD26" s="43"/>
-      <x:c r="AE26" s="43"/>
-      <x:c r="AF26" s="43"/>
-      <x:c r="AG26" s="43"/>
-      <x:c r="AH26" s="43"/>
-      <x:c r="AI26" s="43"/>
-      <x:c r="AJ26" s="43"/>
-      <x:c r="AK26" s="47"/>
+      <x:c r="U26" s="84"/>
+      <x:c r="V26" s="85"/>
+      <x:c r="W26" s="85"/>
+      <x:c r="X26" s="85"/>
+      <x:c r="Y26" s="85"/>
+      <x:c r="Z26" s="86"/>
+      <x:c r="AA26" s="82"/>
+      <x:c r="AB26" s="42"/>
+      <x:c r="AC26" s="42"/>
+      <x:c r="AD26" s="42"/>
+      <x:c r="AE26" s="42"/>
+      <x:c r="AF26" s="42"/>
+      <x:c r="AG26" s="42"/>
+      <x:c r="AH26" s="42"/>
+      <x:c r="AI26" s="42"/>
+      <x:c r="AJ26" s="42"/>
+      <x:c r="AK26" s="83"/>
       <x:c r="AL26" s="1"/>
       <x:c r="AM26" s="6"/>
       <x:c r="AN26" s="23"/>
-      <x:c r="AO26" s="39"/>
-      <x:c r="AP26" s="40"/>
-      <x:c r="AQ26" s="39"/>
-      <x:c r="AR26" s="42"/>
-      <x:c r="AS26" s="42"/>
-      <x:c r="AT26" s="40"/>
-      <x:c r="AU26" s="39"/>
-      <x:c r="AV26" s="40"/>
-      <x:c r="AW26" s="39"/>
-      <x:c r="AX26" s="42"/>
-      <x:c r="AY26" s="40"/>
-      <x:c r="AZ26" s="65"/>
-      <x:c r="BA26" s="42"/>
-      <x:c r="BB26" s="42"/>
-      <x:c r="BC26" s="66"/>
+      <x:c r="AO26" s="38"/>
+      <x:c r="AP26" s="39"/>
+      <x:c r="AQ26" s="38"/>
+      <x:c r="AR26" s="41"/>
+      <x:c r="AS26" s="41"/>
+      <x:c r="AT26" s="39"/>
+      <x:c r="AU26" s="38"/>
+      <x:c r="AV26" s="39"/>
+      <x:c r="AW26" s="38"/>
+      <x:c r="AX26" s="41"/>
+      <x:c r="AY26" s="39"/>
+      <x:c r="AZ26" s="64"/>
+      <x:c r="BA26" s="41"/>
+      <x:c r="BB26" s="41"/>
+      <x:c r="BC26" s="65"/>
       <x:c r="BD26" s="3"/>
       <x:c r="BE26" s="1"/>
       <x:c r="BF26" s="1"/>
@@ -3981,17 +4208,17 @@
       <x:c r="F27" s="6"/>
       <x:c r="G27" s="6"/>
       <x:c r="H27" s="1"/>
-      <x:c r="I27" s="46"/>
-      <x:c r="J27" s="43"/>
-      <x:c r="K27" s="43"/>
-      <x:c r="L27" s="43"/>
-      <x:c r="M27" s="43"/>
-      <x:c r="N27" s="43"/>
-      <x:c r="O27" s="43"/>
-      <x:c r="P27" s="43"/>
-      <x:c r="Q27" s="43"/>
-      <x:c r="R27" s="43"/>
-      <x:c r="S27" s="47"/>
+      <x:c r="I27" s="82"/>
+      <x:c r="J27" s="42"/>
+      <x:c r="K27" s="42"/>
+      <x:c r="L27" s="42"/>
+      <x:c r="M27" s="42"/>
+      <x:c r="N27" s="42"/>
+      <x:c r="O27" s="42"/>
+      <x:c r="P27" s="42"/>
+      <x:c r="Q27" s="42"/>
+      <x:c r="R27" s="42"/>
+      <x:c r="S27" s="83"/>
       <x:c r="T27" s="1"/>
       <x:c r="U27" s="6"/>
       <x:c r="V27" s="6"/>
@@ -3999,47 +4226,47 @@
       <x:c r="X27" s="6"/>
       <x:c r="Y27" s="6"/>
       <x:c r="Z27" s="6"/>
-      <x:c r="AA27" s="46"/>
-      <x:c r="AB27" s="43"/>
-      <x:c r="AC27" s="43"/>
-      <x:c r="AD27" s="43"/>
-      <x:c r="AE27" s="43"/>
-      <x:c r="AF27" s="43"/>
-      <x:c r="AG27" s="43"/>
-      <x:c r="AH27" s="43"/>
-      <x:c r="AI27" s="43"/>
-      <x:c r="AJ27" s="43"/>
-      <x:c r="AK27" s="47"/>
+      <x:c r="AA27" s="82"/>
+      <x:c r="AB27" s="42"/>
+      <x:c r="AC27" s="42"/>
+      <x:c r="AD27" s="42"/>
+      <x:c r="AE27" s="42"/>
+      <x:c r="AF27" s="42"/>
+      <x:c r="AG27" s="42"/>
+      <x:c r="AH27" s="42"/>
+      <x:c r="AI27" s="42"/>
+      <x:c r="AJ27" s="42"/>
+      <x:c r="AK27" s="83"/>
       <x:c r="AL27" s="1"/>
       <x:c r="AM27" s="6"/>
       <x:c r="AN27" s="23" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AO27" s="24" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="AP27" s="26"/>
       <x:c r="AQ27" s="24" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AR27" s="27"/>
       <x:c r="AS27" s="27"/>
       <x:c r="AT27" s="26"/>
       <x:c r="AU27" s="28" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AV27" s="29"/>
       <x:c r="AW27" s="24" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AX27" s="27"/>
       <x:c r="AY27" s="26"/>
-      <x:c r="AZ27" s="65" t="s">
-        <x:v>153</x:v>
+      <x:c r="AZ27" s="64" t="s">
+        <x:v>161</x:v>
       </x:c>
-      <x:c r="BA27" s="42"/>
-      <x:c r="BB27" s="42"/>
-      <x:c r="BC27" s="66"/>
+      <x:c r="BA27" s="41"/>
+      <x:c r="BB27" s="41"/>
+      <x:c r="BC27" s="65"/>
       <x:c r="BD27" s="3"/>
       <x:c r="BE27" s="1"/>
       <x:c r="BF27" s="1"/>
@@ -4060,17 +4287,17 @@
       <x:c r="F28" s="6"/>
       <x:c r="G28" s="6"/>
       <x:c r="H28" s="1"/>
-      <x:c r="I28" s="46"/>
-      <x:c r="J28" s="43"/>
-      <x:c r="K28" s="43"/>
-      <x:c r="L28" s="43"/>
-      <x:c r="M28" s="43"/>
-      <x:c r="N28" s="43"/>
-      <x:c r="O28" s="43"/>
-      <x:c r="P28" s="43"/>
-      <x:c r="Q28" s="43"/>
-      <x:c r="R28" s="43"/>
-      <x:c r="S28" s="47"/>
+      <x:c r="I28" s="82"/>
+      <x:c r="J28" s="42"/>
+      <x:c r="K28" s="42"/>
+      <x:c r="L28" s="42"/>
+      <x:c r="M28" s="42"/>
+      <x:c r="N28" s="42"/>
+      <x:c r="O28" s="42"/>
+      <x:c r="P28" s="42"/>
+      <x:c r="Q28" s="42"/>
+      <x:c r="R28" s="42"/>
+      <x:c r="S28" s="83"/>
       <x:c r="T28" s="6"/>
       <x:c r="U28" s="6"/>
       <x:c r="V28" s="6"/>
@@ -4078,43 +4305,43 @@
       <x:c r="X28" s="6"/>
       <x:c r="Y28" s="6"/>
       <x:c r="Z28" s="6"/>
-      <x:c r="AA28" s="46"/>
-      <x:c r="AB28" s="43"/>
-      <x:c r="AC28" s="43"/>
-      <x:c r="AD28" s="43"/>
-      <x:c r="AE28" s="43"/>
-      <x:c r="AF28" s="43"/>
-      <x:c r="AG28" s="43"/>
-      <x:c r="AH28" s="43"/>
-      <x:c r="AI28" s="43"/>
-      <x:c r="AJ28" s="43"/>
-      <x:c r="AK28" s="47"/>
+      <x:c r="AA28" s="82"/>
+      <x:c r="AB28" s="42"/>
+      <x:c r="AC28" s="42"/>
+      <x:c r="AD28" s="42"/>
+      <x:c r="AE28" s="42"/>
+      <x:c r="AF28" s="42"/>
+      <x:c r="AG28" s="42"/>
+      <x:c r="AH28" s="42"/>
+      <x:c r="AI28" s="42"/>
+      <x:c r="AJ28" s="42"/>
+      <x:c r="AK28" s="83"/>
       <x:c r="AL28" s="1"/>
       <x:c r="AM28" s="6"/>
       <x:c r="AN28" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="AO28" s="30"/>
       <x:c r="AP28" s="29"/>
-      <x:c r="AQ28" s="41" t="s">
-        <x:v>15</x:v>
+      <x:c r="AQ28" s="40" t="s">
+        <x:v>20</x:v>
       </x:c>
-      <x:c r="AR28" s="42"/>
-      <x:c r="AS28" s="42"/>
-      <x:c r="AT28" s="42"/>
-      <x:c r="AU28" s="43" t="s">
-        <x:v>14</x:v>
+      <x:c r="AR28" s="41"/>
+      <x:c r="AS28" s="41"/>
+      <x:c r="AT28" s="41"/>
+      <x:c r="AU28" s="42" t="s">
+        <x:v>22</x:v>
       </x:c>
-      <x:c r="AV28" s="40"/>
-      <x:c r="AW28" s="67" t="s">
-        <x:v>11</x:v>
+      <x:c r="AV28" s="39"/>
+      <x:c r="AW28" s="66" t="s">
+        <x:v>28</x:v>
       </x:c>
-      <x:c r="AX28" s="42"/>
-      <x:c r="AY28" s="42"/>
-      <x:c r="AZ28" s="42"/>
-      <x:c r="BA28" s="42"/>
-      <x:c r="BB28" s="42"/>
-      <x:c r="BC28" s="66"/>
+      <x:c r="AX28" s="41"/>
+      <x:c r="AY28" s="41"/>
+      <x:c r="AZ28" s="41"/>
+      <x:c r="BA28" s="41"/>
+      <x:c r="BB28" s="41"/>
+      <x:c r="BC28" s="65"/>
       <x:c r="BD28" s="14"/>
       <x:c r="BE28" s="1"/>
       <x:c r="BF28" s="1"/>
@@ -4129,47 +4356,49 @@
     <x:row r="29" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="10"/>
-      <x:c r="I29" s="48"/>
-      <x:c r="J29" s="49"/>
-      <x:c r="K29" s="49"/>
-      <x:c r="L29" s="49"/>
-      <x:c r="M29" s="49"/>
-      <x:c r="N29" s="49"/>
-      <x:c r="O29" s="49"/>
-      <x:c r="P29" s="49"/>
-      <x:c r="Q29" s="49"/>
-      <x:c r="R29" s="49"/>
-      <x:c r="S29" s="50"/>
+      <x:c r="H29" s="1"/>
+      <x:c r="I29" s="84"/>
+      <x:c r="J29" s="85"/>
+      <x:c r="K29" s="85"/>
+      <x:c r="L29" s="85"/>
+      <x:c r="M29" s="85"/>
+      <x:c r="N29" s="85"/>
+      <x:c r="O29" s="85"/>
+      <x:c r="P29" s="85"/>
+      <x:c r="Q29" s="85"/>
+      <x:c r="R29" s="85"/>
+      <x:c r="S29" s="86"/>
+      <x:c r="T29" s="1"/>
       <x:c r="Z29" s="6"/>
-      <x:c r="AA29" s="48"/>
-      <x:c r="AB29" s="49"/>
-      <x:c r="AC29" s="49"/>
-      <x:c r="AD29" s="49"/>
-      <x:c r="AE29" s="49"/>
-      <x:c r="AF29" s="49"/>
-      <x:c r="AG29" s="49"/>
-      <x:c r="AH29" s="49"/>
-      <x:c r="AI29" s="49"/>
-      <x:c r="AJ29" s="49"/>
-      <x:c r="AK29" s="50"/>
+      <x:c r="AA29" s="84"/>
+      <x:c r="AB29" s="85"/>
+      <x:c r="AC29" s="85"/>
+      <x:c r="AD29" s="85"/>
+      <x:c r="AE29" s="85"/>
+      <x:c r="AF29" s="85"/>
+      <x:c r="AG29" s="85"/>
+      <x:c r="AH29" s="85"/>
+      <x:c r="AI29" s="85"/>
+      <x:c r="AJ29" s="85"/>
+      <x:c r="AK29" s="86"/>
       <x:c r="AL29" s="1"/>
       <x:c r="AM29" s="6"/>
-      <x:c r="AN29" s="71"/>
-      <x:c r="AO29" s="44"/>
-      <x:c r="AP29" s="45"/>
-      <x:c r="AQ29" s="59"/>
-      <x:c r="AR29" s="44"/>
-      <x:c r="AS29" s="44"/>
-      <x:c r="AT29" s="45"/>
-      <x:c r="AU29" s="77"/>
-      <x:c r="AV29" s="77"/>
-      <x:c r="AW29" s="77"/>
-      <x:c r="AX29" s="77"/>
-      <x:c r="AY29" s="77"/>
-      <x:c r="AZ29" s="77"/>
-      <x:c r="BA29" s="77"/>
-      <x:c r="BB29" s="77"/>
-      <x:c r="BC29" s="62"/>
+      <x:c r="AN29" s="70"/>
+      <x:c r="AO29" s="43"/>
+      <x:c r="AP29" s="44"/>
+      <x:c r="AQ29" s="58"/>
+      <x:c r="AR29" s="43"/>
+      <x:c r="AS29" s="43"/>
+      <x:c r="AT29" s="44"/>
+      <x:c r="AU29" s="76"/>
+      <x:c r="AV29" s="76"/>
+      <x:c r="AW29" s="76"/>
+      <x:c r="AX29" s="76"/>
+      <x:c r="AY29" s="76"/>
+      <x:c r="AZ29" s="76"/>
+      <x:c r="BA29" s="76"/>
+      <x:c r="BB29" s="76"/>
+      <x:c r="BC29" s="61"/>
       <x:c r="BD29" s="3"/>
       <x:c r="BE29" s="1"/>
       <x:c r="BF29" s="1"/>
@@ -4184,25 +4413,49 @@
     <x:row r="30" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="10"/>
+      <x:c r="H30" s="1"/>
+      <x:c r="I30" s="1"/>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+      <x:c r="M30" s="1"/>
+      <x:c r="N30" s="1"/>
+      <x:c r="O30" s="1"/>
+      <x:c r="P30" s="1"/>
+      <x:c r="Q30" s="1"/>
+      <x:c r="R30" s="1"/>
+      <x:c r="S30" s="1"/>
+      <x:c r="T30" s="1"/>
       <x:c r="Z30" s="6"/>
+      <x:c r="AA30" s="1"/>
+      <x:c r="AB30" s="1"/>
+      <x:c r="AC30" s="1"/>
+      <x:c r="AD30" s="1"/>
+      <x:c r="AE30" s="1"/>
+      <x:c r="AF30" s="1"/>
+      <x:c r="AG30" s="1"/>
+      <x:c r="AH30" s="1"/>
+      <x:c r="AI30" s="1"/>
+      <x:c r="AJ30" s="1"/>
+      <x:c r="AK30" s="1"/>
       <x:c r="AL30" s="6"/>
       <x:c r="AM30" s="6"/>
-      <x:c r="AN30" s="46"/>
-      <x:c r="AO30" s="71"/>
-      <x:c r="AP30" s="47"/>
-      <x:c r="AQ30" s="46"/>
-      <x:c r="AR30" s="59"/>
-      <x:c r="AS30" s="59"/>
-      <x:c r="AT30" s="47"/>
-      <x:c r="AU30" s="46"/>
-      <x:c r="AV30" s="77"/>
-      <x:c r="AW30" s="77"/>
-      <x:c r="AX30" s="77"/>
-      <x:c r="AY30" s="77"/>
-      <x:c r="AZ30" s="77"/>
-      <x:c r="BA30" s="77"/>
-      <x:c r="BB30" s="77"/>
-      <x:c r="BC30" s="62"/>
+      <x:c r="AN30" s="45"/>
+      <x:c r="AO30" s="70"/>
+      <x:c r="AP30" s="46"/>
+      <x:c r="AQ30" s="45"/>
+      <x:c r="AR30" s="58"/>
+      <x:c r="AS30" s="58"/>
+      <x:c r="AT30" s="46"/>
+      <x:c r="AU30" s="45"/>
+      <x:c r="AV30" s="76"/>
+      <x:c r="AW30" s="76"/>
+      <x:c r="AX30" s="76"/>
+      <x:c r="AY30" s="76"/>
+      <x:c r="AZ30" s="76"/>
+      <x:c r="BA30" s="76"/>
+      <x:c r="BB30" s="76"/>
+      <x:c r="BC30" s="61"/>
       <x:c r="BD30" s="3"/>
       <x:c r="BE30" s="1"/>
       <x:c r="BF30" s="1"/>
@@ -4223,58 +4476,59 @@
       <x:c r="F31" s="6"/>
       <x:c r="G31" s="6"/>
       <x:c r="H31" s="6"/>
-      <x:c r="I31" s="43" t="s">
-        <x:v>156</x:v>
+      <x:c r="I31" s="79" t="s">
+        <x:v>7</x:v>
       </x:c>
-      <x:c r="J31" s="44"/>
-      <x:c r="K31" s="44"/>
-      <x:c r="L31" s="44"/>
-      <x:c r="M31" s="44"/>
-      <x:c r="N31" s="44"/>
-      <x:c r="O31" s="44"/>
-      <x:c r="P31" s="44"/>
-      <x:c r="Q31" s="44"/>
-      <x:c r="R31" s="44"/>
-      <x:c r="S31" s="45"/>
+      <x:c r="J31" s="80"/>
+      <x:c r="K31" s="80"/>
+      <x:c r="L31" s="80"/>
+      <x:c r="M31" s="80"/>
+      <x:c r="N31" s="80"/>
+      <x:c r="O31" s="80"/>
+      <x:c r="P31" s="80"/>
+      <x:c r="Q31" s="80"/>
+      <x:c r="R31" s="80"/>
+      <x:c r="S31" s="81"/>
       <x:c r="T31" s="6"/>
       <x:c r="U31" s="6"/>
       <x:c r="V31" s="6"/>
       <x:c r="W31" s="6"/>
       <x:c r="X31" s="6"/>
       <x:c r="Y31" s="6"/>
-      <x:c r="AA31" s="43" t="s">
-        <x:v>155</x:v>
+      <x:c r="Z31" s="1"/>
+      <x:c r="AA31" s="79" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="AB31" s="44"/>
-      <x:c r="AC31" s="44"/>
-      <x:c r="AD31" s="44"/>
-      <x:c r="AE31" s="44"/>
-      <x:c r="AF31" s="44"/>
-      <x:c r="AG31" s="44"/>
-      <x:c r="AH31" s="44"/>
-      <x:c r="AI31" s="44"/>
-      <x:c r="AJ31" s="44"/>
-      <x:c r="AK31" s="45"/>
+      <x:c r="AB31" s="80"/>
+      <x:c r="AC31" s="80"/>
+      <x:c r="AD31" s="80"/>
+      <x:c r="AE31" s="80"/>
+      <x:c r="AF31" s="80"/>
+      <x:c r="AG31" s="80"/>
+      <x:c r="AH31" s="80"/>
+      <x:c r="AI31" s="80"/>
+      <x:c r="AJ31" s="80"/>
+      <x:c r="AK31" s="81"/>
       <x:c r="AL31" s="1"/>
       <x:c r="AM31" s="6"/>
-      <x:c r="AN31" s="43"/>
-      <x:c r="AO31" s="44"/>
-      <x:c r="AP31" s="44"/>
-      <x:c r="AQ31" s="44"/>
-      <x:c r="AR31" s="45"/>
-      <x:c r="AS31" s="63" t="s">
-        <x:v>154</x:v>
+      <x:c r="AN31" s="42"/>
+      <x:c r="AO31" s="43"/>
+      <x:c r="AP31" s="43"/>
+      <x:c r="AQ31" s="43"/>
+      <x:c r="AR31" s="44"/>
+      <x:c r="AS31" s="62" t="s">
+        <x:v>152</x:v>
       </x:c>
-      <x:c r="AT31" s="44"/>
-      <x:c r="AU31" s="44"/>
-      <x:c r="AV31" s="44"/>
-      <x:c r="AW31" s="44"/>
-      <x:c r="AX31" s="44"/>
-      <x:c r="AY31" s="44"/>
-      <x:c r="AZ31" s="44"/>
-      <x:c r="BA31" s="44"/>
-      <x:c r="BB31" s="44"/>
-      <x:c r="BC31" s="61"/>
+      <x:c r="AT31" s="43"/>
+      <x:c r="AU31" s="43"/>
+      <x:c r="AV31" s="43"/>
+      <x:c r="AW31" s="43"/>
+      <x:c r="AX31" s="43"/>
+      <x:c r="AY31" s="43"/>
+      <x:c r="AZ31" s="43"/>
+      <x:c r="BA31" s="43"/>
+      <x:c r="BB31" s="43"/>
+      <x:c r="BC31" s="60"/>
       <x:c r="BD31" s="14"/>
       <x:c r="BE31" s="1"/>
       <x:c r="BF31" s="1"/>
@@ -4289,46 +4543,49 @@
     <x:row r="32" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="10"/>
-      <x:c r="I32" s="46"/>
-      <x:c r="J32" s="43"/>
-      <x:c r="K32" s="43"/>
-      <x:c r="L32" s="43"/>
-      <x:c r="M32" s="43"/>
-      <x:c r="N32" s="43"/>
-      <x:c r="O32" s="43"/>
-      <x:c r="P32" s="43"/>
-      <x:c r="Q32" s="43"/>
-      <x:c r="R32" s="43"/>
-      <x:c r="S32" s="47"/>
-      <x:c r="AA32" s="46"/>
-      <x:c r="AB32" s="43"/>
-      <x:c r="AC32" s="43"/>
-      <x:c r="AD32" s="43"/>
-      <x:c r="AE32" s="43"/>
-      <x:c r="AF32" s="43"/>
-      <x:c r="AG32" s="43"/>
-      <x:c r="AH32" s="43"/>
-      <x:c r="AI32" s="43"/>
-      <x:c r="AJ32" s="43"/>
-      <x:c r="AK32" s="47"/>
+      <x:c r="H32" s="1"/>
+      <x:c r="I32" s="82"/>
+      <x:c r="J32" s="42"/>
+      <x:c r="K32" s="42"/>
+      <x:c r="L32" s="42"/>
+      <x:c r="M32" s="42"/>
+      <x:c r="N32" s="42"/>
+      <x:c r="O32" s="42"/>
+      <x:c r="P32" s="42"/>
+      <x:c r="Q32" s="42"/>
+      <x:c r="R32" s="42"/>
+      <x:c r="S32" s="83"/>
+      <x:c r="T32" s="1"/>
+      <x:c r="Z32" s="1"/>
+      <x:c r="AA32" s="82"/>
+      <x:c r="AB32" s="42"/>
+      <x:c r="AC32" s="42"/>
+      <x:c r="AD32" s="42"/>
+      <x:c r="AE32" s="42"/>
+      <x:c r="AF32" s="42"/>
+      <x:c r="AG32" s="42"/>
+      <x:c r="AH32" s="42"/>
+      <x:c r="AI32" s="42"/>
+      <x:c r="AJ32" s="42"/>
+      <x:c r="AK32" s="83"/>
       <x:c r="AL32" s="1"/>
       <x:c r="AM32" s="6"/>
-      <x:c r="AN32" s="46"/>
-      <x:c r="AO32" s="43"/>
-      <x:c r="AP32" s="43"/>
-      <x:c r="AQ32" s="43"/>
-      <x:c r="AR32" s="47"/>
-      <x:c r="AS32" s="48"/>
-      <x:c r="AT32" s="49"/>
-      <x:c r="AU32" s="49"/>
-      <x:c r="AV32" s="49"/>
-      <x:c r="AW32" s="49"/>
-      <x:c r="AX32" s="49"/>
-      <x:c r="AY32" s="49"/>
-      <x:c r="AZ32" s="49"/>
-      <x:c r="BA32" s="49"/>
-      <x:c r="BB32" s="49"/>
-      <x:c r="BC32" s="64"/>
+      <x:c r="AN32" s="45"/>
+      <x:c r="AO32" s="42"/>
+      <x:c r="AP32" s="42"/>
+      <x:c r="AQ32" s="42"/>
+      <x:c r="AR32" s="46"/>
+      <x:c r="AS32" s="47"/>
+      <x:c r="AT32" s="48"/>
+      <x:c r="AU32" s="48"/>
+      <x:c r="AV32" s="48"/>
+      <x:c r="AW32" s="48"/>
+      <x:c r="AX32" s="48"/>
+      <x:c r="AY32" s="48"/>
+      <x:c r="AZ32" s="48"/>
+      <x:c r="BA32" s="48"/>
+      <x:c r="BB32" s="48"/>
+      <x:c r="BC32" s="63"/>
       <x:c r="BD32" s="31"/>
       <x:c r="BE32" s="1"/>
       <x:c r="BF32" s="1"/>
@@ -4349,17 +4606,17 @@
       <x:c r="F33" s="6"/>
       <x:c r="G33" s="6"/>
       <x:c r="H33" s="6"/>
-      <x:c r="I33" s="46"/>
-      <x:c r="J33" s="43"/>
-      <x:c r="K33" s="43"/>
-      <x:c r="L33" s="43"/>
-      <x:c r="M33" s="43"/>
-      <x:c r="N33" s="43"/>
-      <x:c r="O33" s="43"/>
-      <x:c r="P33" s="43"/>
-      <x:c r="Q33" s="43"/>
-      <x:c r="R33" s="43"/>
-      <x:c r="S33" s="47"/>
+      <x:c r="I33" s="82"/>
+      <x:c r="J33" s="42"/>
+      <x:c r="K33" s="42"/>
+      <x:c r="L33" s="42"/>
+      <x:c r="M33" s="42"/>
+      <x:c r="N33" s="42"/>
+      <x:c r="O33" s="42"/>
+      <x:c r="P33" s="42"/>
+      <x:c r="Q33" s="42"/>
+      <x:c r="R33" s="42"/>
+      <x:c r="S33" s="83"/>
       <x:c r="T33" s="6"/>
       <x:c r="U33" s="6"/>
       <x:c r="V33" s="6"/>
@@ -4367,37 +4624,37 @@
       <x:c r="X33" s="6"/>
       <x:c r="Y33" s="6"/>
       <x:c r="Z33" s="6"/>
-      <x:c r="AA33" s="46"/>
-      <x:c r="AB33" s="43"/>
-      <x:c r="AC33" s="43"/>
-      <x:c r="AD33" s="43"/>
-      <x:c r="AE33" s="43"/>
-      <x:c r="AF33" s="43"/>
-      <x:c r="AG33" s="43"/>
-      <x:c r="AH33" s="43"/>
-      <x:c r="AI33" s="43"/>
-      <x:c r="AJ33" s="43"/>
-      <x:c r="AK33" s="47"/>
+      <x:c r="AA33" s="82"/>
+      <x:c r="AB33" s="42"/>
+      <x:c r="AC33" s="42"/>
+      <x:c r="AD33" s="42"/>
+      <x:c r="AE33" s="42"/>
+      <x:c r="AF33" s="42"/>
+      <x:c r="AG33" s="42"/>
+      <x:c r="AH33" s="42"/>
+      <x:c r="AI33" s="42"/>
+      <x:c r="AJ33" s="42"/>
+      <x:c r="AK33" s="83"/>
       <x:c r="AL33" s="1"/>
       <x:c r="AM33" s="6"/>
-      <x:c r="AN33" s="46"/>
-      <x:c r="AO33" s="43"/>
-      <x:c r="AP33" s="43"/>
-      <x:c r="AQ33" s="43"/>
-      <x:c r="AR33" s="47"/>
-      <x:c r="AS33" s="60" t="s">
-        <x:v>158</x:v>
+      <x:c r="AN33" s="45"/>
+      <x:c r="AO33" s="42"/>
+      <x:c r="AP33" s="42"/>
+      <x:c r="AQ33" s="42"/>
+      <x:c r="AR33" s="46"/>
+      <x:c r="AS33" s="59" t="s">
+        <x:v>153</x:v>
       </x:c>
-      <x:c r="AT33" s="44"/>
-      <x:c r="AU33" s="44"/>
-      <x:c r="AV33" s="44"/>
-      <x:c r="AW33" s="44"/>
-      <x:c r="AX33" s="44"/>
-      <x:c r="AY33" s="44"/>
-      <x:c r="AZ33" s="44"/>
-      <x:c r="BA33" s="44"/>
-      <x:c r="BB33" s="44"/>
-      <x:c r="BC33" s="61"/>
+      <x:c r="AT33" s="43"/>
+      <x:c r="AU33" s="43"/>
+      <x:c r="AV33" s="43"/>
+      <x:c r="AW33" s="43"/>
+      <x:c r="AX33" s="43"/>
+      <x:c r="AY33" s="43"/>
+      <x:c r="AZ33" s="43"/>
+      <x:c r="BA33" s="43"/>
+      <x:c r="BB33" s="43"/>
+      <x:c r="BC33" s="60"/>
       <x:c r="BD33" s="31"/>
       <x:c r="BE33" s="1"/>
       <x:c r="BF33" s="1"/>
@@ -4412,63 +4669,63 @@
     <x:row r="34" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="10"/>
-      <x:c r="C34" s="38" t="s">
-        <x:v>157</x:v>
+      <x:c r="C34" s="88" t="s">
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="D34" s="38"/>
-      <x:c r="E34" s="38"/>
-      <x:c r="F34" s="38"/>
-      <x:c r="G34" s="38"/>
-      <x:c r="H34" s="38"/>
-      <x:c r="I34" s="46"/>
-      <x:c r="J34" s="43"/>
-      <x:c r="K34" s="43"/>
-      <x:c r="L34" s="43"/>
-      <x:c r="M34" s="43"/>
-      <x:c r="N34" s="43"/>
-      <x:c r="O34" s="43"/>
-      <x:c r="P34" s="43"/>
-      <x:c r="Q34" s="43"/>
-      <x:c r="R34" s="43"/>
-      <x:c r="S34" s="47"/>
+      <x:c r="D34" s="89"/>
+      <x:c r="E34" s="89"/>
+      <x:c r="F34" s="89"/>
+      <x:c r="G34" s="89"/>
+      <x:c r="H34" s="90"/>
+      <x:c r="I34" s="82"/>
+      <x:c r="J34" s="42"/>
+      <x:c r="K34" s="42"/>
+      <x:c r="L34" s="42"/>
+      <x:c r="M34" s="42"/>
+      <x:c r="N34" s="42"/>
+      <x:c r="O34" s="42"/>
+      <x:c r="P34" s="42"/>
+      <x:c r="Q34" s="42"/>
+      <x:c r="R34" s="42"/>
+      <x:c r="S34" s="83"/>
       <x:c r="T34" s="6"/>
-      <x:c r="U34" s="43" t="s">
-        <x:v>160</x:v>
+      <x:c r="U34" s="79" t="s">
+        <x:v>8</x:v>
       </x:c>
-      <x:c r="V34" s="44"/>
-      <x:c r="W34" s="44"/>
-      <x:c r="X34" s="44"/>
-      <x:c r="Y34" s="44"/>
-      <x:c r="Z34" s="45"/>
-      <x:c r="AA34" s="46"/>
-      <x:c r="AB34" s="43"/>
-      <x:c r="AC34" s="43"/>
-      <x:c r="AD34" s="43"/>
-      <x:c r="AE34" s="43"/>
-      <x:c r="AF34" s="43"/>
-      <x:c r="AG34" s="43"/>
-      <x:c r="AH34" s="43"/>
-      <x:c r="AI34" s="43"/>
-      <x:c r="AJ34" s="43"/>
-      <x:c r="AK34" s="47"/>
+      <x:c r="V34" s="80"/>
+      <x:c r="W34" s="80"/>
+      <x:c r="X34" s="80"/>
+      <x:c r="Y34" s="80"/>
+      <x:c r="Z34" s="81"/>
+      <x:c r="AA34" s="82"/>
+      <x:c r="AB34" s="42"/>
+      <x:c r="AC34" s="42"/>
+      <x:c r="AD34" s="42"/>
+      <x:c r="AE34" s="42"/>
+      <x:c r="AF34" s="42"/>
+      <x:c r="AG34" s="42"/>
+      <x:c r="AH34" s="42"/>
+      <x:c r="AI34" s="42"/>
+      <x:c r="AJ34" s="42"/>
+      <x:c r="AK34" s="83"/>
       <x:c r="AL34" s="1"/>
       <x:c r="AM34" s="6"/>
-      <x:c r="AN34" s="48"/>
-      <x:c r="AO34" s="49"/>
-      <x:c r="AP34" s="49"/>
-      <x:c r="AQ34" s="49"/>
-      <x:c r="AR34" s="50"/>
-      <x:c r="AS34" s="46"/>
-      <x:c r="AT34" s="60"/>
-      <x:c r="AU34" s="60"/>
-      <x:c r="AV34" s="60"/>
-      <x:c r="AW34" s="60"/>
-      <x:c r="AX34" s="60"/>
-      <x:c r="AY34" s="60"/>
-      <x:c r="AZ34" s="60"/>
-      <x:c r="BA34" s="60"/>
-      <x:c r="BB34" s="60"/>
-      <x:c r="BC34" s="62"/>
+      <x:c r="AN34" s="47"/>
+      <x:c r="AO34" s="48"/>
+      <x:c r="AP34" s="48"/>
+      <x:c r="AQ34" s="48"/>
+      <x:c r="AR34" s="49"/>
+      <x:c r="AS34" s="45"/>
+      <x:c r="AT34" s="59"/>
+      <x:c r="AU34" s="59"/>
+      <x:c r="AV34" s="59"/>
+      <x:c r="AW34" s="59"/>
+      <x:c r="AX34" s="59"/>
+      <x:c r="AY34" s="59"/>
+      <x:c r="AZ34" s="59"/>
+      <x:c r="BA34" s="59"/>
+      <x:c r="BB34" s="59"/>
+      <x:c r="BC34" s="61"/>
       <x:c r="BD34" s="32"/>
       <x:c r="BE34" s="1"/>
       <x:c r="BF34" s="1"/>
@@ -4483,63 +4740,63 @@
     <x:row r="35" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="10"/>
-      <x:c r="C35" s="38"/>
-      <x:c r="D35" s="38"/>
-      <x:c r="E35" s="38"/>
-      <x:c r="F35" s="38"/>
-      <x:c r="G35" s="38"/>
-      <x:c r="H35" s="38"/>
-      <x:c r="I35" s="46"/>
-      <x:c r="J35" s="43"/>
-      <x:c r="K35" s="43"/>
-      <x:c r="L35" s="43"/>
-      <x:c r="M35" s="43"/>
-      <x:c r="N35" s="43"/>
-      <x:c r="O35" s="43"/>
-      <x:c r="P35" s="43"/>
-      <x:c r="Q35" s="43"/>
-      <x:c r="R35" s="43"/>
-      <x:c r="S35" s="47"/>
-      <x:c r="T35" s="33"/>
-      <x:c r="U35" s="48"/>
-      <x:c r="V35" s="49"/>
-      <x:c r="W35" s="49"/>
-      <x:c r="X35" s="49"/>
-      <x:c r="Y35" s="49"/>
-      <x:c r="Z35" s="50"/>
-      <x:c r="AA35" s="46"/>
-      <x:c r="AB35" s="43"/>
-      <x:c r="AC35" s="43"/>
-      <x:c r="AD35" s="43"/>
-      <x:c r="AE35" s="43"/>
-      <x:c r="AF35" s="43"/>
-      <x:c r="AG35" s="43"/>
-      <x:c r="AH35" s="43"/>
-      <x:c r="AI35" s="43"/>
-      <x:c r="AJ35" s="43"/>
-      <x:c r="AK35" s="47"/>
+      <x:c r="C35" s="91"/>
+      <x:c r="D35" s="92"/>
+      <x:c r="E35" s="92"/>
+      <x:c r="F35" s="92"/>
+      <x:c r="G35" s="92"/>
+      <x:c r="H35" s="93"/>
+      <x:c r="I35" s="82"/>
+      <x:c r="J35" s="42"/>
+      <x:c r="K35" s="42"/>
+      <x:c r="L35" s="42"/>
+      <x:c r="M35" s="42"/>
+      <x:c r="N35" s="42"/>
+      <x:c r="O35" s="42"/>
+      <x:c r="P35" s="42"/>
+      <x:c r="Q35" s="42"/>
+      <x:c r="R35" s="42"/>
+      <x:c r="S35" s="83"/>
+      <x:c r="T35" s="87"/>
+      <x:c r="U35" s="84"/>
+      <x:c r="V35" s="85"/>
+      <x:c r="W35" s="85"/>
+      <x:c r="X35" s="85"/>
+      <x:c r="Y35" s="85"/>
+      <x:c r="Z35" s="86"/>
+      <x:c r="AA35" s="82"/>
+      <x:c r="AB35" s="42"/>
+      <x:c r="AC35" s="42"/>
+      <x:c r="AD35" s="42"/>
+      <x:c r="AE35" s="42"/>
+      <x:c r="AF35" s="42"/>
+      <x:c r="AG35" s="42"/>
+      <x:c r="AH35" s="42"/>
+      <x:c r="AI35" s="42"/>
+      <x:c r="AJ35" s="42"/>
+      <x:c r="AK35" s="83"/>
       <x:c r="AL35" s="1"/>
       <x:c r="AM35" s="6"/>
-      <x:c r="AN35" s="41" t="s">
-        <x:v>9</x:v>
+      <x:c r="AN35" s="40" t="s">
+        <x:v>25</x:v>
       </x:c>
-      <x:c r="AO35" s="44"/>
-      <x:c r="AP35" s="44"/>
-      <x:c r="AQ35" s="44"/>
-      <x:c r="AR35" s="44"/>
-      <x:c r="AS35" s="63" t="s">
-        <x:v>159</x:v>
+      <x:c r="AO35" s="43"/>
+      <x:c r="AP35" s="43"/>
+      <x:c r="AQ35" s="43"/>
+      <x:c r="AR35" s="43"/>
+      <x:c r="AS35" s="62" t="s">
+        <x:v>155</x:v>
       </x:c>
-      <x:c r="AT35" s="44"/>
-      <x:c r="AU35" s="44"/>
-      <x:c r="AV35" s="44"/>
-      <x:c r="AW35" s="44"/>
-      <x:c r="AX35" s="44"/>
-      <x:c r="AY35" s="44"/>
-      <x:c r="AZ35" s="44"/>
-      <x:c r="BA35" s="44"/>
-      <x:c r="BB35" s="44"/>
-      <x:c r="BC35" s="61"/>
+      <x:c r="AT35" s="43"/>
+      <x:c r="AU35" s="43"/>
+      <x:c r="AV35" s="43"/>
+      <x:c r="AW35" s="43"/>
+      <x:c r="AX35" s="43"/>
+      <x:c r="AY35" s="43"/>
+      <x:c r="AZ35" s="43"/>
+      <x:c r="BA35" s="43"/>
+      <x:c r="BB35" s="43"/>
+      <x:c r="BC35" s="60"/>
       <x:c r="BD35" s="31"/>
       <x:c r="BE35" s="1"/>
       <x:c r="BF35" s="1"/>
@@ -4554,48 +4811,59 @@
     <x:row r="36" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="10"/>
-      <x:c r="I36" s="46"/>
-      <x:c r="J36" s="43"/>
-      <x:c r="K36" s="43"/>
-      <x:c r="L36" s="43"/>
-      <x:c r="M36" s="43"/>
-      <x:c r="N36" s="43"/>
-      <x:c r="O36" s="43"/>
-      <x:c r="P36" s="43"/>
-      <x:c r="Q36" s="43"/>
-      <x:c r="R36" s="43"/>
-      <x:c r="S36" s="47"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
+      <x:c r="I36" s="82"/>
+      <x:c r="J36" s="42"/>
+      <x:c r="K36" s="42"/>
+      <x:c r="L36" s="42"/>
+      <x:c r="M36" s="42"/>
+      <x:c r="N36" s="42"/>
+      <x:c r="O36" s="42"/>
+      <x:c r="P36" s="42"/>
+      <x:c r="Q36" s="42"/>
+      <x:c r="R36" s="42"/>
+      <x:c r="S36" s="83"/>
       <x:c r="T36" s="6"/>
+      <x:c r="U36" s="1"/>
+      <x:c r="V36" s="1"/>
+      <x:c r="W36" s="1"/>
+      <x:c r="X36" s="1"/>
+      <x:c r="Y36" s="1"/>
       <x:c r="Z36" s="6"/>
-      <x:c r="AA36" s="46"/>
-      <x:c r="AB36" s="43"/>
-      <x:c r="AC36" s="43"/>
-      <x:c r="AD36" s="43"/>
-      <x:c r="AE36" s="43"/>
-      <x:c r="AF36" s="43"/>
-      <x:c r="AG36" s="43"/>
-      <x:c r="AH36" s="43"/>
-      <x:c r="AI36" s="43"/>
-      <x:c r="AJ36" s="43"/>
-      <x:c r="AK36" s="47"/>
+      <x:c r="AA36" s="82"/>
+      <x:c r="AB36" s="42"/>
+      <x:c r="AC36" s="42"/>
+      <x:c r="AD36" s="42"/>
+      <x:c r="AE36" s="42"/>
+      <x:c r="AF36" s="42"/>
+      <x:c r="AG36" s="42"/>
+      <x:c r="AH36" s="42"/>
+      <x:c r="AI36" s="42"/>
+      <x:c r="AJ36" s="42"/>
+      <x:c r="AK36" s="83"/>
       <x:c r="AL36" s="1"/>
       <x:c r="AM36" s="6"/>
-      <x:c r="AN36" s="46"/>
-      <x:c r="AO36" s="41"/>
-      <x:c r="AP36" s="41"/>
-      <x:c r="AQ36" s="41"/>
-      <x:c r="AR36" s="41"/>
-      <x:c r="AS36" s="46"/>
-      <x:c r="AT36" s="63"/>
-      <x:c r="AU36" s="63"/>
-      <x:c r="AV36" s="63"/>
-      <x:c r="AW36" s="63"/>
-      <x:c r="AX36" s="63"/>
-      <x:c r="AY36" s="63"/>
-      <x:c r="AZ36" s="63"/>
-      <x:c r="BA36" s="63"/>
-      <x:c r="BB36" s="63"/>
-      <x:c r="BC36" s="62"/>
+      <x:c r="AN36" s="45"/>
+      <x:c r="AO36" s="40"/>
+      <x:c r="AP36" s="40"/>
+      <x:c r="AQ36" s="40"/>
+      <x:c r="AR36" s="40"/>
+      <x:c r="AS36" s="45"/>
+      <x:c r="AT36" s="62"/>
+      <x:c r="AU36" s="62"/>
+      <x:c r="AV36" s="62"/>
+      <x:c r="AW36" s="62"/>
+      <x:c r="AX36" s="62"/>
+      <x:c r="AY36" s="62"/>
+      <x:c r="AZ36" s="62"/>
+      <x:c r="BA36" s="62"/>
+      <x:c r="BB36" s="62"/>
+      <x:c r="BC36" s="61"/>
       <x:c r="BD36" s="31"/>
       <x:c r="BE36" s="1"/>
       <x:c r="BF36" s="1"/>
@@ -4616,17 +4884,17 @@
       <x:c r="F37" s="6"/>
       <x:c r="G37" s="6"/>
       <x:c r="H37" s="6"/>
-      <x:c r="I37" s="46"/>
-      <x:c r="J37" s="43"/>
-      <x:c r="K37" s="43"/>
-      <x:c r="L37" s="43"/>
-      <x:c r="M37" s="43"/>
-      <x:c r="N37" s="43"/>
-      <x:c r="O37" s="43"/>
-      <x:c r="P37" s="43"/>
-      <x:c r="Q37" s="43"/>
-      <x:c r="R37" s="43"/>
-      <x:c r="S37" s="47"/>
+      <x:c r="I37" s="82"/>
+      <x:c r="J37" s="42"/>
+      <x:c r="K37" s="42"/>
+      <x:c r="L37" s="42"/>
+      <x:c r="M37" s="42"/>
+      <x:c r="N37" s="42"/>
+      <x:c r="O37" s="42"/>
+      <x:c r="P37" s="42"/>
+      <x:c r="Q37" s="42"/>
+      <x:c r="R37" s="42"/>
+      <x:c r="S37" s="83"/>
       <x:c r="T37" s="6"/>
       <x:c r="U37" s="6"/>
       <x:c r="V37" s="6"/>
@@ -4634,35 +4902,35 @@
       <x:c r="X37" s="6"/>
       <x:c r="Y37" s="6"/>
       <x:c r="Z37" s="6"/>
-      <x:c r="AA37" s="46"/>
-      <x:c r="AB37" s="43"/>
-      <x:c r="AC37" s="43"/>
-      <x:c r="AD37" s="43"/>
-      <x:c r="AE37" s="43"/>
-      <x:c r="AF37" s="43"/>
-      <x:c r="AG37" s="43"/>
-      <x:c r="AH37" s="43"/>
-      <x:c r="AI37" s="43"/>
-      <x:c r="AJ37" s="43"/>
-      <x:c r="AK37" s="47"/>
+      <x:c r="AA37" s="82"/>
+      <x:c r="AB37" s="42"/>
+      <x:c r="AC37" s="42"/>
+      <x:c r="AD37" s="42"/>
+      <x:c r="AE37" s="42"/>
+      <x:c r="AF37" s="42"/>
+      <x:c r="AG37" s="42"/>
+      <x:c r="AH37" s="42"/>
+      <x:c r="AI37" s="42"/>
+      <x:c r="AJ37" s="42"/>
+      <x:c r="AK37" s="83"/>
       <x:c r="AL37" s="1"/>
       <x:c r="AM37" s="6"/>
-      <x:c r="AN37" s="46"/>
-      <x:c r="AO37" s="41"/>
-      <x:c r="AP37" s="41"/>
-      <x:c r="AQ37" s="41"/>
-      <x:c r="AR37" s="41"/>
-      <x:c r="AS37" s="46"/>
-      <x:c r="AT37" s="63"/>
-      <x:c r="AU37" s="63"/>
-      <x:c r="AV37" s="63"/>
-      <x:c r="AW37" s="63"/>
-      <x:c r="AX37" s="63"/>
-      <x:c r="AY37" s="63"/>
-      <x:c r="AZ37" s="63"/>
-      <x:c r="BA37" s="63"/>
-      <x:c r="BB37" s="63"/>
-      <x:c r="BC37" s="62"/>
+      <x:c r="AN37" s="45"/>
+      <x:c r="AO37" s="40"/>
+      <x:c r="AP37" s="40"/>
+      <x:c r="AQ37" s="40"/>
+      <x:c r="AR37" s="40"/>
+      <x:c r="AS37" s="45"/>
+      <x:c r="AT37" s="62"/>
+      <x:c r="AU37" s="62"/>
+      <x:c r="AV37" s="62"/>
+      <x:c r="AW37" s="62"/>
+      <x:c r="AX37" s="62"/>
+      <x:c r="AY37" s="62"/>
+      <x:c r="AZ37" s="62"/>
+      <x:c r="BA37" s="62"/>
+      <x:c r="BB37" s="62"/>
+      <x:c r="BC37" s="61"/>
       <x:c r="BD37" s="32"/>
       <x:c r="BE37" s="1"/>
       <x:c r="BF37" s="1"/>
@@ -4683,17 +4951,17 @@
       <x:c r="F38" s="6"/>
       <x:c r="G38" s="6"/>
       <x:c r="H38" s="6"/>
-      <x:c r="I38" s="48"/>
-      <x:c r="J38" s="49"/>
-      <x:c r="K38" s="49"/>
-      <x:c r="L38" s="49"/>
-      <x:c r="M38" s="49"/>
-      <x:c r="N38" s="49"/>
-      <x:c r="O38" s="49"/>
-      <x:c r="P38" s="49"/>
-      <x:c r="Q38" s="49"/>
-      <x:c r="R38" s="49"/>
-      <x:c r="S38" s="50"/>
+      <x:c r="I38" s="84"/>
+      <x:c r="J38" s="85"/>
+      <x:c r="K38" s="85"/>
+      <x:c r="L38" s="85"/>
+      <x:c r="M38" s="85"/>
+      <x:c r="N38" s="85"/>
+      <x:c r="O38" s="85"/>
+      <x:c r="P38" s="85"/>
+      <x:c r="Q38" s="85"/>
+      <x:c r="R38" s="85"/>
+      <x:c r="S38" s="86"/>
       <x:c r="T38" s="6"/>
       <x:c r="U38" s="6"/>
       <x:c r="V38" s="6"/>
@@ -4701,35 +4969,35 @@
       <x:c r="X38" s="6"/>
       <x:c r="Y38" s="6"/>
       <x:c r="Z38" s="6"/>
-      <x:c r="AA38" s="48"/>
-      <x:c r="AB38" s="49"/>
-      <x:c r="AC38" s="49"/>
-      <x:c r="AD38" s="49"/>
-      <x:c r="AE38" s="49"/>
-      <x:c r="AF38" s="49"/>
-      <x:c r="AG38" s="49"/>
-      <x:c r="AH38" s="49"/>
-      <x:c r="AI38" s="49"/>
-      <x:c r="AJ38" s="49"/>
-      <x:c r="AK38" s="50"/>
+      <x:c r="AA38" s="84"/>
+      <x:c r="AB38" s="85"/>
+      <x:c r="AC38" s="85"/>
+      <x:c r="AD38" s="85"/>
+      <x:c r="AE38" s="85"/>
+      <x:c r="AF38" s="85"/>
+      <x:c r="AG38" s="85"/>
+      <x:c r="AH38" s="85"/>
+      <x:c r="AI38" s="85"/>
+      <x:c r="AJ38" s="85"/>
+      <x:c r="AK38" s="86"/>
       <x:c r="AL38" s="1"/>
       <x:c r="AM38" s="6"/>
-      <x:c r="AN38" s="48"/>
-      <x:c r="AO38" s="49"/>
-      <x:c r="AP38" s="49"/>
-      <x:c r="AQ38" s="49"/>
-      <x:c r="AR38" s="49"/>
-      <x:c r="AS38" s="48"/>
-      <x:c r="AT38" s="49"/>
-      <x:c r="AU38" s="49"/>
-      <x:c r="AV38" s="49"/>
-      <x:c r="AW38" s="49"/>
-      <x:c r="AX38" s="49"/>
-      <x:c r="AY38" s="49"/>
-      <x:c r="AZ38" s="49"/>
-      <x:c r="BA38" s="49"/>
-      <x:c r="BB38" s="49"/>
-      <x:c r="BC38" s="64"/>
+      <x:c r="AN38" s="47"/>
+      <x:c r="AO38" s="48"/>
+      <x:c r="AP38" s="48"/>
+      <x:c r="AQ38" s="48"/>
+      <x:c r="AR38" s="48"/>
+      <x:c r="AS38" s="47"/>
+      <x:c r="AT38" s="48"/>
+      <x:c r="AU38" s="48"/>
+      <x:c r="AV38" s="48"/>
+      <x:c r="AW38" s="48"/>
+      <x:c r="AX38" s="48"/>
+      <x:c r="AY38" s="48"/>
+      <x:c r="AZ38" s="48"/>
+      <x:c r="BA38" s="48"/>
+      <x:c r="BB38" s="48"/>
+      <x:c r="BC38" s="63"/>
       <x:c r="BD38" s="31"/>
       <x:c r="BE38" s="1"/>
       <x:c r="BF38" s="1"/>
@@ -4750,6 +5018,17 @@
       <x:c r="F39" s="6"/>
       <x:c r="G39" s="6"/>
       <x:c r="H39" s="6"/>
+      <x:c r="I39" s="1"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+      <x:c r="M39" s="1"/>
+      <x:c r="N39" s="1"/>
+      <x:c r="O39" s="1"/>
+      <x:c r="P39" s="1"/>
+      <x:c r="Q39" s="1"/>
+      <x:c r="R39" s="1"/>
+      <x:c r="S39" s="1"/>
       <x:c r="T39" s="6"/>
       <x:c r="U39" s="6"/>
       <x:c r="V39" s="6"/>
@@ -4757,26 +5036,37 @@
       <x:c r="X39" s="6"/>
       <x:c r="Y39" s="6"/>
       <x:c r="Z39" s="6"/>
+      <x:c r="AA39" s="1"/>
+      <x:c r="AB39" s="1"/>
+      <x:c r="AC39" s="1"/>
+      <x:c r="AD39" s="1"/>
+      <x:c r="AE39" s="1"/>
+      <x:c r="AF39" s="1"/>
+      <x:c r="AG39" s="1"/>
+      <x:c r="AH39" s="1"/>
+      <x:c r="AI39" s="1"/>
+      <x:c r="AJ39" s="1"/>
+      <x:c r="AK39" s="1"/>
       <x:c r="AL39" s="1"/>
       <x:c r="AM39" s="6"/>
-      <x:c r="AN39" s="73" t="s">
-        <x:v>18</x:v>
+      <x:c r="AN39" s="72" t="s">
+        <x:v>19</x:v>
       </x:c>
-      <x:c r="AO39" s="73"/>
-      <x:c r="AP39" s="73"/>
-      <x:c r="AQ39" s="73"/>
-      <x:c r="AR39" s="73"/>
-      <x:c r="AS39" s="73"/>
-      <x:c r="AT39" s="73"/>
-      <x:c r="AU39" s="73"/>
-      <x:c r="AV39" s="73"/>
-      <x:c r="AW39" s="73"/>
-      <x:c r="AX39" s="73"/>
-      <x:c r="AY39" s="73"/>
-      <x:c r="AZ39" s="73"/>
-      <x:c r="BA39" s="73"/>
-      <x:c r="BB39" s="73"/>
-      <x:c r="BC39" s="62"/>
+      <x:c r="AO39" s="72"/>
+      <x:c r="AP39" s="72"/>
+      <x:c r="AQ39" s="72"/>
+      <x:c r="AR39" s="72"/>
+      <x:c r="AS39" s="72"/>
+      <x:c r="AT39" s="72"/>
+      <x:c r="AU39" s="72"/>
+      <x:c r="AV39" s="72"/>
+      <x:c r="AW39" s="72"/>
+      <x:c r="AX39" s="72"/>
+      <x:c r="AY39" s="72"/>
+      <x:c r="AZ39" s="72"/>
+      <x:c r="BA39" s="72"/>
+      <x:c r="BB39" s="72"/>
+      <x:c r="BC39" s="61"/>
       <x:c r="BD39" s="3"/>
       <x:c r="BE39" s="1"/>
       <x:c r="BF39" s="1"/>
@@ -4790,60 +5080,60 @@
     </x:row>
     <x:row r="40" spans="1:65" ht="16.5" customHeight="1">
       <x:c r="A40" s="1"/>
-      <x:c r="B40" s="34"/>
-      <x:c r="C40" s="35"/>
-      <x:c r="D40" s="35"/>
-      <x:c r="E40" s="35"/>
-      <x:c r="F40" s="35"/>
-      <x:c r="G40" s="35"/>
-      <x:c r="H40" s="35"/>
-      <x:c r="I40" s="35"/>
-      <x:c r="J40" s="35"/>
-      <x:c r="K40" s="35"/>
-      <x:c r="L40" s="35"/>
-      <x:c r="M40" s="35"/>
-      <x:c r="N40" s="35"/>
-      <x:c r="O40" s="35"/>
-      <x:c r="P40" s="35"/>
-      <x:c r="Q40" s="35"/>
-      <x:c r="R40" s="35"/>
-      <x:c r="S40" s="35"/>
-      <x:c r="T40" s="35"/>
-      <x:c r="U40" s="35"/>
-      <x:c r="V40" s="35"/>
-      <x:c r="W40" s="35"/>
-      <x:c r="X40" s="35"/>
-      <x:c r="Y40" s="35"/>
-      <x:c r="Z40" s="35"/>
-      <x:c r="AA40" s="35"/>
-      <x:c r="AB40" s="35"/>
-      <x:c r="AC40" s="35"/>
-      <x:c r="AD40" s="35"/>
-      <x:c r="AE40" s="35"/>
-      <x:c r="AF40" s="35"/>
-      <x:c r="AG40" s="35"/>
-      <x:c r="AH40" s="35"/>
-      <x:c r="AI40" s="35"/>
-      <x:c r="AJ40" s="35"/>
-      <x:c r="AK40" s="35"/>
-      <x:c r="AL40" s="35"/>
-      <x:c r="AM40" s="35"/>
-      <x:c r="AN40" s="74"/>
-      <x:c r="AO40" s="75"/>
-      <x:c r="AP40" s="75"/>
-      <x:c r="AQ40" s="75"/>
-      <x:c r="AR40" s="75"/>
-      <x:c r="AS40" s="75"/>
-      <x:c r="AT40" s="75"/>
-      <x:c r="AU40" s="75"/>
-      <x:c r="AV40" s="75"/>
-      <x:c r="AW40" s="75"/>
-      <x:c r="AX40" s="75"/>
-      <x:c r="AY40" s="75"/>
-      <x:c r="AZ40" s="75"/>
-      <x:c r="BA40" s="75"/>
-      <x:c r="BB40" s="75"/>
-      <x:c r="BC40" s="76"/>
+      <x:c r="B40" s="33"/>
+      <x:c r="C40" s="34"/>
+      <x:c r="D40" s="34"/>
+      <x:c r="E40" s="34"/>
+      <x:c r="F40" s="34"/>
+      <x:c r="G40" s="34"/>
+      <x:c r="H40" s="34"/>
+      <x:c r="I40" s="34"/>
+      <x:c r="J40" s="34"/>
+      <x:c r="K40" s="34"/>
+      <x:c r="L40" s="34"/>
+      <x:c r="M40" s="34"/>
+      <x:c r="N40" s="34"/>
+      <x:c r="O40" s="34"/>
+      <x:c r="P40" s="34"/>
+      <x:c r="Q40" s="34"/>
+      <x:c r="R40" s="34"/>
+      <x:c r="S40" s="34"/>
+      <x:c r="T40" s="34"/>
+      <x:c r="U40" s="34"/>
+      <x:c r="V40" s="34"/>
+      <x:c r="W40" s="34"/>
+      <x:c r="X40" s="34"/>
+      <x:c r="Y40" s="34"/>
+      <x:c r="Z40" s="34"/>
+      <x:c r="AA40" s="34"/>
+      <x:c r="AB40" s="34"/>
+      <x:c r="AC40" s="34"/>
+      <x:c r="AD40" s="34"/>
+      <x:c r="AE40" s="34"/>
+      <x:c r="AF40" s="34"/>
+      <x:c r="AG40" s="34"/>
+      <x:c r="AH40" s="34"/>
+      <x:c r="AI40" s="34"/>
+      <x:c r="AJ40" s="34"/>
+      <x:c r="AK40" s="34"/>
+      <x:c r="AL40" s="34"/>
+      <x:c r="AM40" s="34"/>
+      <x:c r="AN40" s="73"/>
+      <x:c r="AO40" s="74"/>
+      <x:c r="AP40" s="74"/>
+      <x:c r="AQ40" s="74"/>
+      <x:c r="AR40" s="74"/>
+      <x:c r="AS40" s="74"/>
+      <x:c r="AT40" s="74"/>
+      <x:c r="AU40" s="74"/>
+      <x:c r="AV40" s="74"/>
+      <x:c r="AW40" s="74"/>
+      <x:c r="AX40" s="74"/>
+      <x:c r="AY40" s="74"/>
+      <x:c r="AZ40" s="74"/>
+      <x:c r="BA40" s="74"/>
+      <x:c r="BB40" s="74"/>
+      <x:c r="BC40" s="75"/>
       <x:c r="BD40" s="3"/>
       <x:c r="BE40" s="1"/>
       <x:c r="BF40" s="1"/>
@@ -4859,55 +5149,55 @@
       <x:c r="A41" s="3"/>
       <x:c r="B41" s="3"/>
       <x:c r="C41" s="3"/>
-      <x:c r="D41" s="36"/>
+      <x:c r="D41" s="35"/>
       <x:c r="E41" s="3"/>
       <x:c r="F41" s="3"/>
-      <x:c r="G41" s="36"/>
+      <x:c r="G41" s="35"/>
       <x:c r="H41" s="3"/>
       <x:c r="I41" s="3"/>
-      <x:c r="J41" s="36"/>
+      <x:c r="J41" s="35"/>
       <x:c r="K41" s="3"/>
       <x:c r="L41" s="3"/>
-      <x:c r="M41" s="36"/>
+      <x:c r="M41" s="35"/>
       <x:c r="N41" s="3"/>
       <x:c r="O41" s="3"/>
-      <x:c r="P41" s="36"/>
+      <x:c r="P41" s="35"/>
       <x:c r="Q41" s="3"/>
       <x:c r="R41" s="3"/>
-      <x:c r="S41" s="36"/>
+      <x:c r="S41" s="35"/>
       <x:c r="T41" s="3"/>
       <x:c r="U41" s="3"/>
-      <x:c r="V41" s="36"/>
+      <x:c r="V41" s="35"/>
       <x:c r="W41" s="3"/>
       <x:c r="X41" s="3"/>
-      <x:c r="Y41" s="36"/>
+      <x:c r="Y41" s="35"/>
       <x:c r="Z41" s="3"/>
       <x:c r="AA41" s="3"/>
-      <x:c r="AB41" s="36"/>
+      <x:c r="AB41" s="35"/>
       <x:c r="AC41" s="3"/>
       <x:c r="AD41" s="3"/>
-      <x:c r="AE41" s="36"/>
+      <x:c r="AE41" s="35"/>
       <x:c r="AF41" s="3"/>
       <x:c r="AG41" s="3"/>
-      <x:c r="AH41" s="36"/>
+      <x:c r="AH41" s="35"/>
       <x:c r="AI41" s="3"/>
       <x:c r="AJ41" s="3"/>
-      <x:c r="AK41" s="36"/>
+      <x:c r="AK41" s="35"/>
       <x:c r="AL41" s="3"/>
       <x:c r="AM41" s="3"/>
-      <x:c r="AN41" s="36"/>
+      <x:c r="AN41" s="35"/>
       <x:c r="AO41" s="3"/>
       <x:c r="AP41" s="3"/>
-      <x:c r="AQ41" s="36"/>
+      <x:c r="AQ41" s="35"/>
       <x:c r="AR41" s="3"/>
       <x:c r="AS41" s="3"/>
-      <x:c r="AT41" s="36"/>
+      <x:c r="AT41" s="35"/>
       <x:c r="AU41" s="3"/>
       <x:c r="AV41" s="3"/>
-      <x:c r="AW41" s="36"/>
+      <x:c r="AW41" s="35"/>
       <x:c r="AX41" s="3"/>
       <x:c r="AY41" s="3"/>
-      <x:c r="AZ41" s="36"/>
+      <x:c r="AZ41" s="35"/>
       <x:c r="BA41" s="3"/>
       <x:c r="BB41" s="3"/>
       <x:c r="BC41" s="3"/>
@@ -69312,7 +69602,7 @@
     <x:mergeCell ref="AA22:AK29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <x:pageMargins left="0.82666665315628052" right="0.2361111044883728" top="0.74791663885116577" bottom="0.35430556535720825" header="0" footer="0"/>
+  <x:pageMargins left="0.82652777433395386" right="0.23597222566604614" top="0.74777776002883911" bottom="0.35430556535720825" header="0" footer="0"/>
   <x:pageSetup paperSize="8" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/사용자템플릿_엑셀_가공도.xlsx
+++ b/사용자템플릿_엑셀_가공도.xlsx
@@ -2036,7 +2036,11 @@
       <x:c r="A3" s="29"/>
       <x:c r="B3" s="30"/>
       <x:c r="C3" s="30"/>
-      <x:c r="D3" s="22"/>
+      <x:c r="D3" s="22" t="inlineStr">
+        <x:is>
+          <x:t>{View_1}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E3" s="22"/>
       <x:c r="F3" s="22"/>
       <x:c r="G3" s="22"/>
@@ -2053,7 +2057,11 @@
       <x:c r="R3" s="22"/>
       <x:c r="S3" s="22"/>
       <x:c r="T3" s="9"/>
-      <x:c r="U3" s="22"/>
+      <x:c r="U3" s="22" t="inlineStr">
+        <x:is>
+          <x:t>{View_2}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="V3" s="22"/>
       <x:c r="W3" s="22"/>
       <x:c r="X3" s="22"/>
@@ -3911,7 +3919,11 @@
       <x:c r="A25" s="5"/>
       <x:c r="B25" s="9"/>
       <x:c r="C25" s="9"/>
-      <x:c r="D25" s="22"/>
+      <x:c r="D25" s="22" t="inlineStr">
+        <x:is>
+          <x:t>{View_3}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E25" s="22"/>
       <x:c r="F25" s="22"/>
       <x:c r="G25" s="22"/>
@@ -3928,7 +3940,11 @@
       <x:c r="R25" s="22"/>
       <x:c r="S25" s="22"/>
       <x:c r="T25" s="9"/>
-      <x:c r="U25" s="22"/>
+      <x:c r="U25" s="22" t="inlineStr">
+        <x:is>
+          <x:t>{View_4}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="V25" s="22"/>
       <x:c r="W25" s="22"/>
       <x:c r="X25" s="22"/>

--- a/사용자템플릿_엑셀_가공도.xlsx
+++ b/사용자템플릿_엑셀_가공도.xlsx
@@ -1935,8 +1935,10 @@
       <x:c r="AK1" s="4"/>
       <x:c r="AL1" s="31"/>
       <x:c r="AM1" s="31"/>
-      <x:c r="AN1" s="39" t="s">
-        <x:v>137</x:v>
+      <x:c r="AN1" s="39" t="inlineStr">
+        <x:is>
+          <x:t>BOM TABLE</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO1" s="40"/>
       <x:c r="AP1" s="40"/>
@@ -1969,7 +1971,11 @@
       <x:c r="K2" s="9"/>
       <x:c r="L2" s="9"/>
       <x:c r="M2" s="9"/>
-      <x:c r="N2" s="70"/>
+      <x:c r="N2" s="70" t="inlineStr">
+        <x:is>
+          <x:t>{View_1}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="O2" s="70"/>
       <x:c r="P2" s="70"/>
       <x:c r="Q2" s="70"/>
@@ -1995,38 +2001,54 @@
       <x:c r="AK2" s="9"/>
       <x:c r="AL2" s="34"/>
       <x:c r="AM2" s="34"/>
-      <x:c r="AN2" s="55" t="s">
-        <x:v>19</x:v>
+      <x:c r="AN2" s="55" t="inlineStr">
+        <x:is>
+          <x:t>NO</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO2" s="56"/>
       <x:c r="AP2" s="57"/>
-      <x:c r="AQ2" s="15" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="AR2" s="30" t="s">
-        <x:v>124</x:v>
+      <x:c r="AQ2" s="15" t="inlineStr">
+        <x:is>
+          <x:t>ITEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR2" s="30" t="inlineStr">
+        <x:is>
+          <x:t>MATERIAL</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS2" s="31"/>
       <x:c r="AT2" s="32"/>
-      <x:c r="AU2" s="42" t="s">
-        <x:v>8</x:v>
+      <x:c r="AU2" s="42" t="inlineStr">
+        <x:is>
+          <x:t>SIZE</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV2" s="42"/>
       <x:c r="AW2" s="42"/>
-      <x:c r="AX2" s="55" t="s">
-        <x:v>17</x:v>
+      <x:c r="AX2" s="55" t="inlineStr">
+        <x:is>
+          <x:t>Q'TY</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY2" s="57"/>
-      <x:c r="AZ2" s="42" t="s">
-        <x:v>16</x:v>
+      <x:c r="AZ2" s="42" t="inlineStr">
+        <x:is>
+          <x:t>T/W</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA2" s="42"/>
       <x:c r="BB2" s="42"/>
-      <x:c r="BC2" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="BD2" s="16" t="s">
-        <x:v>18</x:v>
+      <x:c r="BC2" s="16" t="inlineStr">
+        <x:is>
+          <x:t>MA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD2" s="16" t="inlineStr">
+        <x:is>
+          <x:t>FA</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:56" ht="17.149999999999999" customHeight="1">
@@ -2069,38 +2091,54 @@
       <x:c r="AK3" s="21"/>
       <x:c r="AL3" s="34"/>
       <x:c r="AM3" s="34"/>
-      <x:c r="AN3" s="58" t="s">
-        <x:v>94</x:v>
+      <x:c r="AN3" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_10}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO3" s="59"/>
       <x:c r="AP3" s="60"/>
-      <x:c r="AQ3" s="13" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="AR3" s="58" t="s">
-        <x:v>104</x:v>
+      <x:c r="AQ3" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_25}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR3" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_40}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS3" s="72"/>
       <x:c r="AT3" s="73"/>
-      <x:c r="AU3" s="59" t="s">
-        <x:v>23</x:v>
+      <x:c r="AU3" s="59" t="inlineStr">
+        <x:is>
+          <x:t>{Input_55}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV3" s="65"/>
       <x:c r="AW3" s="65"/>
-      <x:c r="AX3" s="47" t="s">
-        <x:v>122</x:v>
+      <x:c r="AX3" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_70}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY3" s="54"/>
-      <x:c r="AZ3" s="67" t="s">
-        <x:v>2</x:v>
+      <x:c r="AZ3" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_85}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA3" s="68"/>
       <x:c r="BB3" s="68"/>
-      <x:c r="BC3" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="BD3" s="11" t="s">
-        <x:v>123</x:v>
+      <x:c r="BC3" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_100}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD3" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_115}</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:81" ht="17.149999999999999" customHeight="1">
@@ -2143,38 +2181,54 @@
       <x:c r="AK4" s="21"/>
       <x:c r="AL4" s="34"/>
       <x:c r="AM4" s="34"/>
-      <x:c r="AN4" s="61" t="s">
-        <x:v>115</x:v>
+      <x:c r="AN4" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_11}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO4" s="62"/>
       <x:c r="AP4" s="63"/>
-      <x:c r="AQ4" s="24" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AR4" s="44" t="s">
-        <x:v>37</x:v>
+      <x:c r="AQ4" s="24" t="inlineStr">
+        <x:is>
+          <x:t>{Input_26}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR4" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_41}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS4" s="45"/>
       <x:c r="AT4" s="46"/>
-      <x:c r="AU4" s="62" t="s">
-        <x:v>65</x:v>
+      <x:c r="AU4" s="62" t="inlineStr">
+        <x:is>
+          <x:t>{Input_56}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV4" s="66"/>
       <x:c r="AW4" s="66"/>
-      <x:c r="AX4" s="44" t="s">
-        <x:v>103</x:v>
+      <x:c r="AX4" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_71}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY4" s="46"/>
-      <x:c r="AZ4" s="69" t="s">
-        <x:v>129</x:v>
+      <x:c r="AZ4" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_86}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA4" s="70"/>
       <x:c r="BB4" s="70"/>
-      <x:c r="BC4" s="17" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="BD4" s="17" t="s">
-        <x:v>41</x:v>
+      <x:c r="BC4" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_101}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD4" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_116}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM4" s="21"/>
       <x:c r="BN4" s="23"/>
@@ -2196,7 +2250,11 @@
     </x:row>
     <x:row r="5" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A5" s="5"/>
-      <x:c r="B5" s="70"/>
+      <x:c r="B5" s="70" t="inlineStr">
+        <x:is>
+          <x:t>1. {Input_5}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C5" s="70"/>
       <x:c r="D5" s="70"/>
       <x:c r="E5" s="70"/>
@@ -2234,38 +2292,54 @@
       <x:c r="AK5" s="21"/>
       <x:c r="AL5" s="34"/>
       <x:c r="AM5" s="34"/>
-      <x:c r="AN5" s="58" t="s">
-        <x:v>86</x:v>
+      <x:c r="AN5" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_12}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO5" s="59"/>
       <x:c r="AP5" s="60"/>
-      <x:c r="AQ5" s="13" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="AR5" s="47" t="s">
-        <x:v>29</x:v>
+      <x:c r="AQ5" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_27}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR5" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_42}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS5" s="48"/>
       <x:c r="AT5" s="49"/>
-      <x:c r="AU5" s="67" t="s">
-        <x:v>45</x:v>
+      <x:c r="AU5" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_57}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV5" s="68"/>
       <x:c r="AW5" s="68"/>
-      <x:c r="AX5" s="47" t="s">
-        <x:v>130</x:v>
+      <x:c r="AX5" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_72}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY5" s="49"/>
-      <x:c r="AZ5" s="67" t="s">
-        <x:v>141</x:v>
+      <x:c r="AZ5" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_87}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA5" s="68"/>
       <x:c r="BB5" s="68"/>
-      <x:c r="BC5" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="BD5" s="11" t="s">
-        <x:v>112</x:v>
+      <x:c r="BC5" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_102}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD5" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_117}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM5" s="23"/>
       <x:c r="BN5" s="23"/>
@@ -2325,38 +2399,54 @@
       <x:c r="AK6" s="21"/>
       <x:c r="AL6" s="9"/>
       <x:c r="AM6" s="9"/>
-      <x:c r="AN6" s="61" t="s">
-        <x:v>139</x:v>
+      <x:c r="AN6" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_13}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO6" s="62"/>
       <x:c r="AP6" s="63"/>
-      <x:c r="AQ6" s="18" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AR6" s="44" t="s">
-        <x:v>53</x:v>
+      <x:c r="AQ6" s="18" t="inlineStr">
+        <x:is>
+          <x:t>{Input_28}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR6" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_43}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS6" s="45"/>
       <x:c r="AT6" s="46"/>
-      <x:c r="AU6" s="69" t="s">
-        <x:v>58</x:v>
+      <x:c r="AU6" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_58}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV6" s="70"/>
       <x:c r="AW6" s="70"/>
-      <x:c r="AX6" s="44" t="s">
-        <x:v>138</x:v>
+      <x:c r="AX6" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_73}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY6" s="46"/>
-      <x:c r="AZ6" s="69" t="s">
-        <x:v>25</x:v>
+      <x:c r="AZ6" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_88}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA6" s="70"/>
       <x:c r="BB6" s="70"/>
-      <x:c r="BC6" s="17" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="BD6" s="17" t="s">
-        <x:v>39</x:v>
+      <x:c r="BC6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_103}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD6" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_118}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM6" s="23"/>
       <x:c r="BN6" s="23"/>
@@ -2416,38 +2506,54 @@
       <x:c r="AK7" s="21"/>
       <x:c r="AL7" s="9"/>
       <x:c r="AM7" s="9"/>
-      <x:c r="AN7" s="58" t="s">
-        <x:v>91</x:v>
+      <x:c r="AN7" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_14}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO7" s="59"/>
       <x:c r="AP7" s="60"/>
-      <x:c r="AQ7" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="AR7" s="47" t="s">
-        <x:v>60</x:v>
+      <x:c r="AQ7" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_29}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR7" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_44}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS7" s="48"/>
       <x:c r="AT7" s="49"/>
-      <x:c r="AU7" s="67" t="s">
-        <x:v>95</x:v>
+      <x:c r="AU7" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_59}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV7" s="68"/>
       <x:c r="AW7" s="68"/>
-      <x:c r="AX7" s="47" t="s">
-        <x:v>96</x:v>
+      <x:c r="AX7" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_74}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY7" s="49"/>
-      <x:c r="AZ7" s="67" t="s">
-        <x:v>133</x:v>
+      <x:c r="AZ7" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_89}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA7" s="68"/>
       <x:c r="BB7" s="68"/>
-      <x:c r="BC7" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="BD7" s="11" t="s">
-        <x:v>3</x:v>
+      <x:c r="BC7" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_104}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD7" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_119}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM7" s="23"/>
       <x:c r="BN7" s="23"/>
@@ -2506,38 +2612,54 @@
       <x:c r="AK8" s="21"/>
       <x:c r="AL8" s="9"/>
       <x:c r="AM8" s="9"/>
-      <x:c r="AN8" s="61" t="s">
-        <x:v>117</x:v>
+      <x:c r="AN8" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_15}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO8" s="62"/>
       <x:c r="AP8" s="63"/>
-      <x:c r="AQ8" s="18" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AR8" s="44" t="s">
-        <x:v>42</x:v>
+      <x:c r="AQ8" s="18" t="inlineStr">
+        <x:is>
+          <x:t>{Input_30}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR8" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_45}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS8" s="45"/>
       <x:c r="AT8" s="46"/>
-      <x:c r="AU8" s="69" t="s">
-        <x:v>59</x:v>
+      <x:c r="AU8" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_60}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV8" s="70"/>
       <x:c r="AW8" s="70"/>
-      <x:c r="AX8" s="44" t="s">
-        <x:v>34</x:v>
+      <x:c r="AX8" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_75}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY8" s="46"/>
-      <x:c r="AZ8" s="69" t="s">
-        <x:v>63</x:v>
+      <x:c r="AZ8" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_90}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA8" s="70"/>
       <x:c r="BB8" s="70"/>
-      <x:c r="BC8" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="BD8" s="17" t="s">
-        <x:v>44</x:v>
+      <x:c r="BC8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_105}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD8" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_120}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM8" s="23"/>
       <x:c r="BN8" s="23"/>
@@ -2597,38 +2719,54 @@
       <x:c r="AK9" s="21"/>
       <x:c r="AL9" s="9"/>
       <x:c r="AM9" s="9"/>
-      <x:c r="AN9" s="58" t="s">
-        <x:v>92</x:v>
+      <x:c r="AN9" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_16}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO9" s="59"/>
       <x:c r="AP9" s="60"/>
-      <x:c r="AQ9" s="13" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="AR9" s="47" t="s">
-        <x:v>56</x:v>
+      <x:c r="AQ9" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_31}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR9" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_46}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS9" s="48"/>
       <x:c r="AT9" s="49"/>
-      <x:c r="AU9" s="67" t="s">
-        <x:v>35</x:v>
+      <x:c r="AU9" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_61}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV9" s="68"/>
       <x:c r="AW9" s="68"/>
-      <x:c r="AX9" s="47" t="s">
-        <x:v>73</x:v>
+      <x:c r="AX9" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_76}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY9" s="49"/>
-      <x:c r="AZ9" s="67" t="s">
-        <x:v>77</x:v>
+      <x:c r="AZ9" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_91}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA9" s="68"/>
       <x:c r="BB9" s="68"/>
-      <x:c r="BC9" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="BD9" s="11" t="s">
-        <x:v>79</x:v>
+      <x:c r="BC9" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_106}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD9" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_121}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM9" s="23"/>
       <x:c r="BN9" s="23"/>
@@ -2688,38 +2826,54 @@
       <x:c r="AK10" s="21"/>
       <x:c r="AL10" s="9"/>
       <x:c r="AM10" s="9"/>
-      <x:c r="AN10" s="61" t="s">
-        <x:v>100</x:v>
+      <x:c r="AN10" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_17}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO10" s="62"/>
       <x:c r="AP10" s="63"/>
-      <x:c r="AQ10" s="18" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AR10" s="44" t="s">
-        <x:v>67</x:v>
+      <x:c r="AQ10" s="18" t="inlineStr">
+        <x:is>
+          <x:t>{Input_32}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR10" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_47}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS10" s="45"/>
       <x:c r="AT10" s="46"/>
-      <x:c r="AU10" s="69" t="s">
-        <x:v>26</x:v>
+      <x:c r="AU10" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_62}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV10" s="70"/>
       <x:c r="AW10" s="70"/>
-      <x:c r="AX10" s="44" t="s">
-        <x:v>46</x:v>
+      <x:c r="AX10" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_77}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY10" s="46"/>
-      <x:c r="AZ10" s="69" t="s">
-        <x:v>84</x:v>
+      <x:c r="AZ10" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_92}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA10" s="70"/>
       <x:c r="BB10" s="70"/>
-      <x:c r="BC10" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BD10" s="17" t="s">
-        <x:v>78</x:v>
+      <x:c r="BC10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_107}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_122}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM10" s="23"/>
       <x:c r="BN10" s="23"/>
@@ -2753,7 +2907,11 @@
       <x:c r="K11" s="21"/>
       <x:c r="L11" s="21"/>
       <x:c r="M11" s="21"/>
-      <x:c r="N11" s="70"/>
+      <x:c r="N11" s="70" t="inlineStr">
+        <x:is>
+          <x:t>{View_2}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="O11" s="70"/>
       <x:c r="P11" s="70"/>
       <x:c r="Q11" s="70"/>
@@ -2779,38 +2937,54 @@
       <x:c r="AK11" s="21"/>
       <x:c r="AL11" s="9"/>
       <x:c r="AM11" s="9"/>
-      <x:c r="AN11" s="58" t="s">
-        <x:v>71</x:v>
+      <x:c r="AN11" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_18}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO11" s="59"/>
       <x:c r="AP11" s="60"/>
-      <x:c r="AQ11" s="13" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="AR11" s="47" t="s">
-        <x:v>40</x:v>
+      <x:c r="AQ11" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_33}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR11" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_48}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS11" s="48"/>
       <x:c r="AT11" s="49"/>
-      <x:c r="AU11" s="67" t="s">
-        <x:v>54</x:v>
+      <x:c r="AU11" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_63}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV11" s="68"/>
       <x:c r="AW11" s="68"/>
-      <x:c r="AX11" s="47" t="s">
-        <x:v>57</x:v>
+      <x:c r="AX11" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_78}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY11" s="49"/>
-      <x:c r="AZ11" s="67" t="s">
-        <x:v>75</x:v>
+      <x:c r="AZ11" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_93}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA11" s="68"/>
       <x:c r="BB11" s="68"/>
-      <x:c r="BC11" s="11" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="BD11" s="11" t="s">
-        <x:v>107</x:v>
+      <x:c r="BC11" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_108}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD11" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_123}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM11" s="45"/>
       <x:c r="BN11" s="45"/>
@@ -2870,38 +3044,54 @@
       <x:c r="AK12" s="21"/>
       <x:c r="AL12" s="9"/>
       <x:c r="AM12" s="9"/>
-      <x:c r="AN12" s="61" t="s">
-        <x:v>61</x:v>
+      <x:c r="AN12" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_19}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO12" s="62"/>
       <x:c r="AP12" s="63"/>
-      <x:c r="AQ12" s="18" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AR12" s="44" t="s">
-        <x:v>83</x:v>
+      <x:c r="AQ12" s="18" t="inlineStr">
+        <x:is>
+          <x:t>{Input_34}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR12" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_49}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS12" s="45"/>
       <x:c r="AT12" s="46"/>
-      <x:c r="AU12" s="69" t="s">
-        <x:v>55</x:v>
+      <x:c r="AU12" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_64}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV12" s="70"/>
       <x:c r="AW12" s="70"/>
-      <x:c r="AX12" s="44" t="s">
-        <x:v>106</x:v>
+      <x:c r="AX12" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_79}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY12" s="46"/>
-      <x:c r="AZ12" s="69" t="s">
-        <x:v>69</x:v>
+      <x:c r="AZ12" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_94}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA12" s="70"/>
       <x:c r="BB12" s="70"/>
-      <x:c r="BC12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="BD12" s="17" t="s">
-        <x:v>33</x:v>
+      <x:c r="BC12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_109}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_124}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM12" s="23"/>
       <x:c r="BN12" s="23"/>
@@ -2961,38 +3151,54 @@
       <x:c r="AK13" s="21"/>
       <x:c r="AL13" s="9"/>
       <x:c r="AM13" s="9"/>
-      <x:c r="AN13" s="58" t="s">
-        <x:v>87</x:v>
+      <x:c r="AN13" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_20}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO13" s="59"/>
       <x:c r="AP13" s="60"/>
-      <x:c r="AQ13" s="13" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="AR13" s="47" t="s">
-        <x:v>97</x:v>
+      <x:c r="AQ13" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_35}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR13" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_50}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS13" s="48"/>
       <x:c r="AT13" s="49"/>
-      <x:c r="AU13" s="67" t="s">
-        <x:v>89</x:v>
+      <x:c r="AU13" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_65}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV13" s="68"/>
       <x:c r="AW13" s="68"/>
-      <x:c r="AX13" s="47" t="s">
-        <x:v>105</x:v>
+      <x:c r="AX13" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_80}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY13" s="49"/>
-      <x:c r="AZ13" s="67" t="s">
-        <x:v>113</x:v>
+      <x:c r="AZ13" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_95}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA13" s="68"/>
       <x:c r="BB13" s="68"/>
-      <x:c r="BC13" s="11" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="BD13" s="11" t="s">
-        <x:v>101</x:v>
+      <x:c r="BC13" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_110}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD13" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_125}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM13" s="23"/>
       <x:c r="BN13" s="23"/>
@@ -3014,7 +3220,11 @@
     </x:row>
     <x:row r="14" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A14" s="5"/>
-      <x:c r="B14" s="70"/>
+      <x:c r="B14" s="70" t="inlineStr">
+        <x:is>
+          <x:t>2. {Input_6}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C14" s="70"/>
       <x:c r="D14" s="70"/>
       <x:c r="E14" s="70"/>
@@ -3052,38 +3262,54 @@
       <x:c r="AK14" s="21"/>
       <x:c r="AL14" s="9"/>
       <x:c r="AM14" s="9"/>
-      <x:c r="AN14" s="61" t="s">
-        <x:v>70</x:v>
+      <x:c r="AN14" s="61" t="inlineStr">
+        <x:is>
+          <x:t>{Input_21}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO14" s="62"/>
       <x:c r="AP14" s="63"/>
-      <x:c r="AQ14" s="18" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AR14" s="44" t="s">
-        <x:v>66</x:v>
+      <x:c r="AQ14" s="18" t="inlineStr">
+        <x:is>
+          <x:t>{Input_36}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR14" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_51}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS14" s="45"/>
       <x:c r="AT14" s="46"/>
-      <x:c r="AU14" s="69" t="s">
-        <x:v>102</x:v>
+      <x:c r="AU14" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_66}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV14" s="70"/>
       <x:c r="AW14" s="70"/>
-      <x:c r="AX14" s="44" t="s">
-        <x:v>74</x:v>
+      <x:c r="AX14" s="44" t="inlineStr">
+        <x:is>
+          <x:t>{Input_81}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY14" s="46"/>
-      <x:c r="AZ14" s="69" t="s">
-        <x:v>116</x:v>
+      <x:c r="AZ14" s="69" t="inlineStr">
+        <x:is>
+          <x:t>{Input_96}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA14" s="70"/>
       <x:c r="BB14" s="70"/>
-      <x:c r="BC14" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="BD14" s="17" t="s">
-        <x:v>114</x:v>
+      <x:c r="BC14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_111}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD14" s="17" t="inlineStr">
+        <x:is>
+          <x:t>{Input_126}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM14" s="23"/>
       <x:c r="BN14" s="23"/>
@@ -3143,38 +3369,54 @@
       <x:c r="AK15" s="21"/>
       <x:c r="AL15" s="9"/>
       <x:c r="AM15" s="9"/>
-      <x:c r="AN15" s="58" t="s">
-        <x:v>140</x:v>
+      <x:c r="AN15" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_22}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO15" s="59"/>
       <x:c r="AP15" s="64"/>
-      <x:c r="AQ15" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AR15" s="50" t="s">
-        <x:v>49</x:v>
+      <x:c r="AQ15" s="14" t="inlineStr">
+        <x:is>
+          <x:t>{Input_37}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR15" s="50" t="inlineStr">
+        <x:is>
+          <x:t>{Input_52}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS15" s="51"/>
       <x:c r="AT15" s="52"/>
-      <x:c r="AU15" s="71" t="s">
-        <x:v>22</x:v>
+      <x:c r="AU15" s="71" t="inlineStr">
+        <x:is>
+          <x:t>{Input_67}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV15" s="68"/>
       <x:c r="AW15" s="68"/>
-      <x:c r="AX15" s="50" t="s">
-        <x:v>80</x:v>
+      <x:c r="AX15" s="50" t="inlineStr">
+        <x:is>
+          <x:t>{Input_82}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY15" s="52"/>
-      <x:c r="AZ15" s="71" t="s">
-        <x:v>121</x:v>
+      <x:c r="AZ15" s="71" t="inlineStr">
+        <x:is>
+          <x:t>{Input_97}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA15" s="68"/>
       <x:c r="BB15" s="68"/>
-      <x:c r="BC15" s="12" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="BD15" s="11" t="s">
-        <x:v>128</x:v>
+      <x:c r="BC15" s="12" t="inlineStr">
+        <x:is>
+          <x:t>{Input_112}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD15" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_127}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM15" s="23"/>
       <x:c r="BN15" s="23"/>
@@ -3234,38 +3476,54 @@
       <x:c r="AK16" s="21"/>
       <x:c r="AL16" s="9"/>
       <x:c r="AM16" s="9"/>
-      <x:c r="AN16" s="58" t="s">
-        <x:v>1</x:v>
+      <x:c r="AN16" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_23}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO16" s="59"/>
       <x:c r="AP16" s="60"/>
-      <x:c r="AQ16" s="13" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="AR16" s="47" t="s">
-        <x:v>36</x:v>
+      <x:c r="AQ16" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_38}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR16" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_53}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS16" s="53"/>
       <x:c r="AT16" s="54"/>
-      <x:c r="AU16" s="67" t="s">
-        <x:v>47</x:v>
+      <x:c r="AU16" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_68}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV16" s="68"/>
       <x:c r="AW16" s="68"/>
-      <x:c r="AX16" s="47" t="s">
-        <x:v>145</x:v>
+      <x:c r="AX16" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_83}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY16" s="54"/>
-      <x:c r="AZ16" s="67" t="s">
-        <x:v>134</x:v>
+      <x:c r="AZ16" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_98}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA16" s="68"/>
       <x:c r="BB16" s="68"/>
-      <x:c r="BC16" s="11" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="BD16" s="11" t="s">
-        <x:v>118</x:v>
+      <x:c r="BC16" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_113}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD16" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_128}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM16" s="23"/>
       <x:c r="BN16" s="23"/>
@@ -3325,38 +3583,54 @@
       <x:c r="AK17" s="21"/>
       <x:c r="AL17" s="9"/>
       <x:c r="AM17" s="9"/>
-      <x:c r="AN17" s="58" t="s">
-        <x:v>28</x:v>
+      <x:c r="AN17" s="58" t="inlineStr">
+        <x:is>
+          <x:t>{Input_24}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AO17" s="59"/>
       <x:c r="AP17" s="60"/>
-      <x:c r="AQ17" s="13" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="AR17" s="47" t="s">
-        <x:v>68</x:v>
+      <x:c r="AQ17" s="13" t="inlineStr">
+        <x:is>
+          <x:t>{Input_39}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AR17" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_54}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AS17" s="53"/>
       <x:c r="AT17" s="54"/>
-      <x:c r="AU17" s="67" t="s">
-        <x:v>24</x:v>
+      <x:c r="AU17" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_69}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AV17" s="68"/>
       <x:c r="AW17" s="68"/>
-      <x:c r="AX17" s="47" t="s">
-        <x:v>30</x:v>
+      <x:c r="AX17" s="47" t="inlineStr">
+        <x:is>
+          <x:t>{Input_84}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AY17" s="54"/>
-      <x:c r="AZ17" s="67" t="s">
-        <x:v>0</x:v>
+      <x:c r="AZ17" s="67" t="inlineStr">
+        <x:is>
+          <x:t>{Input_99}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BA17" s="68"/>
       <x:c r="BB17" s="68"/>
-      <x:c r="BC17" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="BD17" s="11" t="s">
-        <x:v>119</x:v>
+      <x:c r="BC17" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_114}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BD17" s="11" t="inlineStr">
+        <x:is>
+          <x:t>{Input_129}</x:t>
+        </x:is>
       </x:c>
       <x:c r="BM17" s="23"/>
       <x:c r="BN17" s="23"/>
@@ -3540,7 +3814,11 @@
       <x:c r="K20" s="21"/>
       <x:c r="L20" s="21"/>
       <x:c r="M20" s="21"/>
-      <x:c r="N20" s="70"/>
+      <x:c r="N20" s="70" t="inlineStr">
+        <x:is>
+          <x:t>{View_3}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="O20" s="70"/>
       <x:c r="P20" s="70"/>
       <x:c r="Q20" s="70"/>
@@ -3753,7 +4031,11 @@
     </x:row>
     <x:row r="23" spans="1:83">
       <x:c r="A23" s="5"/>
-      <x:c r="B23" s="70"/>
+      <x:c r="B23" s="70" t="inlineStr">
+        <x:is>
+          <x:t>3. {Input_7}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C23" s="70"/>
       <x:c r="D23" s="70"/>
       <x:c r="E23" s="70"/>
@@ -4150,7 +4432,11 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
       <x:c r="M29" s="21"/>
-      <x:c r="N29" s="70"/>
+      <x:c r="N29" s="70" t="inlineStr">
+        <x:is>
+          <x:t>{View_4}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="O29" s="70"/>
       <x:c r="P29" s="70"/>
       <x:c r="Q29" s="70"/>
@@ -4312,7 +4598,11 @@
     </x:row>
     <x:row r="32" spans="1:56">
       <x:c r="A32" s="5"/>
-      <x:c r="B32" s="70"/>
+      <x:c r="B32" s="70" t="inlineStr">
+        <x:is>
+          <x:t>4. {Input_8}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C32" s="70"/>
       <x:c r="D32" s="70"/>
       <x:c r="E32" s="70"/>
@@ -4666,8 +4956,10 @@
       <x:c r="AQ37" s="31"/>
       <x:c r="AR37" s="31"/>
       <x:c r="AS37" s="32"/>
-      <x:c r="AT37" s="30" t="s">
-        <x:v>62</x:v>
+      <x:c r="AT37" s="30" t="inlineStr">
+        <x:is>
+          <x:t>{Input_1}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AU37" s="31"/>
       <x:c r="AV37" s="31"/>
@@ -4694,7 +4986,11 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
       <x:c r="M38" s="21"/>
-      <x:c r="N38" s="70"/>
+      <x:c r="N38" s="70" t="inlineStr">
+        <x:is>
+          <x:t>{View_5}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="O38" s="70"/>
       <x:c r="P38" s="70"/>
       <x:c r="Q38" s="70"/>
@@ -4784,8 +5080,10 @@
       <x:c r="AQ39" s="34"/>
       <x:c r="AR39" s="34"/>
       <x:c r="AS39" s="35"/>
-      <x:c r="AT39" s="30" t="s">
-        <x:v>76</x:v>
+      <x:c r="AT39" s="30" t="inlineStr">
+        <x:is>
+          <x:t>{Input_2}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AU39" s="31"/>
       <x:c r="AV39" s="31"/>
@@ -4858,7 +5156,11 @@
     </x:row>
     <x:row r="41" spans="1:56">
       <x:c r="A41" s="5"/>
-      <x:c r="B41" s="70"/>
+      <x:c r="B41" s="70" t="inlineStr">
+        <x:is>
+          <x:t>5. {Input_9}</x:t>
+        </x:is>
+      </x:c>
       <x:c r="C41" s="70"/>
       <x:c r="D41" s="70"/>
       <x:c r="E41" s="70"/>
@@ -4904,8 +5206,10 @@
       <x:c r="AQ41" s="31"/>
       <x:c r="AR41" s="31"/>
       <x:c r="AS41" s="32"/>
-      <x:c r="AT41" s="30" t="s">
-        <x:v>99</x:v>
+      <x:c r="AT41" s="30" t="inlineStr">
+        <x:is>
+          <x:t>{Input_3}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AU41" s="31"/>
       <x:c r="AV41" s="31"/>

--- a/사용자템플릿_엑셀_가공도.xlsx
+++ b/사용자템플릿_엑셀_가공도.xlsx
@@ -19,444 +19,474 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+  <x:si>
+    <x:t>{Input_39}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_20}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_112}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_42}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_110}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_103}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_51}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_114}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_71}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_46}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T/W</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_18}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_118}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_96}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_69}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_55}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_35}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_78}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_47}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_23}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_36}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q'TY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Note:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHECKED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[no]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIZE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Image}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DP NO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRAWN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REV.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[code]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_66}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_31}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_81}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_33}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_21}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_16}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATERIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_106}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_80}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_19}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_83}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_67}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_105}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPROVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_92}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOM TABLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_77}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_54}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_38}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_13}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_99}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_50}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_24}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_98}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_108}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_57}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_40}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_72}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_52}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_58}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_84}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_37}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_100}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_116}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_45}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_87}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_15}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_41}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_85}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_115}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_12}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_76}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_27}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_75}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_48}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_88}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_70}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_101}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_30}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_22}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_43}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_59}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_10}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_25}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_86}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_14}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_26}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_68}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_53}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_44}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_11}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_34}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_119}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_29}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_65}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_117}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_60}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_73}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_107}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_97}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_74}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_111}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_102}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_89}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_32}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_3}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESCRIPTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_90}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAINT CODE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_123}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_121}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_95}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_122}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_91}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_64}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_104}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_120}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_109}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_62}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_61}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_28}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_56}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_63}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_82}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_49}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_94}</x:t>
+  </x:si>
   <x:si>
     <x:t>{Input_93}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_79}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_17}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_79}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_113}</x:t>
   </x:si>
   <x:si>
+    <x:t>{View_4}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_124}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_126}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_125}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_127}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_129}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_128}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_3}</x:t>
+  </x:si>
+  <x:si>
     <x:t>TAG NO. [text]</x:t>
   </x:si>
   <x:si>
-    <x:t>[no]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Note:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHECKED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIZE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Image}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DRAWN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DP NO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REV.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[code]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T/W</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_61}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_49}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_63}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_82}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_56}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_94}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_18}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_36}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_78}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_23}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_96}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_118}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_69}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_55}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_47}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_35}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_103}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_112}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_42}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_110}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_39}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_20}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_114}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_51}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_71}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_62}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_28}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_46}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_108}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_24}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_98}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_37}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_57}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_58}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_40}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_72}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_52}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_54}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_38}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_13}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_84}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_99}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_50}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_45}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_41}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_48}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_88}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_15}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_12}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_100}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_70}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_75}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_87}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_2}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_85}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_116}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_115}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_76}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_27}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_101}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_43}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_86}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_26}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_6}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_14}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_30}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_59}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_22}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_8}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_10}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_25}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_4}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_53}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_68}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_44}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_32}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_3}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_11}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_119}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_60}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_65}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_34}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_74}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_73}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_117}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_102}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_29}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_107}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_97}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_111}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_89}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_120}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_5}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_90}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_9}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_122}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_123}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_104}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_91}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_64}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_109}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METERIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESCRIPTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_95}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAINT CODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_121}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_80}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_66}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_19}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_31}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_83}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_92}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_21}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_105}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATERIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_67}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_7}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_16}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_81}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APPROVED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_33}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_106}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_77}</x:t>
+    <x:t>2. {Input_6}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. {Input_5}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. {Input_7}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. {Input_8}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. {Input_9}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_5}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1935,10 +1965,8 @@
       <x:c r="AK1" s="4"/>
       <x:c r="AL1" s="31"/>
       <x:c r="AM1" s="31"/>
-      <x:c r="AN1" s="39" t="inlineStr">
-        <x:is>
-          <x:t>BOM TABLE</x:t>
-        </x:is>
+      <x:c r="AN1" s="39" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO1" s="40"/>
       <x:c r="AP1" s="40"/>
@@ -1971,10 +1999,8 @@
       <x:c r="K2" s="9"/>
       <x:c r="L2" s="9"/>
       <x:c r="M2" s="9"/>
-      <x:c r="N2" s="70" t="inlineStr">
-        <x:is>
-          <x:t>{View_1}</x:t>
-        </x:is>
+      <x:c r="N2" s="70" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="70"/>
       <x:c r="P2" s="70"/>
@@ -2001,54 +2027,38 @@
       <x:c r="AK2" s="9"/>
       <x:c r="AL2" s="34"/>
       <x:c r="AM2" s="34"/>
-      <x:c r="AN2" s="55" t="inlineStr">
-        <x:is>
-          <x:t>NO</x:t>
-        </x:is>
+      <x:c r="AN2" s="55" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AO2" s="56"/>
       <x:c r="AP2" s="57"/>
-      <x:c r="AQ2" s="15" t="inlineStr">
-        <x:is>
-          <x:t>ITEM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR2" s="30" t="inlineStr">
-        <x:is>
-          <x:t>MATERIAL</x:t>
-        </x:is>
+      <x:c r="AQ2" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="AR2" s="30" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="AS2" s="31"/>
       <x:c r="AT2" s="32"/>
-      <x:c r="AU2" s="42" t="inlineStr">
-        <x:is>
-          <x:t>SIZE</x:t>
-        </x:is>
+      <x:c r="AU2" s="42" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AV2" s="42"/>
       <x:c r="AW2" s="42"/>
-      <x:c r="AX2" s="55" t="inlineStr">
-        <x:is>
-          <x:t>Q'TY</x:t>
-        </x:is>
+      <x:c r="AX2" s="55" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AY2" s="57"/>
-      <x:c r="AZ2" s="42" t="inlineStr">
-        <x:is>
-          <x:t>T/W</x:t>
-        </x:is>
+      <x:c r="AZ2" s="42" t="s">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BA2" s="42"/>
       <x:c r="BB2" s="42"/>
-      <x:c r="BC2" s="16" t="inlineStr">
-        <x:is>
-          <x:t>MA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD2" s="16" t="inlineStr">
-        <x:is>
-          <x:t>FA</x:t>
-        </x:is>
+      <x:c r="BC2" s="16" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="BD2" s="16" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:56" ht="17.149999999999999" customHeight="1">
@@ -2091,54 +2101,38 @@
       <x:c r="AK3" s="21"/>
       <x:c r="AL3" s="34"/>
       <x:c r="AM3" s="34"/>
-      <x:c r="AN3" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_10}</x:t>
-        </x:is>
+      <x:c r="AN3" s="58" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="AO3" s="59"/>
       <x:c r="AP3" s="60"/>
-      <x:c r="AQ3" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_25}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR3" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_40}</x:t>
-        </x:is>
+      <x:c r="AQ3" s="13" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="AR3" s="58" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AS3" s="72"/>
       <x:c r="AT3" s="73"/>
-      <x:c r="AU3" s="59" t="inlineStr">
-        <x:is>
-          <x:t>{Input_55}</x:t>
-        </x:is>
+      <x:c r="AU3" s="59" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AV3" s="65"/>
       <x:c r="AW3" s="65"/>
-      <x:c r="AX3" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_70}</x:t>
-        </x:is>
+      <x:c r="AX3" s="47" t="s">
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AY3" s="54"/>
-      <x:c r="AZ3" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_85}</x:t>
-        </x:is>
+      <x:c r="AZ3" s="67" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BA3" s="68"/>
       <x:c r="BB3" s="68"/>
-      <x:c r="BC3" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_100}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD3" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_115}</x:t>
-        </x:is>
+      <x:c r="BC3" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="BD3" s="11" t="s">
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:81" ht="17.149999999999999" customHeight="1">
@@ -2181,54 +2175,38 @@
       <x:c r="AK4" s="21"/>
       <x:c r="AL4" s="34"/>
       <x:c r="AM4" s="34"/>
-      <x:c r="AN4" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_11}</x:t>
-        </x:is>
+      <x:c r="AN4" s="61" t="s">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AO4" s="62"/>
       <x:c r="AP4" s="63"/>
-      <x:c r="AQ4" s="24" t="inlineStr">
-        <x:is>
-          <x:t>{Input_26}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR4" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_41}</x:t>
-        </x:is>
+      <x:c r="AQ4" s="24" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="AR4" s="44" t="s">
+        <x:v>77</x:v>
       </x:c>
       <x:c r="AS4" s="45"/>
       <x:c r="AT4" s="46"/>
-      <x:c r="AU4" s="62" t="inlineStr">
-        <x:is>
-          <x:t>{Input_56}</x:t>
-        </x:is>
+      <x:c r="AU4" s="62" t="s">
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AV4" s="66"/>
       <x:c r="AW4" s="66"/>
-      <x:c r="AX4" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_71}</x:t>
-        </x:is>
+      <x:c r="AX4" s="44" t="s">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AY4" s="46"/>
-      <x:c r="AZ4" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_86}</x:t>
-        </x:is>
+      <x:c r="AZ4" s="69" t="s">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BA4" s="70"/>
       <x:c r="BB4" s="70"/>
-      <x:c r="BC4" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_101}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD4" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_116}</x:t>
-        </x:is>
+      <x:c r="BC4" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="BD4" s="17" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BM4" s="21"/>
       <x:c r="BN4" s="23"/>
@@ -2250,10 +2228,8 @@
     </x:row>
     <x:row r="5" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A5" s="5"/>
-      <x:c r="B5" s="70" t="inlineStr">
-        <x:is>
-          <x:t>1. {Input_5}</x:t>
-        </x:is>
+      <x:c r="B5" s="70" t="s">
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C5" s="70"/>
       <x:c r="D5" s="70"/>
@@ -2292,54 +2268,38 @@
       <x:c r="AK5" s="21"/>
       <x:c r="AL5" s="34"/>
       <x:c r="AM5" s="34"/>
-      <x:c r="AN5" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_12}</x:t>
-        </x:is>
+      <x:c r="AN5" s="58" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AO5" s="59"/>
       <x:c r="AP5" s="60"/>
-      <x:c r="AQ5" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_27}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR5" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_42}</x:t>
-        </x:is>
+      <x:c r="AQ5" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="AR5" s="47" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AS5" s="48"/>
       <x:c r="AT5" s="49"/>
-      <x:c r="AU5" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_57}</x:t>
-        </x:is>
+      <x:c r="AU5" s="67" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AV5" s="68"/>
       <x:c r="AW5" s="68"/>
-      <x:c r="AX5" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_72}</x:t>
-        </x:is>
+      <x:c r="AX5" s="47" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AY5" s="49"/>
-      <x:c r="AZ5" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_87}</x:t>
-        </x:is>
+      <x:c r="AZ5" s="67" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BA5" s="68"/>
       <x:c r="BB5" s="68"/>
-      <x:c r="BC5" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_102}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD5" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_117}</x:t>
-        </x:is>
+      <x:c r="BC5" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="BD5" s="11" t="s">
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BM5" s="23"/>
       <x:c r="BN5" s="23"/>
@@ -2399,54 +2359,38 @@
       <x:c r="AK6" s="21"/>
       <x:c r="AL6" s="9"/>
       <x:c r="AM6" s="9"/>
-      <x:c r="AN6" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_13}</x:t>
-        </x:is>
+      <x:c r="AN6" s="61" t="s">
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO6" s="62"/>
       <x:c r="AP6" s="63"/>
-      <x:c r="AQ6" s="18" t="inlineStr">
-        <x:is>
-          <x:t>{Input_28}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR6" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_43}</x:t>
-        </x:is>
+      <x:c r="AQ6" s="18" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="AR6" s="44" t="s">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="AS6" s="45"/>
       <x:c r="AT6" s="46"/>
-      <x:c r="AU6" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_58}</x:t>
-        </x:is>
+      <x:c r="AU6" s="69" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AV6" s="70"/>
       <x:c r="AW6" s="70"/>
-      <x:c r="AX6" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_73}</x:t>
-        </x:is>
+      <x:c r="AX6" s="44" t="s">
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AY6" s="46"/>
-      <x:c r="AZ6" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_88}</x:t>
-        </x:is>
+      <x:c r="AZ6" s="69" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BA6" s="70"/>
       <x:c r="BB6" s="70"/>
-      <x:c r="BC6" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_103}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD6" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_118}</x:t>
-        </x:is>
+      <x:c r="BC6" s="17" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BD6" s="17" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BM6" s="23"/>
       <x:c r="BN6" s="23"/>
@@ -2506,54 +2450,38 @@
       <x:c r="AK7" s="21"/>
       <x:c r="AL7" s="9"/>
       <x:c r="AM7" s="9"/>
-      <x:c r="AN7" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_14}</x:t>
-        </x:is>
+      <x:c r="AN7" s="58" t="s">
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AO7" s="59"/>
       <x:c r="AP7" s="60"/>
-      <x:c r="AQ7" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_29}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR7" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_44}</x:t>
-        </x:is>
+      <x:c r="AQ7" s="13" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AR7" s="47" t="s">
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AS7" s="48"/>
       <x:c r="AT7" s="49"/>
-      <x:c r="AU7" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_59}</x:t>
-        </x:is>
+      <x:c r="AU7" s="67" t="s">
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AV7" s="68"/>
       <x:c r="AW7" s="68"/>
-      <x:c r="AX7" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_74}</x:t>
-        </x:is>
+      <x:c r="AX7" s="47" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AY7" s="49"/>
-      <x:c r="AZ7" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_89}</x:t>
-        </x:is>
+      <x:c r="AZ7" s="67" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BA7" s="68"/>
       <x:c r="BB7" s="68"/>
-      <x:c r="BC7" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_104}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD7" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_119}</x:t>
-        </x:is>
+      <x:c r="BC7" s="11" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="BD7" s="11" t="s">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="BM7" s="23"/>
       <x:c r="BN7" s="23"/>
@@ -2612,54 +2540,38 @@
       <x:c r="AK8" s="21"/>
       <x:c r="AL8" s="9"/>
       <x:c r="AM8" s="9"/>
-      <x:c r="AN8" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_15}</x:t>
-        </x:is>
+      <x:c r="AN8" s="61" t="s">
+        <x:v>76</x:v>
       </x:c>
       <x:c r="AO8" s="62"/>
       <x:c r="AP8" s="63"/>
-      <x:c r="AQ8" s="18" t="inlineStr">
-        <x:is>
-          <x:t>{Input_30}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR8" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_45}</x:t>
-        </x:is>
+      <x:c r="AQ8" s="18" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="AR8" s="44" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AS8" s="45"/>
       <x:c r="AT8" s="46"/>
-      <x:c r="AU8" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_60}</x:t>
-        </x:is>
+      <x:c r="AU8" s="69" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AV8" s="70"/>
       <x:c r="AW8" s="70"/>
-      <x:c r="AX8" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_75}</x:t>
-        </x:is>
+      <x:c r="AX8" s="44" t="s">
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AY8" s="46"/>
-      <x:c r="AZ8" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_90}</x:t>
-        </x:is>
+      <x:c r="AZ8" s="69" t="s">
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BA8" s="70"/>
       <x:c r="BB8" s="70"/>
-      <x:c r="BC8" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_105}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD8" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_120}</x:t>
-        </x:is>
+      <x:c r="BC8" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BD8" s="17" t="s">
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BM8" s="23"/>
       <x:c r="BN8" s="23"/>
@@ -2719,54 +2631,38 @@
       <x:c r="AK9" s="21"/>
       <x:c r="AL9" s="9"/>
       <x:c r="AM9" s="9"/>
-      <x:c r="AN9" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_16}</x:t>
-        </x:is>
+      <x:c r="AN9" s="58" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AO9" s="59"/>
       <x:c r="AP9" s="60"/>
-      <x:c r="AQ9" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_31}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR9" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_46}</x:t>
-        </x:is>
+      <x:c r="AQ9" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="AR9" s="47" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="AS9" s="48"/>
       <x:c r="AT9" s="49"/>
-      <x:c r="AU9" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_61}</x:t>
-        </x:is>
+      <x:c r="AU9" s="67" t="s">
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AV9" s="68"/>
       <x:c r="AW9" s="68"/>
-      <x:c r="AX9" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_76}</x:t>
-        </x:is>
+      <x:c r="AX9" s="47" t="s">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AY9" s="49"/>
-      <x:c r="AZ9" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_91}</x:t>
-        </x:is>
+      <x:c r="AZ9" s="67" t="s">
+        <x:v>123</x:v>
       </x:c>
       <x:c r="BA9" s="68"/>
       <x:c r="BB9" s="68"/>
-      <x:c r="BC9" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_106}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD9" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_121}</x:t>
-        </x:is>
+      <x:c r="BC9" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="BD9" s="11" t="s">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BM9" s="23"/>
       <x:c r="BN9" s="23"/>
@@ -2826,54 +2722,38 @@
       <x:c r="AK10" s="21"/>
       <x:c r="AL10" s="9"/>
       <x:c r="AM10" s="9"/>
-      <x:c r="AN10" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_17}</x:t>
-        </x:is>
+      <x:c r="AN10" s="61" t="s">
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AO10" s="62"/>
       <x:c r="AP10" s="63"/>
-      <x:c r="AQ10" s="18" t="inlineStr">
-        <x:is>
-          <x:t>{Input_32}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR10" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_47}</x:t>
-        </x:is>
+      <x:c r="AQ10" s="18" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AR10" s="44" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AS10" s="45"/>
       <x:c r="AT10" s="46"/>
-      <x:c r="AU10" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_62}</x:t>
-        </x:is>
+      <x:c r="AU10" s="69" t="s">
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AV10" s="70"/>
       <x:c r="AW10" s="70"/>
-      <x:c r="AX10" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_77}</x:t>
-        </x:is>
+      <x:c r="AX10" s="44" t="s">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AY10" s="46"/>
-      <x:c r="AZ10" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_92}</x:t>
-        </x:is>
+      <x:c r="AZ10" s="69" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA10" s="70"/>
       <x:c r="BB10" s="70"/>
-      <x:c r="BC10" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_107}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD10" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_122}</x:t>
-        </x:is>
+      <x:c r="BC10" s="17" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="BD10" s="17" t="s">
+        <x:v>122</x:v>
       </x:c>
       <x:c r="BM10" s="23"/>
       <x:c r="BN10" s="23"/>
@@ -2907,10 +2787,8 @@
       <x:c r="K11" s="21"/>
       <x:c r="L11" s="21"/>
       <x:c r="M11" s="21"/>
-      <x:c r="N11" s="70" t="inlineStr">
-        <x:is>
-          <x:t>{View_2}</x:t>
-        </x:is>
+      <x:c r="N11" s="70" t="s">
+        <x:v>141</x:v>
       </x:c>
       <x:c r="O11" s="70"/>
       <x:c r="P11" s="70"/>
@@ -2937,54 +2815,38 @@
       <x:c r="AK11" s="21"/>
       <x:c r="AL11" s="9"/>
       <x:c r="AM11" s="9"/>
-      <x:c r="AN11" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_18}</x:t>
-        </x:is>
+      <x:c r="AN11" s="58" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AO11" s="59"/>
       <x:c r="AP11" s="60"/>
-      <x:c r="AQ11" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_33}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR11" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_48}</x:t>
-        </x:is>
+      <x:c r="AQ11" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="AR11" s="47" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AS11" s="48"/>
       <x:c r="AT11" s="49"/>
-      <x:c r="AU11" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_63}</x:t>
-        </x:is>
+      <x:c r="AU11" s="67" t="s">
+        <x:v>132</x:v>
       </x:c>
       <x:c r="AV11" s="68"/>
       <x:c r="AW11" s="68"/>
-      <x:c r="AX11" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_78}</x:t>
-        </x:is>
+      <x:c r="AX11" s="47" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AY11" s="49"/>
-      <x:c r="AZ11" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_93}</x:t>
-        </x:is>
+      <x:c r="AZ11" s="67" t="s">
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BA11" s="68"/>
       <x:c r="BB11" s="68"/>
-      <x:c r="BC11" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_108}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD11" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_123}</x:t>
-        </x:is>
+      <x:c r="BC11" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="BD11" s="11" t="s">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="BM11" s="45"/>
       <x:c r="BN11" s="45"/>
@@ -3044,54 +2906,38 @@
       <x:c r="AK12" s="21"/>
       <x:c r="AL12" s="9"/>
       <x:c r="AM12" s="9"/>
-      <x:c r="AN12" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_19}</x:t>
-        </x:is>
+      <x:c r="AN12" s="61" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO12" s="62"/>
       <x:c r="AP12" s="63"/>
-      <x:c r="AQ12" s="18" t="inlineStr">
-        <x:is>
-          <x:t>{Input_34}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR12" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_49}</x:t>
-        </x:is>
+      <x:c r="AQ12" s="18" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AR12" s="44" t="s">
+        <x:v>134</x:v>
       </x:c>
       <x:c r="AS12" s="45"/>
       <x:c r="AT12" s="46"/>
-      <x:c r="AU12" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_64}</x:t>
-        </x:is>
+      <x:c r="AU12" s="69" t="s">
+        <x:v>124</x:v>
       </x:c>
       <x:c r="AV12" s="70"/>
       <x:c r="AW12" s="70"/>
-      <x:c r="AX12" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_79}</x:t>
-        </x:is>
+      <x:c r="AX12" s="44" t="s">
+        <x:v>137</x:v>
       </x:c>
       <x:c r="AY12" s="46"/>
-      <x:c r="AZ12" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_94}</x:t>
-        </x:is>
+      <x:c r="AZ12" s="69" t="s">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="BA12" s="70"/>
       <x:c r="BB12" s="70"/>
-      <x:c r="BC12" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_109}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD12" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_124}</x:t>
-        </x:is>
+      <x:c r="BC12" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="BD12" s="17" t="s">
+        <x:v>142</x:v>
       </x:c>
       <x:c r="BM12" s="23"/>
       <x:c r="BN12" s="23"/>
@@ -3151,54 +2997,38 @@
       <x:c r="AK13" s="21"/>
       <x:c r="AL13" s="9"/>
       <x:c r="AM13" s="9"/>
-      <x:c r="AN13" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_20}</x:t>
-        </x:is>
+      <x:c r="AN13" s="58" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO13" s="59"/>
       <x:c r="AP13" s="60"/>
-      <x:c r="AQ13" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_35}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR13" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_50}</x:t>
-        </x:is>
+      <x:c r="AQ13" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AR13" s="47" t="s">
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS13" s="48"/>
       <x:c r="AT13" s="49"/>
-      <x:c r="AU13" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_65}</x:t>
-        </x:is>
+      <x:c r="AU13" s="67" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="AV13" s="68"/>
       <x:c r="AW13" s="68"/>
-      <x:c r="AX13" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_80}</x:t>
-        </x:is>
+      <x:c r="AX13" s="47" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AY13" s="49"/>
-      <x:c r="AZ13" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_95}</x:t>
-        </x:is>
+      <x:c r="AZ13" s="67" t="s">
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BA13" s="68"/>
       <x:c r="BB13" s="68"/>
-      <x:c r="BC13" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_110}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD13" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_125}</x:t>
-        </x:is>
+      <x:c r="BC13" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="BD13" s="11" t="s">
+        <x:v>144</x:v>
       </x:c>
       <x:c r="BM13" s="23"/>
       <x:c r="BN13" s="23"/>
@@ -3220,10 +3050,8 @@
     </x:row>
     <x:row r="14" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A14" s="5"/>
-      <x:c r="B14" s="70" t="inlineStr">
-        <x:is>
-          <x:t>2. {Input_6}</x:t>
-        </x:is>
+      <x:c r="B14" s="70" t="s">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C14" s="70"/>
       <x:c r="D14" s="70"/>
@@ -3262,54 +3090,38 @@
       <x:c r="AK14" s="21"/>
       <x:c r="AL14" s="9"/>
       <x:c r="AM14" s="9"/>
-      <x:c r="AN14" s="61" t="inlineStr">
-        <x:is>
-          <x:t>{Input_21}</x:t>
-        </x:is>
+      <x:c r="AN14" s="61" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="AO14" s="62"/>
       <x:c r="AP14" s="63"/>
-      <x:c r="AQ14" s="18" t="inlineStr">
-        <x:is>
-          <x:t>{Input_36}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR14" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_51}</x:t>
-        </x:is>
+      <x:c r="AQ14" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="AR14" s="44" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AS14" s="45"/>
       <x:c r="AT14" s="46"/>
-      <x:c r="AU14" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_66}</x:t>
-        </x:is>
+      <x:c r="AU14" s="69" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AV14" s="70"/>
       <x:c r="AW14" s="70"/>
-      <x:c r="AX14" s="44" t="inlineStr">
-        <x:is>
-          <x:t>{Input_81}</x:t>
-        </x:is>
+      <x:c r="AX14" s="44" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="AY14" s="46"/>
-      <x:c r="AZ14" s="69" t="inlineStr">
-        <x:is>
-          <x:t>{Input_96}</x:t>
-        </x:is>
+      <x:c r="AZ14" s="69" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BA14" s="70"/>
       <x:c r="BB14" s="70"/>
-      <x:c r="BC14" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_111}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD14" s="17" t="inlineStr">
-        <x:is>
-          <x:t>{Input_126}</x:t>
-        </x:is>
+      <x:c r="BC14" s="17" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="BD14" s="17" t="s">
+        <x:v>143</x:v>
       </x:c>
       <x:c r="BM14" s="23"/>
       <x:c r="BN14" s="23"/>
@@ -3369,54 +3181,38 @@
       <x:c r="AK15" s="21"/>
       <x:c r="AL15" s="9"/>
       <x:c r="AM15" s="9"/>
-      <x:c r="AN15" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_22}</x:t>
-        </x:is>
+      <x:c r="AN15" s="58" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AO15" s="59"/>
       <x:c r="AP15" s="64"/>
-      <x:c r="AQ15" s="14" t="inlineStr">
-        <x:is>
-          <x:t>{Input_37}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR15" s="50" t="inlineStr">
-        <x:is>
-          <x:t>{Input_52}</x:t>
-        </x:is>
+      <x:c r="AQ15" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="AR15" s="50" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AS15" s="51"/>
       <x:c r="AT15" s="52"/>
-      <x:c r="AU15" s="71" t="inlineStr">
-        <x:is>
-          <x:t>{Input_67}</x:t>
-        </x:is>
+      <x:c r="AU15" s="71" t="s">
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AV15" s="68"/>
       <x:c r="AW15" s="68"/>
-      <x:c r="AX15" s="50" t="inlineStr">
-        <x:is>
-          <x:t>{Input_82}</x:t>
-        </x:is>
+      <x:c r="AX15" s="50" t="s">
+        <x:v>133</x:v>
       </x:c>
       <x:c r="AY15" s="52"/>
-      <x:c r="AZ15" s="71" t="inlineStr">
-        <x:is>
-          <x:t>{Input_97}</x:t>
-        </x:is>
+      <x:c r="AZ15" s="71" t="s">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA15" s="68"/>
       <x:c r="BB15" s="68"/>
-      <x:c r="BC15" s="12" t="inlineStr">
-        <x:is>
-          <x:t>{Input_112}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD15" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_127}</x:t>
-        </x:is>
+      <x:c r="BC15" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD15" s="11" t="s">
+        <x:v>145</x:v>
       </x:c>
       <x:c r="BM15" s="23"/>
       <x:c r="BN15" s="23"/>
@@ -3476,54 +3272,38 @@
       <x:c r="AK16" s="21"/>
       <x:c r="AL16" s="9"/>
       <x:c r="AM16" s="9"/>
-      <x:c r="AN16" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_23}</x:t>
-        </x:is>
+      <x:c r="AN16" s="58" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AO16" s="59"/>
       <x:c r="AP16" s="60"/>
-      <x:c r="AQ16" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_38}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR16" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_53}</x:t>
-        </x:is>
+      <x:c r="AQ16" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AR16" s="47" t="s">
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AS16" s="53"/>
       <x:c r="AT16" s="54"/>
-      <x:c r="AU16" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_68}</x:t>
-        </x:is>
+      <x:c r="AU16" s="67" t="s">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AV16" s="68"/>
       <x:c r="AW16" s="68"/>
-      <x:c r="AX16" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_83}</x:t>
-        </x:is>
+      <x:c r="AX16" s="47" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AY16" s="54"/>
-      <x:c r="AZ16" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_98}</x:t>
-        </x:is>
+      <x:c r="AZ16" s="67" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BA16" s="68"/>
       <x:c r="BB16" s="68"/>
-      <x:c r="BC16" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_113}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD16" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_128}</x:t>
-        </x:is>
+      <x:c r="BC16" s="11" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="BD16" s="11" t="s">
+        <x:v>147</x:v>
       </x:c>
       <x:c r="BM16" s="23"/>
       <x:c r="BN16" s="23"/>
@@ -3583,54 +3363,38 @@
       <x:c r="AK17" s="21"/>
       <x:c r="AL17" s="9"/>
       <x:c r="AM17" s="9"/>
-      <x:c r="AN17" s="58" t="inlineStr">
-        <x:is>
-          <x:t>{Input_24}</x:t>
-        </x:is>
+      <x:c r="AN17" s="58" t="s">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO17" s="59"/>
       <x:c r="AP17" s="60"/>
-      <x:c r="AQ17" s="13" t="inlineStr">
-        <x:is>
-          <x:t>{Input_39}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AR17" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_54}</x:t>
-        </x:is>
+      <x:c r="AQ17" s="13" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR17" s="47" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS17" s="53"/>
       <x:c r="AT17" s="54"/>
-      <x:c r="AU17" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_69}</x:t>
-        </x:is>
+      <x:c r="AU17" s="67" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AV17" s="68"/>
       <x:c r="AW17" s="68"/>
-      <x:c r="AX17" s="47" t="inlineStr">
-        <x:is>
-          <x:t>{Input_84}</x:t>
-        </x:is>
+      <x:c r="AX17" s="47" t="s">
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AY17" s="54"/>
-      <x:c r="AZ17" s="67" t="inlineStr">
-        <x:is>
-          <x:t>{Input_99}</x:t>
-        </x:is>
+      <x:c r="AZ17" s="67" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA17" s="68"/>
       <x:c r="BB17" s="68"/>
-      <x:c r="BC17" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_114}</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="BD17" s="11" t="inlineStr">
-        <x:is>
-          <x:t>{Input_129}</x:t>
-        </x:is>
+      <x:c r="BC17" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="BD17" s="11" t="s">
+        <x:v>146</x:v>
       </x:c>
       <x:c r="BM17" s="23"/>
       <x:c r="BN17" s="23"/>
@@ -3814,10 +3578,8 @@
       <x:c r="K20" s="21"/>
       <x:c r="L20" s="21"/>
       <x:c r="M20" s="21"/>
-      <x:c r="N20" s="70" t="inlineStr">
-        <x:is>
-          <x:t>{View_3}</x:t>
-        </x:is>
+      <x:c r="N20" s="70" t="s">
+        <x:v>148</x:v>
       </x:c>
       <x:c r="O20" s="70"/>
       <x:c r="P20" s="70"/>
@@ -4031,10 +3793,8 @@
     </x:row>
     <x:row r="23" spans="1:83">
       <x:c r="A23" s="5"/>
-      <x:c r="B23" s="70" t="inlineStr">
-        <x:is>
-          <x:t>3. {Input_7}</x:t>
-        </x:is>
+      <x:c r="B23" s="70" t="s">
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C23" s="70"/>
       <x:c r="D23" s="70"/>
@@ -4150,7 +3910,7 @@
       <x:c r="AL24" s="9"/>
       <x:c r="AM24" s="9"/>
       <x:c r="AN24" s="43" t="s">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AO24" s="31"/>
       <x:c r="AP24" s="31"/>
@@ -4432,10 +4192,8 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
       <x:c r="M29" s="21"/>
-      <x:c r="N29" s="70" t="inlineStr">
-        <x:is>
-          <x:t>{View_4}</x:t>
-        </x:is>
+      <x:c r="N29" s="70" t="s">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="O29" s="70"/>
       <x:c r="P29" s="70"/>
@@ -4598,10 +4356,8 @@
     </x:row>
     <x:row r="32" spans="1:56">
       <x:c r="A32" s="5"/>
-      <x:c r="B32" s="70" t="inlineStr">
-        <x:is>
-          <x:t>4. {Input_8}</x:t>
-        </x:is>
+      <x:c r="B32" s="70" t="s">
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C32" s="70"/>
       <x:c r="D32" s="70"/>
@@ -4699,30 +4455,30 @@
       <x:c r="AL33" s="9"/>
       <x:c r="AM33" s="9"/>
       <x:c r="AN33" s="39" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AO33" s="41"/>
       <x:c r="AP33" s="39" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="AQ33" s="41"/>
       <x:c r="AR33" s="39" t="s">
-        <x:v>125</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="AS33" s="40"/>
       <x:c r="AT33" s="40"/>
       <x:c r="AU33" s="41"/>
       <x:c r="AV33" s="39" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="AW33" s="41"/>
       <x:c r="AX33" s="39" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AY33" s="40"/>
       <x:c r="AZ33" s="41"/>
       <x:c r="BA33" s="39" t="s">
-        <x:v>142</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB33" s="40"/>
       <x:c r="BC33" s="40"/>
@@ -4769,23 +4525,23 @@
       <x:c r="AL34" s="9"/>
       <x:c r="AM34" s="9"/>
       <x:c r="AN34" s="39" t="s">
-        <x:v>127</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="AO34" s="40"/>
       <x:c r="AP34" s="40"/>
       <x:c r="AQ34" s="41"/>
       <x:c r="AR34" s="39" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AS34" s="40"/>
       <x:c r="AT34" s="40"/>
       <x:c r="AU34" s="41"/>
       <x:c r="AV34" s="39" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AW34" s="41"/>
       <x:c r="AX34" s="39" t="s">
-        <x:v>5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AY34" s="40"/>
       <x:c r="AZ34" s="40"/>
@@ -4956,10 +4712,8 @@
       <x:c r="AQ37" s="31"/>
       <x:c r="AR37" s="31"/>
       <x:c r="AS37" s="32"/>
-      <x:c r="AT37" s="30" t="inlineStr">
-        <x:is>
-          <x:t>{Input_1}</x:t>
-        </x:is>
+      <x:c r="AT37" s="30" t="s">
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AU37" s="31"/>
       <x:c r="AV37" s="31"/>
@@ -4986,10 +4740,8 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
       <x:c r="M38" s="21"/>
-      <x:c r="N38" s="70" t="inlineStr">
-        <x:is>
-          <x:t>{View_5}</x:t>
-        </x:is>
+      <x:c r="N38" s="70" t="s">
+        <x:v>155</x:v>
       </x:c>
       <x:c r="O38" s="70"/>
       <x:c r="P38" s="70"/>
@@ -5080,10 +4832,8 @@
       <x:c r="AQ39" s="34"/>
       <x:c r="AR39" s="34"/>
       <x:c r="AS39" s="35"/>
-      <x:c r="AT39" s="30" t="inlineStr">
-        <x:is>
-          <x:t>{Input_2}</x:t>
-        </x:is>
+      <x:c r="AT39" s="30" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AU39" s="31"/>
       <x:c r="AV39" s="31"/>
@@ -5156,10 +4906,8 @@
     </x:row>
     <x:row r="41" spans="1:56">
       <x:c r="A41" s="5"/>
-      <x:c r="B41" s="70" t="inlineStr">
-        <x:is>
-          <x:t>5. {Input_9}</x:t>
-        </x:is>
+      <x:c r="B41" s="70" t="s">
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C41" s="70"/>
       <x:c r="D41" s="70"/>
@@ -5199,17 +4947,15 @@
       <x:c r="AL41" s="9"/>
       <x:c r="AM41" s="9"/>
       <x:c r="AN41" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AO41" s="31"/>
       <x:c r="AP41" s="31"/>
       <x:c r="AQ41" s="31"/>
       <x:c r="AR41" s="31"/>
       <x:c r="AS41" s="32"/>
-      <x:c r="AT41" s="30" t="inlineStr">
-        <x:is>
-          <x:t>{Input_3}</x:t>
-        </x:is>
+      <x:c r="AT41" s="30" t="s">
+        <x:v>115</x:v>
       </x:c>
       <x:c r="AU41" s="31"/>
       <x:c r="AV41" s="31"/>
@@ -5437,7 +5183,7 @@
       <x:c r="AL45" s="9"/>
       <x:c r="AM45" s="9"/>
       <x:c r="AN45" s="30" t="s">
-        <x:v>4</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="AO45" s="31"/>
       <x:c r="AP45" s="31"/>
@@ -5503,7 +5249,7 @@
       <x:c r="AK46" s="8"/>
       <x:c r="AL46" s="8"/>
       <x:c r="AM46" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AN46" s="36"/>
       <x:c r="AO46" s="37"/>

--- a/사용자템플릿_엑셀_가공도.xlsx
+++ b/사용자템플릿_엑셀_가공도.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17580" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet3" sheetId="1" r:id="rId4"/>
@@ -21,484 +21,484 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <x:si>
+    <x:t>{Input_88}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_12}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_100}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_127}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_87}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_52}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_125}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_115}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DP NO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIZE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHECKED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[no]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[code]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q'TY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Image}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REV.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRAWN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Note:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T/W</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>1.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAG NO. [text]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_24}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_74}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_29}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_37}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_102}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_2}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_28}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_5}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_113}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_17}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_128}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_126}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_57}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_58}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_34}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_44}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_11}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_14}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESCRIPTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_53}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAINT CODE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_107}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_68}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_60}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_97}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_26}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_89}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_7}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_6}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_117}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_111}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_118}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_32}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_108}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_98}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_123}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_121}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_64}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_104}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_95}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_46}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_119}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_73}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_65}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_120}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_111}</x:t>
+    <x:t>{Input_109}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_78}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_69}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_3}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_47}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_91}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_3}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_104}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_64}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_98}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_29}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_117}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_34}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_108}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_6}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_7}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_57}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_24}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_14}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_119}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_53}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_89}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAINT CODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_73}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_97}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_44}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESCRIPTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_11}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_26}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_107}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_65}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_60}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_74}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_68}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_102}</x:t>
+    <x:t>{Input_5}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_124}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_23}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_35}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_55}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_112}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_90}</x:t>
   </x:si>
   <x:si>
-    <x:t>2.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T/W</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>NO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_18}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_112}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_46}</x:t>
+    <x:t>{Input_36}</x:t>
   </x:si>
   <x:si>
     <x:t>{Input_96}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_69}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_78}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_47}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_118}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_36}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_55}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_23}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_35}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_5}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_8}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_49}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_93}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_82}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_9}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_61}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_122}</x:t>
   </x:si>
   <x:si>
+    <x:t>{Input_56}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_63}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_62}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{Input_79}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_56}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_124}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_82}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_93}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_61}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_62}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_63}</x:t>
-  </x:si>
-  <x:si>
     <x:t>{Input_94}</x:t>
   </x:si>
   <x:si>
-    <x:t>{Input_109}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_49}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_2}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_28}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_113}</x:t>
+    <x:t>{Input_45}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_30}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_15}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_48}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_99}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_84}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_22}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_76}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_54}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_72}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_129}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_70}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_40}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_27}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_105}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_85}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_10}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_41}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_31}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_67}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_83}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_116}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPROVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_86}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_43}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_81}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATERIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_25}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_75}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_42}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_106}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_16}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_66}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_38}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_33}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_80}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_110}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_101}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_92}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOM TABLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_114}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_21}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_59}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_103}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_50}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_77}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_19}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_20}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_13}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_39}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_51}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{Input_71}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_1}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{View_3}</x:t>
   </x:si>
   <x:si>
     <x:t>{View_4}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_125}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_127}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_87}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_5}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_115}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_126}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_37}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_58}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_52}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_128}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_17}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_129}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_3}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_72}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_40}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_76}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_100}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_48}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_27}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_12}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_2}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_88}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_43}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_45}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_84}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_15}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_85}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_75}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_86}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_41}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_116}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_10}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_101}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_30}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_70}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_59}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_25}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_22}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_66}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_54}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_83}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_105}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_99}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_77}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_16}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APPROVED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_13}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_21}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_81}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATERIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_38}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_50}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_31}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_33}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOM TABLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_67}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_92}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_42}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_80}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_106}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{View_1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_114}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_103}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_110}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_71}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_20}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_19}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_51}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Input_39}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Note:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q'TY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DP NO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REV.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{Image}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIZE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[no]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHECKED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DRAWN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[code]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAG NO. [text]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1995,7 +1995,7 @@
       <x:c r="AL1" s="33"/>
       <x:c r="AM1" s="33"/>
       <x:c r="AN1" s="41" t="s">
-        <x:v>132</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="AO1" s="42"/>
       <x:c r="AP1" s="42"/>
@@ -2028,10 +2028,9 @@
       <x:c r="K2" s="10"/>
       <x:c r="L2" s="10"/>
       <x:c r="M2" s="10"/>
-      <x:c r="N2" s="72" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="O2" s="72"/>
+      <x:c r="O2" s="72" t="s">
+        <x:v>157</x:v>
+      </x:c>
       <x:c r="P2" s="72"/>
       <x:c r="Q2" s="72"/>
       <x:c r="R2" s="72"/>
@@ -2045,7 +2044,7 @@
       <x:c r="Z2" s="72"/>
       <x:c r="AA2" s="72"/>
       <x:c r="AB2" s="72"/>
-      <x:c r="AC2" s="10"/>
+      <x:c r="AC2" s="72"/>
       <x:c r="AD2" s="10"/>
       <x:c r="AE2" s="10"/>
       <x:c r="AF2" s="10"/>
@@ -2057,37 +2056,37 @@
       <x:c r="AL2" s="36"/>
       <x:c r="AM2" s="36"/>
       <x:c r="AN2" s="57" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AO2" s="58"/>
       <x:c r="AP2" s="59"/>
       <x:c r="AQ2" s="16" t="s">
-        <x:v>148</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AR2" s="32" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AS2" s="33"/>
       <x:c r="AT2" s="34"/>
       <x:c r="AU2" s="44" t="s">
-        <x:v>154</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="AV2" s="44"/>
       <x:c r="AW2" s="44"/>
       <x:c r="AX2" s="57" t="s">
-        <x:v>149</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="AY2" s="59"/>
       <x:c r="AZ2" s="44" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BA2" s="44"/>
       <x:c r="BB2" s="44"/>
       <x:c r="BC2" s="17" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BD2" s="17" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:56" ht="17.149999999999999" customHeight="1">
@@ -2104,7 +2103,6 @@
       <x:c r="K3" s="22"/>
       <x:c r="L3" s="22"/>
       <x:c r="M3" s="22"/>
-      <x:c r="N3" s="72"/>
       <x:c r="O3" s="72"/>
       <x:c r="P3" s="72"/>
       <x:c r="Q3" s="72"/>
@@ -2119,7 +2117,7 @@
       <x:c r="Z3" s="72"/>
       <x:c r="AA3" s="72"/>
       <x:c r="AB3" s="72"/>
-      <x:c r="AC3" s="22"/>
+      <x:c r="AC3" s="72"/>
       <x:c r="AD3" s="22"/>
       <x:c r="AE3" s="22"/>
       <x:c r="AF3" s="22"/>
@@ -2131,37 +2129,37 @@
       <x:c r="AL3" s="36"/>
       <x:c r="AM3" s="36"/>
       <x:c r="AN3" s="60" t="s">
-        <x:v>109</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="AO3" s="61"/>
       <x:c r="AP3" s="62"/>
       <x:c r="AQ3" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="AR3" s="60" t="s">
-        <x:v>92</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="AS3" s="74"/>
       <x:c r="AT3" s="75"/>
       <x:c r="AU3" s="61" t="s">
-        <x:v>55</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AV3" s="67"/>
       <x:c r="AW3" s="67"/>
       <x:c r="AX3" s="49" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="AY3" s="56"/>
       <x:c r="AZ3" s="69" t="s">
-        <x:v>104</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="BA3" s="70"/>
       <x:c r="BB3" s="70"/>
       <x:c r="BC3" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BD3" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:81" ht="17.149999999999999" customHeight="1">
@@ -2178,7 +2176,6 @@
       <x:c r="K4" s="22"/>
       <x:c r="L4" s="22"/>
       <x:c r="M4" s="22"/>
-      <x:c r="N4" s="72"/>
       <x:c r="O4" s="72"/>
       <x:c r="P4" s="72"/>
       <x:c r="Q4" s="72"/>
@@ -2193,7 +2190,7 @@
       <x:c r="Z4" s="72"/>
       <x:c r="AA4" s="72"/>
       <x:c r="AB4" s="72"/>
-      <x:c r="AC4" s="22"/>
+      <x:c r="AC4" s="72"/>
       <x:c r="AD4" s="22"/>
       <x:c r="AE4" s="22"/>
       <x:c r="AF4" s="22"/>
@@ -2205,37 +2202,37 @@
       <x:c r="AL4" s="36"/>
       <x:c r="AM4" s="36"/>
       <x:c r="AN4" s="63" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO4" s="64"/>
       <x:c r="AP4" s="65"/>
       <x:c r="AQ4" s="25" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AR4" s="46" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="AS4" s="47"/>
       <x:c r="AT4" s="48"/>
       <x:c r="AU4" s="64" t="s">
-        <x:v>63</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AV4" s="68"/>
       <x:c r="AW4" s="68"/>
       <x:c r="AX4" s="46" t="s">
-        <x:v>142</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="AY4" s="48"/>
       <x:c r="AZ4" s="71" t="s">
-        <x:v>106</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="BA4" s="72"/>
       <x:c r="BB4" s="72"/>
       <x:c r="BC4" s="18" t="s">
-        <x:v>110</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="BD4" s="18" t="s">
-        <x:v>108</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BM4" s="22"/>
       <x:c r="BN4" s="24"/>
@@ -2258,22 +2255,19 @@
     <x:row r="5" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A5" s="6"/>
       <x:c r="B5" s="31" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C5" s="27" t="s">
-        <x:v>58</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="27"/>
       <x:c r="E5" s="27"/>
       <x:c r="F5" s="27"/>
-      <x:c r="G5" s="27"/>
-      <x:c r="H5" s="27"/>
+      <x:c r="H5" s="27" t="s">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="I5" s="27"/>
       <x:c r="J5" s="27"/>
       <x:c r="K5" s="27"/>
       <x:c r="L5" s="27"/>
       <x:c r="M5" s="22"/>
-      <x:c r="N5" s="72"/>
       <x:c r="O5" s="72"/>
       <x:c r="P5" s="72"/>
       <x:c r="Q5" s="72"/>
@@ -2288,7 +2282,7 @@
       <x:c r="Z5" s="72"/>
       <x:c r="AA5" s="72"/>
       <x:c r="AB5" s="72"/>
-      <x:c r="AC5" s="22"/>
+      <x:c r="AC5" s="72"/>
       <x:c r="AD5" s="22"/>
       <x:c r="AE5" s="22"/>
       <x:c r="AF5" s="22"/>
@@ -2300,37 +2294,37 @@
       <x:c r="AL5" s="36"/>
       <x:c r="AM5" s="36"/>
       <x:c r="AN5" s="60" t="s">
-        <x:v>97</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO5" s="61"/>
       <x:c r="AP5" s="62"/>
       <x:c r="AQ5" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="AR5" s="49" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="AS5" s="50"/>
       <x:c r="AT5" s="51"/>
       <x:c r="AU5" s="69" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AV5" s="70"/>
       <x:c r="AW5" s="70"/>
       <x:c r="AX5" s="49" t="s">
-        <x:v>91</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AY5" s="51"/>
       <x:c r="AZ5" s="69" t="s">
-        <x:v>80</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="BA5" s="70"/>
       <x:c r="BB5" s="70"/>
       <x:c r="BC5" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BD5" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BM5" s="24"/>
       <x:c r="BN5" s="24"/>
@@ -2353,11 +2347,9 @@
     <x:row r="6" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A6" s="6"/>
       <x:c r="B6" s="27"/>
-      <x:c r="C6" s="27"/>
       <x:c r="D6" s="27"/>
       <x:c r="E6" s="27"/>
       <x:c r="F6" s="27"/>
-      <x:c r="G6" s="27"/>
       <x:c r="H6" s="27"/>
       <x:c r="I6" s="27"/>
       <x:c r="J6" s="27"/>
@@ -2391,37 +2383,37 @@
       <x:c r="AL6" s="10"/>
       <x:c r="AM6" s="10"/>
       <x:c r="AN6" s="63" t="s">
-        <x:v>124</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="AO6" s="64"/>
       <x:c r="AP6" s="65"/>
       <x:c r="AQ6" s="19" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="AR6" s="46" t="s">
-        <x:v>100</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AS6" s="47"/>
       <x:c r="AT6" s="48"/>
       <x:c r="AU6" s="71" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AV6" s="72"/>
       <x:c r="AW6" s="72"/>
       <x:c r="AX6" s="46" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="AY6" s="48"/>
       <x:c r="AZ6" s="71" t="s">
-        <x:v>99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BA6" s="72"/>
       <x:c r="BB6" s="72"/>
       <x:c r="BC6" s="18" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="BD6" s="18" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BM6" s="24"/>
       <x:c r="BN6" s="24"/>
@@ -2444,12 +2436,10 @@
     <x:row r="7" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A7" s="6"/>
       <x:c r="B7" s="10"/>
-      <x:c r="C7" s="10"/>
       <x:c r="D7" s="22"/>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22"/>
-      <x:c r="G7" s="22"/>
-      <x:c r="H7" s="22"/>
+      <x:c r="H7" s="10"/>
       <x:c r="I7" s="22"/>
       <x:c r="J7" s="22"/>
       <x:c r="K7" s="22"/>
@@ -2482,37 +2472,37 @@
       <x:c r="AL7" s="10"/>
       <x:c r="AM7" s="10"/>
       <x:c r="AN7" s="60" t="s">
-        <x:v>19</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO7" s="61"/>
       <x:c r="AP7" s="62"/>
       <x:c r="AQ7" s="14" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="AR7" s="49" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AS7" s="50"/>
       <x:c r="AT7" s="51"/>
       <x:c r="AU7" s="69" t="s">
-        <x:v>113</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="AV7" s="70"/>
       <x:c r="AW7" s="70"/>
       <x:c r="AX7" s="49" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AY7" s="51"/>
       <x:c r="AZ7" s="69" t="s">
-        <x:v>22</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA7" s="70"/>
       <x:c r="BB7" s="70"/>
       <x:c r="BC7" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BD7" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BM7" s="24"/>
       <x:c r="BN7" s="24"/>
@@ -2534,11 +2524,9 @@
     <x:row r="8" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A8" s="6"/>
       <x:c r="B8" s="22"/>
-      <x:c r="C8" s="22"/>
       <x:c r="D8" s="22"/>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22"/>
-      <x:c r="G8" s="22"/>
       <x:c r="H8" s="22"/>
       <x:c r="I8" s="22"/>
       <x:c r="J8" s="22"/>
@@ -2572,29 +2560,29 @@
       <x:c r="AL8" s="10"/>
       <x:c r="AM8" s="10"/>
       <x:c r="AN8" s="63" t="s">
-        <x:v>103</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AO8" s="64"/>
       <x:c r="AP8" s="65"/>
       <x:c r="AQ8" s="19" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="AR8" s="46" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AS8" s="47"/>
       <x:c r="AT8" s="48"/>
       <x:c r="AU8" s="71" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AV8" s="72"/>
       <x:c r="AW8" s="72"/>
       <x:c r="AX8" s="46" t="s">
-        <x:v>105</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="AY8" s="48"/>
       <x:c r="AZ8" s="71" t="s">
-        <x:v>36</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BA8" s="72"/>
       <x:c r="BB8" s="72"/>
@@ -2602,7 +2590,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="BD8" s="18" t="s">
-        <x:v>4</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BM8" s="24"/>
       <x:c r="BN8" s="24"/>
@@ -2625,12 +2613,10 @@
     <x:row r="9" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A9" s="6"/>
       <x:c r="B9" s="10"/>
-      <x:c r="C9" s="10"/>
       <x:c r="D9" s="22"/>
       <x:c r="E9" s="22"/>
       <x:c r="F9" s="22"/>
-      <x:c r="G9" s="22"/>
-      <x:c r="H9" s="22"/>
+      <x:c r="H9" s="10"/>
       <x:c r="I9" s="22"/>
       <x:c r="J9" s="22"/>
       <x:c r="K9" s="22"/>
@@ -2663,37 +2649,37 @@
       <x:c r="AL9" s="10"/>
       <x:c r="AM9" s="10"/>
       <x:c r="AN9" s="60" t="s">
-        <x:v>122</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="AO9" s="61"/>
       <x:c r="AP9" s="62"/>
       <x:c r="AQ9" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="AR9" s="49" t="s">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AS9" s="50"/>
       <x:c r="AT9" s="51"/>
       <x:c r="AU9" s="69" t="s">
-        <x:v>67</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="AV9" s="70"/>
       <x:c r="AW9" s="70"/>
       <x:c r="AX9" s="49" t="s">
-        <x:v>93</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AY9" s="51"/>
       <x:c r="AZ9" s="69" t="s">
-        <x:v>6</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA9" s="70"/>
       <x:c r="BB9" s="70"/>
       <x:c r="BC9" s="12" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="BD9" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BM9" s="24"/>
       <x:c r="BN9" s="24"/>
@@ -2716,12 +2702,10 @@
     <x:row r="10" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A10" s="6"/>
       <x:c r="B10" s="10"/>
-      <x:c r="C10" s="10"/>
       <x:c r="D10" s="22"/>
       <x:c r="E10" s="22"/>
       <x:c r="F10" s="22"/>
-      <x:c r="G10" s="22"/>
-      <x:c r="H10" s="22"/>
+      <x:c r="H10" s="10"/>
       <x:c r="I10" s="22"/>
       <x:c r="J10" s="22"/>
       <x:c r="K10" s="22"/>
@@ -2754,37 +2738,37 @@
       <x:c r="AL10" s="10"/>
       <x:c r="AM10" s="10"/>
       <x:c r="AN10" s="63" t="s">
-        <x:v>88</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="AO10" s="64"/>
       <x:c r="AP10" s="65"/>
       <x:c r="AQ10" s="19" t="s">
-        <x:v>0</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AR10" s="46" t="s">
-        <x:v>52</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AS10" s="47"/>
       <x:c r="AT10" s="48"/>
       <x:c r="AU10" s="71" t="s">
-        <x:v>68</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="AV10" s="72"/>
       <x:c r="AW10" s="72"/>
       <x:c r="AX10" s="46" t="s">
-        <x:v>121</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="AY10" s="48"/>
       <x:c r="AZ10" s="71" t="s">
-        <x:v>134</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="BA10" s="72"/>
       <x:c r="BB10" s="72"/>
       <x:c r="BC10" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BD10" s="18" t="s">
-        <x:v>61</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BM10" s="24"/>
       <x:c r="BN10" s="24"/>
@@ -2807,21 +2791,19 @@
     <x:row r="11" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A11" s="6"/>
       <x:c r="B11" s="10"/>
-      <x:c r="C11" s="10"/>
       <x:c r="D11" s="22"/>
       <x:c r="E11" s="22"/>
       <x:c r="F11" s="22"/>
-      <x:c r="G11" s="22"/>
-      <x:c r="H11" s="22"/>
+      <x:c r="H11" s="10"/>
       <x:c r="I11" s="22"/>
       <x:c r="J11" s="22"/>
       <x:c r="K11" s="22"/>
       <x:c r="L11" s="22"/>
       <x:c r="M11" s="22"/>
-      <x:c r="N11" s="72" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="O11" s="72"/>
+      <x:c r="N11" s="27"/>
+      <x:c r="O11" s="72" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="P11" s="72"/>
       <x:c r="Q11" s="72"/>
       <x:c r="R11" s="72"/>
@@ -2835,7 +2817,7 @@
       <x:c r="Z11" s="72"/>
       <x:c r="AA11" s="72"/>
       <x:c r="AB11" s="72"/>
-      <x:c r="AC11" s="22"/>
+      <x:c r="AC11" s="72"/>
       <x:c r="AD11" s="22"/>
       <x:c r="AE11" s="22"/>
       <x:c r="AF11" s="22"/>
@@ -2847,37 +2829,37 @@
       <x:c r="AL11" s="10"/>
       <x:c r="AM11" s="10"/>
       <x:c r="AN11" s="60" t="s">
-        <x:v>46</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="AO11" s="61"/>
       <x:c r="AP11" s="62"/>
       <x:c r="AQ11" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="AR11" s="49" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="AS11" s="50"/>
       <x:c r="AT11" s="51"/>
       <x:c r="AU11" s="69" t="s">
-        <x:v>69</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AV11" s="70"/>
       <x:c r="AW11" s="70"/>
       <x:c r="AX11" s="49" t="s">
-        <x:v>51</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="AY11" s="51"/>
       <x:c r="AZ11" s="69" t="s">
-        <x:v>66</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BA11" s="70"/>
       <x:c r="BB11" s="70"/>
       <x:c r="BC11" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BD11" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BM11" s="47"/>
       <x:c r="BN11" s="47"/>
@@ -2900,18 +2882,16 @@
     <x:row r="12" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="10"/>
-      <x:c r="C12" s="10"/>
       <x:c r="D12" s="22"/>
       <x:c r="E12" s="22"/>
       <x:c r="F12" s="22"/>
-      <x:c r="G12" s="22"/>
-      <x:c r="H12" s="22"/>
+      <x:c r="H12" s="10"/>
       <x:c r="I12" s="22"/>
       <x:c r="J12" s="22"/>
       <x:c r="K12" s="22"/>
       <x:c r="L12" s="22"/>
       <x:c r="M12" s="22"/>
-      <x:c r="N12" s="72"/>
+      <x:c r="N12" s="27"/>
       <x:c r="O12" s="72"/>
       <x:c r="P12" s="72"/>
       <x:c r="Q12" s="72"/>
@@ -2926,7 +2906,7 @@
       <x:c r="Z12" s="72"/>
       <x:c r="AA12" s="72"/>
       <x:c r="AB12" s="72"/>
-      <x:c r="AC12" s="22"/>
+      <x:c r="AC12" s="72"/>
       <x:c r="AD12" s="22"/>
       <x:c r="AE12" s="22"/>
       <x:c r="AF12" s="22"/>
@@ -2938,37 +2918,37 @@
       <x:c r="AL12" s="10"/>
       <x:c r="AM12" s="10"/>
       <x:c r="AN12" s="63" t="s">
-        <x:v>144</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="AO12" s="64"/>
       <x:c r="AP12" s="65"/>
       <x:c r="AQ12" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AR12" s="46" t="s">
-        <x:v>72</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="AS12" s="47"/>
       <x:c r="AT12" s="48"/>
       <x:c r="AU12" s="71" t="s">
-        <x:v>9</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AV12" s="72"/>
       <x:c r="AW12" s="72"/>
       <x:c r="AX12" s="46" t="s">
-        <x:v>62</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AY12" s="48"/>
       <x:c r="AZ12" s="71" t="s">
-        <x:v>70</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BA12" s="72"/>
       <x:c r="BB12" s="72"/>
       <x:c r="BC12" s="18" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BD12" s="18" t="s">
-        <x:v>64</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="BM12" s="24"/>
       <x:c r="BN12" s="24"/>
@@ -2991,18 +2971,16 @@
     <x:row r="13" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A13" s="6"/>
       <x:c r="B13" s="10"/>
-      <x:c r="C13" s="10"/>
       <x:c r="D13" s="22"/>
       <x:c r="E13" s="22"/>
       <x:c r="F13" s="22"/>
-      <x:c r="G13" s="22"/>
-      <x:c r="H13" s="22"/>
+      <x:c r="H13" s="10"/>
       <x:c r="I13" s="22"/>
       <x:c r="J13" s="22"/>
       <x:c r="K13" s="22"/>
       <x:c r="L13" s="22"/>
       <x:c r="M13" s="22"/>
-      <x:c r="N13" s="72"/>
+      <x:c r="N13" s="27"/>
       <x:c r="O13" s="72"/>
       <x:c r="P13" s="72"/>
       <x:c r="Q13" s="72"/>
@@ -3017,7 +2995,7 @@
       <x:c r="Z13" s="72"/>
       <x:c r="AA13" s="72"/>
       <x:c r="AB13" s="72"/>
-      <x:c r="AC13" s="22"/>
+      <x:c r="AC13" s="72"/>
       <x:c r="AD13" s="22"/>
       <x:c r="AE13" s="22"/>
       <x:c r="AF13" s="22"/>
@@ -3029,29 +3007,29 @@
       <x:c r="AL13" s="10"/>
       <x:c r="AM13" s="10"/>
       <x:c r="AN13" s="60" t="s">
-        <x:v>143</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="AO13" s="61"/>
       <x:c r="AP13" s="62"/>
       <x:c r="AQ13" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AR13" s="49" t="s">
-        <x:v>129</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="AS13" s="50"/>
       <x:c r="AT13" s="51"/>
       <x:c r="AU13" s="69" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AV13" s="70"/>
       <x:c r="AW13" s="70"/>
       <x:c r="AX13" s="49" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="AY13" s="51"/>
       <x:c r="AZ13" s="69" t="s">
-        <x:v>3</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BA13" s="70"/>
       <x:c r="BB13" s="70"/>
@@ -3059,7 +3037,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="BD13" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BM13" s="24"/>
       <x:c r="BN13" s="24"/>
@@ -3082,22 +3060,20 @@
     <x:row r="14" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A14" s="6"/>
       <x:c r="B14" s="31" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" s="27"/>
       <x:c r="E14" s="27"/>
       <x:c r="F14" s="27"/>
-      <x:c r="G14" s="27"/>
-      <x:c r="H14" s="27"/>
+      <x:c r="H14" s="27" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="I14" s="27"/>
       <x:c r="J14" s="27"/>
       <x:c r="K14" s="27"/>
       <x:c r="L14" s="27"/>
       <x:c r="M14" s="22"/>
-      <x:c r="N14" s="72"/>
+      <x:c r="N14" s="27"/>
       <x:c r="O14" s="72"/>
       <x:c r="P14" s="72"/>
       <x:c r="Q14" s="72"/>
@@ -3112,7 +3088,7 @@
       <x:c r="Z14" s="72"/>
       <x:c r="AA14" s="72"/>
       <x:c r="AB14" s="72"/>
-      <x:c r="AC14" s="22"/>
+      <x:c r="AC14" s="72"/>
       <x:c r="AD14" s="22"/>
       <x:c r="AE14" s="22"/>
       <x:c r="AF14" s="22"/>
@@ -3124,37 +3100,37 @@
       <x:c r="AL14" s="10"/>
       <x:c r="AM14" s="10"/>
       <x:c r="AN14" s="63" t="s">
-        <x:v>125</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="AO14" s="64"/>
       <x:c r="AP14" s="65"/>
       <x:c r="AQ14" s="19" t="s">
-        <x:v>54</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AR14" s="46" t="s">
-        <x:v>145</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="AS14" s="47"/>
       <x:c r="AT14" s="48"/>
       <x:c r="AU14" s="71" t="s">
-        <x:v>116</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="AV14" s="72"/>
       <x:c r="AW14" s="72"/>
       <x:c r="AX14" s="46" t="s">
-        <x:v>126</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AY14" s="48"/>
       <x:c r="AZ14" s="71" t="s">
-        <x:v>49</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BA14" s="72"/>
       <x:c r="BB14" s="72"/>
       <x:c r="BC14" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BD14" s="18" t="s">
-        <x:v>83</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BM14" s="24"/>
       <x:c r="BN14" s="24"/>
@@ -3177,11 +3153,9 @@
     <x:row r="15" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A15" s="6"/>
       <x:c r="B15" s="27"/>
-      <x:c r="C15" s="27"/>
       <x:c r="D15" s="27"/>
       <x:c r="E15" s="27"/>
       <x:c r="F15" s="27"/>
-      <x:c r="G15" s="27"/>
       <x:c r="H15" s="27"/>
       <x:c r="I15" s="27"/>
       <x:c r="J15" s="27"/>
@@ -3215,37 +3189,37 @@
       <x:c r="AL15" s="10"/>
       <x:c r="AM15" s="10"/>
       <x:c r="AN15" s="60" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="AO15" s="61"/>
       <x:c r="AP15" s="66"/>
       <x:c r="AQ15" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AR15" s="52" t="s">
-        <x:v>86</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AS15" s="53"/>
       <x:c r="AT15" s="54"/>
       <x:c r="AU15" s="73" t="s">
-        <x:v>133</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="AV15" s="70"/>
       <x:c r="AW15" s="70"/>
       <x:c r="AX15" s="52" t="s">
-        <x:v>65</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AY15" s="54"/>
       <x:c r="AZ15" s="73" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BA15" s="70"/>
       <x:c r="BB15" s="70"/>
       <x:c r="BC15" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BD15" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BM15" s="24"/>
       <x:c r="BN15" s="24"/>
@@ -3268,12 +3242,10 @@
     <x:row r="16" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A16" s="6"/>
       <x:c r="B16" s="10"/>
-      <x:c r="C16" s="10"/>
       <x:c r="D16" s="22"/>
       <x:c r="E16" s="22"/>
       <x:c r="F16" s="22"/>
-      <x:c r="G16" s="22"/>
-      <x:c r="H16" s="22"/>
+      <x:c r="H16" s="10"/>
       <x:c r="I16" s="22"/>
       <x:c r="J16" s="22"/>
       <x:c r="K16" s="22"/>
@@ -3306,37 +3278,37 @@
       <x:c r="AL16" s="10"/>
       <x:c r="AM16" s="10"/>
       <x:c r="AN16" s="60" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AO16" s="61"/>
       <x:c r="AP16" s="62"/>
       <x:c r="AQ16" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AR16" s="49" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS16" s="55"/>
       <x:c r="AT16" s="56"/>
       <x:c r="AU16" s="69" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AV16" s="70"/>
       <x:c r="AW16" s="70"/>
       <x:c r="AX16" s="49" t="s">
-        <x:v>118</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="AY16" s="56"/>
       <x:c r="AZ16" s="69" t="s">
-        <x:v>10</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BA16" s="70"/>
       <x:c r="BB16" s="70"/>
       <x:c r="BC16" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BD16" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BM16" s="24"/>
       <x:c r="BN16" s="24"/>
@@ -3359,12 +3331,10 @@
     <x:row r="17" spans="1:81" ht="17.149999999999999" customHeight="1">
       <x:c r="A17" s="6"/>
       <x:c r="B17" s="10"/>
-      <x:c r="C17" s="10"/>
       <x:c r="D17" s="22"/>
       <x:c r="E17" s="22"/>
       <x:c r="F17" s="22"/>
-      <x:c r="G17" s="22"/>
-      <x:c r="H17" s="22"/>
+      <x:c r="H17" s="10"/>
       <x:c r="I17" s="22"/>
       <x:c r="J17" s="22"/>
       <x:c r="K17" s="22"/>
@@ -3397,37 +3367,37 @@
       <x:c r="AL17" s="10"/>
       <x:c r="AM17" s="10"/>
       <x:c r="AN17" s="60" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AO17" s="61"/>
       <x:c r="AP17" s="62"/>
       <x:c r="AQ17" s="14" t="s">
-        <x:v>146</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AR17" s="49" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="AS17" s="55"/>
       <x:c r="AT17" s="56"/>
       <x:c r="AU17" s="69" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AV17" s="70"/>
       <x:c r="AW17" s="70"/>
       <x:c r="AX17" s="49" t="s">
-        <x:v>102</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AY17" s="56"/>
       <x:c r="AZ17" s="69" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA17" s="70"/>
       <x:c r="BB17" s="70"/>
       <x:c r="BC17" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="BD17" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="BM17" s="24"/>
       <x:c r="BN17" s="24"/>
@@ -3450,12 +3420,10 @@
     <x:row r="18" spans="1:81">
       <x:c r="A18" s="6"/>
       <x:c r="B18" s="10"/>
-      <x:c r="C18" s="10"/>
       <x:c r="D18" s="22"/>
       <x:c r="E18" s="22"/>
       <x:c r="F18" s="22"/>
-      <x:c r="G18" s="22"/>
-      <x:c r="H18" s="22"/>
+      <x:c r="H18" s="10"/>
       <x:c r="I18" s="22"/>
       <x:c r="J18" s="22"/>
       <x:c r="K18" s="22"/>
@@ -3525,12 +3493,10 @@
     <x:row r="19" spans="1:81">
       <x:c r="A19" s="6"/>
       <x:c r="B19" s="10"/>
-      <x:c r="C19" s="10"/>
       <x:c r="D19" s="22"/>
       <x:c r="E19" s="22"/>
       <x:c r="F19" s="22"/>
-      <x:c r="G19" s="22"/>
-      <x:c r="H19" s="22"/>
+      <x:c r="H19" s="10"/>
       <x:c r="I19" s="22"/>
       <x:c r="J19" s="22"/>
       <x:c r="K19" s="22"/>
@@ -3600,21 +3566,19 @@
     <x:row r="20" spans="1:81">
       <x:c r="A20" s="6"/>
       <x:c r="B20" s="10"/>
-      <x:c r="C20" s="10"/>
       <x:c r="D20" s="22"/>
       <x:c r="E20" s="22"/>
       <x:c r="F20" s="22"/>
-      <x:c r="G20" s="22"/>
-      <x:c r="H20" s="22"/>
+      <x:c r="H20" s="10"/>
       <x:c r="I20" s="22"/>
       <x:c r="J20" s="22"/>
       <x:c r="K20" s="22"/>
       <x:c r="L20" s="22"/>
       <x:c r="M20" s="22"/>
-      <x:c r="N20" s="72" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="O20" s="72"/>
+      <x:c r="N20" s="27"/>
+      <x:c r="O20" s="72" t="s">
+        <x:v>158</x:v>
+      </x:c>
       <x:c r="P20" s="72"/>
       <x:c r="Q20" s="72"/>
       <x:c r="R20" s="72"/>
@@ -3628,7 +3592,7 @@
       <x:c r="Z20" s="72"/>
       <x:c r="AA20" s="72"/>
       <x:c r="AB20" s="72"/>
-      <x:c r="AC20" s="22"/>
+      <x:c r="AC20" s="72"/>
       <x:c r="AD20" s="22"/>
       <x:c r="AE20" s="22"/>
       <x:c r="AF20" s="22"/>
@@ -3677,18 +3641,16 @@
     <x:row r="21" spans="1:81">
       <x:c r="A21" s="6"/>
       <x:c r="B21" s="10"/>
-      <x:c r="C21" s="10"/>
       <x:c r="D21" s="22"/>
       <x:c r="E21" s="22"/>
       <x:c r="F21" s="22"/>
-      <x:c r="G21" s="22"/>
-      <x:c r="H21" s="22"/>
+      <x:c r="H21" s="10"/>
       <x:c r="I21" s="22"/>
       <x:c r="J21" s="22"/>
       <x:c r="K21" s="22"/>
       <x:c r="L21" s="22"/>
       <x:c r="M21" s="22"/>
-      <x:c r="N21" s="72"/>
+      <x:c r="N21" s="27"/>
       <x:c r="O21" s="72"/>
       <x:c r="P21" s="72"/>
       <x:c r="Q21" s="72"/>
@@ -3703,7 +3665,7 @@
       <x:c r="Z21" s="72"/>
       <x:c r="AA21" s="72"/>
       <x:c r="AB21" s="72"/>
-      <x:c r="AC21" s="22"/>
+      <x:c r="AC21" s="72"/>
       <x:c r="AD21" s="22"/>
       <x:c r="AE21" s="22"/>
       <x:c r="AF21" s="22"/>
@@ -3752,18 +3714,16 @@
     <x:row r="22" spans="1:81">
       <x:c r="A22" s="6"/>
       <x:c r="B22" s="10"/>
-      <x:c r="C22" s="10"/>
       <x:c r="D22" s="22"/>
       <x:c r="E22" s="22"/>
       <x:c r="F22" s="22"/>
-      <x:c r="G22" s="22"/>
-      <x:c r="H22" s="22"/>
+      <x:c r="H22" s="10"/>
       <x:c r="I22" s="22"/>
       <x:c r="J22" s="22"/>
       <x:c r="K22" s="22"/>
       <x:c r="L22" s="22"/>
       <x:c r="M22" s="22"/>
-      <x:c r="N22" s="72"/>
+      <x:c r="N22" s="27"/>
       <x:c r="O22" s="72"/>
       <x:c r="P22" s="72"/>
       <x:c r="Q22" s="72"/>
@@ -3778,7 +3738,7 @@
       <x:c r="Z22" s="72"/>
       <x:c r="AA22" s="72"/>
       <x:c r="AB22" s="72"/>
-      <x:c r="AC22" s="22"/>
+      <x:c r="AC22" s="72"/>
       <x:c r="AD22" s="22"/>
       <x:c r="AE22" s="22"/>
       <x:c r="AF22" s="22"/>
@@ -3827,22 +3787,20 @@
     <x:row r="23" spans="1:83">
       <x:c r="A23" s="6"/>
       <x:c r="B23" s="31" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D23" s="27"/>
       <x:c r="E23" s="27"/>
       <x:c r="F23" s="27"/>
-      <x:c r="G23" s="27"/>
-      <x:c r="H23" s="27"/>
+      <x:c r="H23" s="27" t="s">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="I23" s="27"/>
       <x:c r="J23" s="27"/>
       <x:c r="K23" s="27"/>
       <x:c r="L23" s="27"/>
       <x:c r="M23" s="22"/>
-      <x:c r="N23" s="72"/>
+      <x:c r="N23" s="27"/>
       <x:c r="O23" s="72"/>
       <x:c r="P23" s="72"/>
       <x:c r="Q23" s="72"/>
@@ -3857,7 +3815,7 @@
       <x:c r="Z23" s="72"/>
       <x:c r="AA23" s="72"/>
       <x:c r="AB23" s="72"/>
-      <x:c r="AC23" s="22"/>
+      <x:c r="AC23" s="72"/>
       <x:c r="AD23" s="22"/>
       <x:c r="AE23" s="22"/>
       <x:c r="AF23" s="22"/>
@@ -3907,11 +3865,9 @@
     <x:row r="24" spans="1:81">
       <x:c r="A24" s="6"/>
       <x:c r="B24" s="27"/>
-      <x:c r="C24" s="27"/>
       <x:c r="D24" s="27"/>
       <x:c r="E24" s="27"/>
       <x:c r="F24" s="27"/>
-      <x:c r="G24" s="27"/>
       <x:c r="H24" s="27"/>
       <x:c r="I24" s="27"/>
       <x:c r="J24" s="27"/>
@@ -3945,7 +3901,7 @@
       <x:c r="AL24" s="10"/>
       <x:c r="AM24" s="10"/>
       <x:c r="AN24" s="45" t="s">
-        <x:v>147</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="AO24" s="33"/>
       <x:c r="AP24" s="33"/>
@@ -3984,12 +3940,10 @@
     <x:row r="25" spans="1:56">
       <x:c r="A25" s="6"/>
       <x:c r="B25" s="10"/>
-      <x:c r="C25" s="10"/>
       <x:c r="D25" s="22"/>
       <x:c r="E25" s="22"/>
       <x:c r="F25" s="22"/>
-      <x:c r="G25" s="22"/>
-      <x:c r="H25" s="22"/>
+      <x:c r="H25" s="10"/>
       <x:c r="I25" s="22"/>
       <x:c r="J25" s="22"/>
       <x:c r="K25" s="22"/>
@@ -4042,12 +3996,10 @@
     <x:row r="26" spans="1:56">
       <x:c r="A26" s="6"/>
       <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
       <x:c r="D26" s="22"/>
       <x:c r="E26" s="22"/>
       <x:c r="F26" s="22"/>
-      <x:c r="G26" s="22"/>
-      <x:c r="H26" s="22"/>
+      <x:c r="H26" s="10"/>
       <x:c r="I26" s="22"/>
       <x:c r="J26" s="22"/>
       <x:c r="K26" s="22"/>
@@ -4100,12 +4052,10 @@
     <x:row r="27" spans="1:56">
       <x:c r="A27" s="6"/>
       <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
       <x:c r="D27" s="22"/>
       <x:c r="E27" s="22"/>
       <x:c r="F27" s="22"/>
-      <x:c r="G27" s="22"/>
-      <x:c r="H27" s="22"/>
+      <x:c r="H27" s="10"/>
       <x:c r="I27" s="22"/>
       <x:c r="J27" s="22"/>
       <x:c r="K27" s="22"/>
@@ -4158,12 +4108,10 @@
     <x:row r="28" spans="1:56">
       <x:c r="A28" s="6"/>
       <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
       <x:c r="D28" s="22"/>
       <x:c r="E28" s="22"/>
       <x:c r="F28" s="22"/>
-      <x:c r="G28" s="22"/>
-      <x:c r="H28" s="22"/>
+      <x:c r="H28" s="10"/>
       <x:c r="I28" s="22"/>
       <x:c r="J28" s="22"/>
       <x:c r="K28" s="22"/>
@@ -4216,21 +4164,19 @@
     <x:row r="29" spans="1:56">
       <x:c r="A29" s="6"/>
       <x:c r="B29" s="10"/>
-      <x:c r="C29" s="10"/>
       <x:c r="D29" s="22"/>
       <x:c r="E29" s="22"/>
       <x:c r="F29" s="22"/>
-      <x:c r="G29" s="22"/>
-      <x:c r="H29" s="22"/>
+      <x:c r="H29" s="10"/>
       <x:c r="I29" s="22"/>
       <x:c r="J29" s="22"/>
       <x:c r="K29" s="22"/>
       <x:c r="L29" s="22"/>
       <x:c r="M29" s="22"/>
-      <x:c r="N29" s="72" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="O29" s="72"/>
+      <x:c r="N29" s="27"/>
+      <x:c r="O29" s="72" t="s">
+        <x:v>159</x:v>
+      </x:c>
       <x:c r="P29" s="72"/>
       <x:c r="Q29" s="72"/>
       <x:c r="R29" s="72"/>
@@ -4244,7 +4190,7 @@
       <x:c r="Z29" s="72"/>
       <x:c r="AA29" s="72"/>
       <x:c r="AB29" s="72"/>
-      <x:c r="AC29" s="22"/>
+      <x:c r="AC29" s="72"/>
       <x:c r="AD29" s="22"/>
       <x:c r="AE29" s="22"/>
       <x:c r="AF29" s="22"/>
@@ -4276,18 +4222,16 @@
     <x:row r="30" spans="1:56">
       <x:c r="A30" s="6"/>
       <x:c r="B30" s="10"/>
-      <x:c r="C30" s="10"/>
       <x:c r="D30" s="22"/>
       <x:c r="E30" s="22"/>
       <x:c r="F30" s="22"/>
-      <x:c r="G30" s="22"/>
-      <x:c r="H30" s="22"/>
+      <x:c r="H30" s="10"/>
       <x:c r="I30" s="22"/>
       <x:c r="J30" s="22"/>
       <x:c r="K30" s="22"/>
       <x:c r="L30" s="22"/>
       <x:c r="M30" s="22"/>
-      <x:c r="N30" s="72"/>
+      <x:c r="N30" s="27"/>
       <x:c r="O30" s="72"/>
       <x:c r="P30" s="72"/>
       <x:c r="Q30" s="72"/>
@@ -4302,7 +4246,7 @@
       <x:c r="Z30" s="72"/>
       <x:c r="AA30" s="72"/>
       <x:c r="AB30" s="72"/>
-      <x:c r="AC30" s="22"/>
+      <x:c r="AC30" s="72"/>
       <x:c r="AD30" s="22"/>
       <x:c r="AE30" s="22"/>
       <x:c r="AF30" s="22"/>
@@ -4334,18 +4278,16 @@
     <x:row r="31" spans="1:56">
       <x:c r="A31" s="6"/>
       <x:c r="B31" s="10"/>
-      <x:c r="C31" s="10"/>
       <x:c r="D31" s="22"/>
       <x:c r="E31" s="22"/>
       <x:c r="F31" s="22"/>
-      <x:c r="G31" s="22"/>
-      <x:c r="H31" s="22"/>
+      <x:c r="H31" s="10"/>
       <x:c r="I31" s="22"/>
       <x:c r="J31" s="22"/>
       <x:c r="K31" s="22"/>
       <x:c r="L31" s="22"/>
       <x:c r="M31" s="22"/>
-      <x:c r="N31" s="72"/>
+      <x:c r="N31" s="27"/>
       <x:c r="O31" s="72"/>
       <x:c r="P31" s="72"/>
       <x:c r="Q31" s="72"/>
@@ -4360,7 +4302,7 @@
       <x:c r="Z31" s="72"/>
       <x:c r="AA31" s="72"/>
       <x:c r="AB31" s="72"/>
-      <x:c r="AC31" s="22"/>
+      <x:c r="AC31" s="72"/>
       <x:c r="AD31" s="22"/>
       <x:c r="AE31" s="22"/>
       <x:c r="AF31" s="22"/>
@@ -4392,22 +4334,20 @@
     <x:row r="32" spans="1:56">
       <x:c r="A32" s="6"/>
       <x:c r="B32" s="31" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D32" s="27"/>
       <x:c r="E32" s="27"/>
       <x:c r="F32" s="27"/>
-      <x:c r="G32" s="27"/>
-      <x:c r="H32" s="27"/>
+      <x:c r="H32" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
       <x:c r="I32" s="27"/>
       <x:c r="J32" s="27"/>
       <x:c r="K32" s="27"/>
       <x:c r="L32" s="27"/>
       <x:c r="M32" s="22"/>
-      <x:c r="N32" s="72"/>
+      <x:c r="N32" s="27"/>
       <x:c r="O32" s="72"/>
       <x:c r="P32" s="72"/>
       <x:c r="Q32" s="72"/>
@@ -4422,7 +4362,7 @@
       <x:c r="Z32" s="72"/>
       <x:c r="AA32" s="72"/>
       <x:c r="AB32" s="72"/>
-      <x:c r="AC32" s="22"/>
+      <x:c r="AC32" s="72"/>
       <x:c r="AD32" s="22"/>
       <x:c r="AE32" s="22"/>
       <x:c r="AF32" s="22"/>
@@ -4454,11 +4394,9 @@
     <x:row r="33" spans="1:56">
       <x:c r="A33" s="6"/>
       <x:c r="B33" s="27"/>
-      <x:c r="C33" s="27"/>
       <x:c r="D33" s="27"/>
       <x:c r="E33" s="27"/>
       <x:c r="F33" s="27"/>
-      <x:c r="G33" s="27"/>
       <x:c r="H33" s="27"/>
       <x:c r="I33" s="27"/>
       <x:c r="J33" s="27"/>
@@ -4492,30 +4430,30 @@
       <x:c r="AL33" s="10"/>
       <x:c r="AM33" s="10"/>
       <x:c r="AN33" s="41" t="s">
-        <x:v>152</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AO33" s="43"/>
       <x:c r="AP33" s="41" t="s">
-        <x:v>150</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AQ33" s="43"/>
       <x:c r="AR33" s="41" t="s">
-        <x:v>27</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS33" s="42"/>
       <x:c r="AT33" s="42"/>
       <x:c r="AU33" s="43"/>
       <x:c r="AV33" s="41" t="s">
-        <x:v>157</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AW33" s="43"/>
       <x:c r="AX33" s="41" t="s">
-        <x:v>156</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AY33" s="42"/>
       <x:c r="AZ33" s="43"/>
       <x:c r="BA33" s="41" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="BB33" s="42"/>
       <x:c r="BC33" s="42"/>
@@ -4524,12 +4462,10 @@
     <x:row r="34" spans="1:56">
       <x:c r="A34" s="6"/>
       <x:c r="B34" s="10"/>
-      <x:c r="C34" s="10"/>
       <x:c r="D34" s="22"/>
       <x:c r="E34" s="22"/>
       <x:c r="F34" s="22"/>
-      <x:c r="G34" s="22"/>
-      <x:c r="H34" s="22"/>
+      <x:c r="H34" s="10"/>
       <x:c r="I34" s="22"/>
       <x:c r="J34" s="22"/>
       <x:c r="K34" s="22"/>
@@ -4562,23 +4498,23 @@
       <x:c r="AL34" s="10"/>
       <x:c r="AM34" s="10"/>
       <x:c r="AN34" s="41" t="s">
-        <x:v>23</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO34" s="42"/>
       <x:c r="AP34" s="42"/>
       <x:c r="AQ34" s="43"/>
       <x:c r="AR34" s="41" t="s">
-        <x:v>158</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AS34" s="42"/>
       <x:c r="AT34" s="42"/>
       <x:c r="AU34" s="43"/>
       <x:c r="AV34" s="41" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AW34" s="43"/>
       <x:c r="AX34" s="41" t="s">
-        <x:v>155</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AY34" s="42"/>
       <x:c r="AZ34" s="42"/>
@@ -4590,12 +4526,10 @@
     <x:row r="35" spans="1:56">
       <x:c r="A35" s="6"/>
       <x:c r="B35" s="10"/>
-      <x:c r="C35" s="10"/>
       <x:c r="D35" s="22"/>
       <x:c r="E35" s="22"/>
       <x:c r="F35" s="22"/>
-      <x:c r="G35" s="22"/>
-      <x:c r="H35" s="22"/>
+      <x:c r="H35" s="10"/>
       <x:c r="I35" s="22"/>
       <x:c r="J35" s="22"/>
       <x:c r="K35" s="22"/>
@@ -4648,12 +4582,10 @@
     <x:row r="36" spans="1:56">
       <x:c r="A36" s="6"/>
       <x:c r="B36" s="10"/>
-      <x:c r="C36" s="10"/>
       <x:c r="D36" s="22"/>
       <x:c r="E36" s="22"/>
       <x:c r="F36" s="22"/>
-      <x:c r="G36" s="22"/>
-      <x:c r="H36" s="22"/>
+      <x:c r="H36" s="10"/>
       <x:c r="I36" s="22"/>
       <x:c r="J36" s="22"/>
       <x:c r="K36" s="22"/>
@@ -4706,12 +4638,10 @@
     <x:row r="37" spans="1:56">
       <x:c r="A37" s="6"/>
       <x:c r="B37" s="10"/>
-      <x:c r="C37" s="10"/>
       <x:c r="D37" s="22"/>
       <x:c r="E37" s="22"/>
       <x:c r="F37" s="22"/>
-      <x:c r="G37" s="22"/>
-      <x:c r="H37" s="22"/>
+      <x:c r="H37" s="10"/>
       <x:c r="I37" s="22"/>
       <x:c r="J37" s="22"/>
       <x:c r="K37" s="22"/>
@@ -4750,7 +4680,7 @@
       <x:c r="AR37" s="33"/>
       <x:c r="AS37" s="34"/>
       <x:c r="AT37" s="32" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="AU37" s="33"/>
       <x:c r="AV37" s="33"/>
@@ -4766,21 +4696,19 @@
     <x:row r="38" spans="1:56">
       <x:c r="A38" s="6"/>
       <x:c r="B38" s="10"/>
-      <x:c r="C38" s="10"/>
       <x:c r="D38" s="22"/>
       <x:c r="E38" s="22"/>
       <x:c r="F38" s="22"/>
-      <x:c r="G38" s="22"/>
-      <x:c r="H38" s="22"/>
+      <x:c r="H38" s="10"/>
       <x:c r="I38" s="22"/>
       <x:c r="J38" s="22"/>
       <x:c r="K38" s="22"/>
       <x:c r="L38" s="22"/>
       <x:c r="M38" s="22"/>
-      <x:c r="N38" s="72" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="O38" s="72"/>
+      <x:c r="N38" s="27"/>
+      <x:c r="O38" s="72" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="P38" s="72"/>
       <x:c r="Q38" s="72"/>
       <x:c r="R38" s="72"/>
@@ -4794,7 +4722,7 @@
       <x:c r="Z38" s="72"/>
       <x:c r="AA38" s="72"/>
       <x:c r="AB38" s="72"/>
-      <x:c r="AC38" s="22"/>
+      <x:c r="AC38" s="72"/>
       <x:c r="AD38" s="22"/>
       <x:c r="AE38" s="22"/>
       <x:c r="AF38" s="22"/>
@@ -4826,18 +4754,16 @@
     <x:row r="39" spans="1:56">
       <x:c r="A39" s="6"/>
       <x:c r="B39" s="10"/>
-      <x:c r="C39" s="10"/>
       <x:c r="D39" s="22"/>
       <x:c r="E39" s="22"/>
       <x:c r="F39" s="22"/>
-      <x:c r="G39" s="22"/>
-      <x:c r="H39" s="22"/>
+      <x:c r="H39" s="10"/>
       <x:c r="I39" s="22"/>
       <x:c r="J39" s="22"/>
       <x:c r="K39" s="22"/>
       <x:c r="L39" s="22"/>
       <x:c r="M39" s="22"/>
-      <x:c r="N39" s="72"/>
+      <x:c r="N39" s="27"/>
       <x:c r="O39" s="72"/>
       <x:c r="P39" s="72"/>
       <x:c r="Q39" s="72"/>
@@ -4852,7 +4778,7 @@
       <x:c r="Z39" s="72"/>
       <x:c r="AA39" s="72"/>
       <x:c r="AB39" s="72"/>
-      <x:c r="AC39" s="22"/>
+      <x:c r="AC39" s="72"/>
       <x:c r="AD39" s="22"/>
       <x:c r="AE39" s="22"/>
       <x:c r="AF39" s="22"/>
@@ -4870,7 +4796,7 @@
       <x:c r="AR39" s="36"/>
       <x:c r="AS39" s="37"/>
       <x:c r="AT39" s="32" t="s">
-        <x:v>98</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AU39" s="33"/>
       <x:c r="AV39" s="33"/>
@@ -4886,18 +4812,16 @@
     <x:row r="40" spans="1:56">
       <x:c r="A40" s="6"/>
       <x:c r="B40" s="10"/>
-      <x:c r="C40" s="10"/>
       <x:c r="D40" s="22"/>
       <x:c r="E40" s="22"/>
       <x:c r="F40" s="22"/>
-      <x:c r="G40" s="22"/>
-      <x:c r="H40" s="22"/>
+      <x:c r="H40" s="10"/>
       <x:c r="I40" s="22"/>
       <x:c r="J40" s="22"/>
       <x:c r="K40" s="22"/>
       <x:c r="L40" s="22"/>
       <x:c r="M40" s="22"/>
-      <x:c r="N40" s="72"/>
+      <x:c r="N40" s="27"/>
       <x:c r="O40" s="72"/>
       <x:c r="P40" s="72"/>
       <x:c r="Q40" s="72"/>
@@ -4912,7 +4836,7 @@
       <x:c r="Z40" s="72"/>
       <x:c r="AA40" s="72"/>
       <x:c r="AB40" s="72"/>
-      <x:c r="AC40" s="22"/>
+      <x:c r="AC40" s="72"/>
       <x:c r="AD40" s="22"/>
       <x:c r="AE40" s="22"/>
       <x:c r="AF40" s="22"/>
@@ -4946,20 +4870,18 @@
       <x:c r="B41" s="27">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C41" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="D41" s="27"/>
       <x:c r="E41" s="27"/>
       <x:c r="F41" s="27"/>
-      <x:c r="G41" s="27"/>
-      <x:c r="H41" s="27"/>
+      <x:c r="H41" s="27" t="s">
+        <x:v>97</x:v>
+      </x:c>
       <x:c r="I41" s="27"/>
       <x:c r="J41" s="27"/>
       <x:c r="K41" s="27"/>
       <x:c r="L41" s="27"/>
       <x:c r="M41" s="22"/>
-      <x:c r="N41" s="72"/>
+      <x:c r="N41" s="27"/>
       <x:c r="O41" s="72"/>
       <x:c r="P41" s="72"/>
       <x:c r="Q41" s="72"/>
@@ -4974,7 +4896,7 @@
       <x:c r="Z41" s="72"/>
       <x:c r="AA41" s="72"/>
       <x:c r="AB41" s="72"/>
-      <x:c r="AC41" s="22"/>
+      <x:c r="AC41" s="72"/>
       <x:c r="AD41" s="22"/>
       <x:c r="AE41" s="22"/>
       <x:c r="AF41" s="22"/>
@@ -4986,7 +4908,7 @@
       <x:c r="AL41" s="10"/>
       <x:c r="AM41" s="10"/>
       <x:c r="AN41" s="32" t="s">
-        <x:v>153</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AO41" s="33"/>
       <x:c r="AP41" s="33"/>
@@ -4994,7 +4916,7 @@
       <x:c r="AR41" s="33"/>
       <x:c r="AS41" s="34"/>
       <x:c r="AT41" s="32" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="AU41" s="33"/>
       <x:c r="AV41" s="33"/>
@@ -5222,7 +5144,7 @@
       <x:c r="AL45" s="10"/>
       <x:c r="AM45" s="10"/>
       <x:c r="AN45" s="32" t="s">
-        <x:v>159</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AO45" s="33"/>
       <x:c r="AP45" s="33"/>
@@ -5288,7 +5210,7 @@
       <x:c r="AK46" s="9"/>
       <x:c r="AL46" s="9"/>
       <x:c r="AM46" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AN46" s="38"/>
       <x:c r="AO46" s="39"/>
@@ -5511,11 +5433,11 @@
     <x:mergeCell ref="AN17:AP17"/>
     <x:mergeCell ref="AU17:AW17"/>
     <x:mergeCell ref="AZ17:BB17"/>
-    <x:mergeCell ref="N2:AB5"/>
-    <x:mergeCell ref="N11:AB14"/>
-    <x:mergeCell ref="N20:AB23"/>
-    <x:mergeCell ref="N29:AB32"/>
-    <x:mergeCell ref="N38:AB41"/>
+    <x:mergeCell ref="O11:AC14"/>
+    <x:mergeCell ref="O2:AC5"/>
+    <x:mergeCell ref="O38:AC41"/>
+    <x:mergeCell ref="O20:AC23"/>
+    <x:mergeCell ref="O29:AC32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <x:pageMargins left="0.8263888955116272" right="0.23597222566604614" top="0.74750000238418579" bottom="0.35430556535720825" header="0.31486111879348755" footer="0.31486111879348755"/>
